--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 695-2023</t>
+          <t>A 25306-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44930</v>
+        <v>46176</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>13.6</v>
+        <v>3.2</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -647,12 +647,244 @@
         <v>10</v>
       </c>
       <c r="T2" t="n">
+        <v>14</v>
+      </c>
+      <c r="U2" t="n">
+        <v>14</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Slåtterfibbla
+Tallticka
+Blåmossa
+Mindre märgborre
+Kransmossa
+Liljekonvalj
+Spillkråka
+Tofsmes
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 24599-2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44727</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
+        <v>11</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Almsnabbvinge
+Mindre tåtelsmygare
+Igelkottsröksvamp
+Mandelriska
+Sotriska
+Mattlummer
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 695-2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>44930</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="n">
         <v>18</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U4" t="n">
         <v>18</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Brunlångöra
 Dropptaggsvamp
@@ -666,268 +898,36 @@
 Vattenfladdermus</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 24599-2022</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>44727</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="n">
-        <v>11</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Almsnabbvinge
-Mindre tåtelsmygare
-Igelkottsröksvamp
-Mandelriska
-Sotriska
-Mattlummer
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 25306-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>14</v>
-      </c>
-      <c r="U4" t="n">
-        <v>14</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Slåtterfibbla
-Tallticka
-Blåmossa
-Mindre märgborre
-Kransmossa
-Liljekonvalj
-Spillkråka
-Tofsmes
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
         <v/>
       </c>
     </row>
@@ -951,7 +951,7 @@
         <v>46154</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>45684</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 12818-2026</t>
+          <t>A 48514-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46092</v>
+        <v>45936</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1203,20 +1203,20 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>17.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="n">
         <v>2</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
@@ -1227,21 +1227,142 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
+        <v>7</v>
+      </c>
+      <c r="R7" t="n">
         <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
       </c>
       <c r="T7" t="n">
+        <v>90</v>
+      </c>
+      <c r="U7" t="n">
+        <v>88</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Lammticka
+Motaggsvamp
+Skarp dropptaggsvamp
+Svartvit taggsvamp
+Tallticka
+Talltita
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 48514-2025 artfynd.xlsx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 48514-2025 karta.png", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 48514-2025 georefererad karta.tif", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 48514-2025 FSC-klagomål.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 48514-2025 FSC-klagomål mail.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 48514-2025 tillsynsbegäran.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 48514-2025 tillsynsbegäran mail.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 48514-2025 prioriterade fågelarter.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 12818-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
         <v>13</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>3</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Vintertagging
@@ -1253,157 +1374,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12818-2026 artfynd.xlsx", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12818-2026 karta.png", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12818-2026 georefererad karta.tif", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12818-2026 FSC-klagomål.docx", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12818-2026 FSC-klagomål mail.docx", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12818-2026 tillsynsbegäran.docx", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12818-2026 tillsynsbegäran mail.docx", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12818-2026 prioriterade fågelarter.docx", "A 12818-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 48514-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45936</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>7</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>90</v>
-      </c>
-      <c r="U8" t="n">
-        <v>88</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Lammticka
-Motaggsvamp
-Skarp dropptaggsvamp
-Svartvit taggsvamp
-Tallticka
-Talltita
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 48514-2025 artfynd.xlsx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 48514-2025 karta.png", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 48514-2025 georefererad karta.tif", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 48514-2025 FSC-klagomål.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 48514-2025 FSC-klagomål mail.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 48514-2025 tillsynsbegäran.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 48514-2025 tillsynsbegäran mail.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 48514-2025 prioriterade fågelarter.docx", "A 48514-2025")</f>
         <v/>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>46171</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 18100-2022</t>
+          <t>A 25319-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44684</v>
+        <v>46176</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2695,256 +2695,256 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
+          <t>Grovticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 25315-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 18100-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44684</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>Svart trolldruva
 Gullviva</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 25319-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Grovticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 25315-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
         <v/>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 15690-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45481</v>
+        <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3090,17 +3090,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3130,42 +3130,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 61514-2022</t>
+          <t>A 14214-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44916</v>
+        <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3207,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3219,51 +3219,55 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
         <v/>
       </c>
     </row>
@@ -3287,7 +3291,7 @@
         <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3401,7 +3405,7 @@
         <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3515,7 +3519,7 @@
         <v>46092</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3608,7 +3612,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 14214-2025</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3622,10 +3626,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45740</v>
+        <v>44586</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3638,19 +3642,19 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>17.1</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3662,62 +3666,58 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1691-2023</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44938</v>
+        <v>45481</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
@@ -3791,38 +3791,38 @@
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 1691-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44586</v>
+        <v>44938</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>17.1</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3888,46 +3888,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 15690-2023</t>
+          <t>A 61514-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45020</v>
+        <v>44916</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3957,16 +3957,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3997,35 +3997,35 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>44463</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>44859</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 48656-2022</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44859</v>
+        <v>45740</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4514,13 +4514,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4563,7 +4558,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4577,10 +4572,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45406</v>
+        <v>45062</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4593,7 +4588,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4636,7 +4631,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 46405-2022</t>
+          <t>A 30925-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4650,10 +4645,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44846</v>
+        <v>45113</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4665,8 +4660,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4709,7 +4709,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 14217-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44812</v>
+        <v>45740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4782,7 +4782,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 73194-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4799,7 +4799,7 @@
         <v>44550</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4855,7 +4855,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 16483-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45020</v>
+        <v>45029</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4928,7 +4928,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 12306-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4942,10 +4942,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45740</v>
+        <v>46087</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4957,8 +4957,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5001,7 +5006,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 12306-2026</t>
+          <t>A 12294-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5018,7 +5023,7 @@
         <v>46087</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5036,7 +5041,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5079,7 +5084,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 12294-2026</t>
+          <t>A 54468-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5093,10 +5098,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46087</v>
+        <v>45965</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5108,13 +5113,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 46405-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45062</v>
+        <v>44846</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 20649-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45678</v>
+        <v>44700</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5308,7 +5308,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 54468-2025</t>
+          <t>A 8528-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5318,14 +5318,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45965</v>
+        <v>45355</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5381,7 +5381,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 45869-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45376</v>
+        <v>44844</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5454,7 +5454,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 3686-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44550</v>
+        <v>44586</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5527,7 +5527,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 73194-2021</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5541,10 +5541,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44550</v>
+        <v>45020</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5600,7 +5600,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46154</v>
+        <v>44550</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5673,7 +5673,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5746,7 +5746,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5763,7 +5763,7 @@
         <v>46164</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5836,7 +5836,7 @@
         <v>46164</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 20649-2022</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44700</v>
+        <v>46164</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5921,13 +5921,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5970,7 +5965,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 27717-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5980,14 +5975,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44599</v>
+        <v>46190</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5999,8 +5994,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6043,7 +6043,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8528-2024</t>
+          <t>A 9032-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6053,14 +6053,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45355</v>
+        <v>44979</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6116,7 +6116,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3686-2022</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6130,10 +6130,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44586</v>
+        <v>44550</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6189,7 +6189,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 27717-2026</t>
+          <t>A 35108-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6203,10 +6203,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46190</v>
+        <v>46258</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6218,13 +6218,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6267,7 +6262,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9032-2023</t>
+          <t>A 48656-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6281,10 +6276,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44979</v>
+        <v>44859</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6296,8 +6291,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6340,7 +6340,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 25217-2024</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6350,14 +6350,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45462</v>
+        <v>44812</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6369,13 +6369,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6418,7 +6413,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16483-2023</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6432,10 +6427,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45029</v>
+        <v>45376</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6448,7 +6443,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6491,7 +6486,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 35108-2026</t>
+          <t>A 25217-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6501,14 +6496,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46258</v>
+        <v>45462</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6520,8 +6515,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>6.4</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6581,7 +6581,7 @@
         <v>45495</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 30925-2023</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45113</v>
+        <v>45406</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6666,13 +6666,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6715,7 +6710,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 45869-2022</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6729,10 +6724,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44844</v>
+        <v>45678</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6744,8 +6739,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6788,7 +6788,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14217-2025</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6798,14 +6798,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45740</v>
+        <v>44599</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6861,7 +6861,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11876-2024</t>
+          <t>A 16142-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45376</v>
+        <v>45406</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6934,7 +6934,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 16142-2024</t>
+          <t>A 11876-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6948,10 +6948,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45406</v>
+        <v>45376</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
         <v>46065</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 25306-2026</t>
+          <t>A 24599-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46176</v>
+        <v>44727</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,45 +614,277 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>4</v>
       </c>
-      <c r="K2" t="n">
+      <c r="R2" t="n">
         <v>2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
       </c>
       <c r="T2" t="n">
+        <v>11</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Almsnabbvinge
+Mindre tåtelsmygare
+Igelkottsröksvamp
+Mandelriska
+Sotriska
+Mattlummer
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 695-2023</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44930</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
+        <v>18</v>
+      </c>
+      <c r="U3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Brunlångöra
+Dropptaggsvamp
+Gulsparv
+Motaggsvamp
+Nordfladdermus
+Spillkråka
+Dvärgpipistrell
+Kungsfågel
+Större brunfladdermus
+Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 25306-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="n">
         <v>14</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U4" t="n">
         <v>14</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Slåtterfibbla
@@ -666,268 +898,36 @@
 Gröngöling</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 24599-2022</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>44727</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="n">
-        <v>11</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Almsnabbvinge
-Mindre tåtelsmygare
-Igelkottsröksvamp
-Mandelriska
-Sotriska
-Mattlummer
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 695-2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44930</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>18</v>
-      </c>
-      <c r="U4" t="n">
-        <v>18</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Brunlångöra
-Dropptaggsvamp
-Gulsparv
-Motaggsvamp
-Nordfladdermus
-Spillkråka
-Dvärgpipistrell
-Kungsfågel
-Större brunfladdermus
-Vattenfladdermus</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
         <v/>
       </c>
     </row>
@@ -951,7 +951,7 @@
         <v>46154</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>45684</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 48514-2025</t>
+          <t>A 12818-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45936</v>
+        <v>46092</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1203,45 +1203,166 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>17.1</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>7</v>
-      </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
       </c>
       <c r="T7" t="n">
+        <v>13</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Vintertagging
+Blomkålssvamp
+Blåmossa
+Grovticka
+Nattskärra
+Tofsmes
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12818-2026 artfynd.xlsx", "A 12818-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12818-2026 karta.png", "A 12818-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12818-2026 georefererad karta.tif", "A 12818-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12818-2026 FSC-klagomål.docx", "A 12818-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12818-2026 FSC-klagomål mail.docx", "A 12818-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12818-2026 tillsynsbegäran.docx", "A 12818-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12818-2026 tillsynsbegäran mail.docx", "A 12818-2026")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12818-2026 prioriterade fågelarter.docx", "A 12818-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 48514-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45936</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
         <v>90</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>88</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Lammticka
@@ -1253,157 +1374,36 @@
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 48514-2025 artfynd.xlsx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 48514-2025 karta.png", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 48514-2025 georefererad karta.tif", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 48514-2025 FSC-klagomål.docx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 48514-2025 FSC-klagomål mail.docx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 48514-2025 tillsynsbegäran.docx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 48514-2025 tillsynsbegäran mail.docx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 48514-2025 prioriterade fågelarter.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 12818-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46092</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>13</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Vintertagging
-Blomkålssvamp
-Blåmossa
-Grovticka
-Nattskärra
-Tofsmes
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12818-2026 artfynd.xlsx", "A 12818-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12818-2026 karta.png", "A 12818-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12818-2026 georefererad karta.tif", "A 12818-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12818-2026 FSC-klagomål.docx", "A 12818-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12818-2026 FSC-klagomål mail.docx", "A 12818-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12818-2026 tillsynsbegäran.docx", "A 12818-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12818-2026 tillsynsbegäran mail.docx", "A 12818-2026")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12818-2026 prioriterade fågelarter.docx", "A 12818-2026")</f>
         <v/>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 30378-2024</t>
+          <t>A 18100-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2202,14 +2202,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45491</v>
+        <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2222,16 +2222,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2246,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2255,696 +2255,696 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Svart trolldruva
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 30378-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45491</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Mindre tåtelsmygare
 Svinrot</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 30378-2024 artfynd.xlsx", "A 30378-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 30378-2024 karta.png", "A 30378-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 30378-2024 georefererad karta.tif", "A 30378-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 30378-2024 FSC-klagomål.docx", "A 30378-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 30378-2024 FSC-klagomål mail.docx", "A 30378-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 30378-2024 tillsynsbegäran.docx", "A 30378-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 30378-2024 tillsynsbegäran mail.docx", "A 30378-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 15905-2022</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>44664</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>11.2</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>2</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>3</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15905-2022 artfynd.xlsx", "A 15905-2022")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15905-2022 karta.png", "A 15905-2022")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15905-2022 georefererad karta.tif", "A 15905-2022")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15905-2022 FSC-klagomål.docx", "A 15905-2022")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15905-2022 FSC-klagomål mail.docx", "A 15905-2022")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15905-2022 tillsynsbegäran.docx", "A 15905-2022")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15905-2022 tillsynsbegäran mail.docx", "A 15905-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 60406-2025</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>45995</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="E19" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I19" t="n">
         <v>2.3</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>2</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>2</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 60406-2025 artfynd.xlsx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 60406-2025 karta.png", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 60406-2025 georefererad karta.tif", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 60406-2025 FSC-klagomål.docx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 60406-2025 FSC-klagomål mail.docx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 60406-2025 tillsynsbegäran.docx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 60406-2025 tillsynsbegäran mail.docx", "A 60406-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 24799-2026</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>46171</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>1.7</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>2</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Mindre märgborre
 Spillkråka</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24799-2026 artfynd.xlsx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24799-2026 karta.png", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24799-2026 georefererad karta.tif", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24799-2026 FSC-klagomål.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24799-2026 FSC-klagomål mail.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24799-2026 tillsynsbegäran.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24799-2026 tillsynsbegäran mail.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 24799-2026 prioriterade fågelarter.docx", "A 24799-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 25319-2026</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>46176</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>1.6</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>3</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Grovticka
 Spillkråka</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 25315-2026</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>46176</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+      <c r="E22" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>1.4</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>3</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>3</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tofsmes</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 18100-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44684</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Svart trolldruva
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
         <v/>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15690-2023</t>
+          <t>A 12305-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45020</v>
+        <v>46087</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3089,17 +3089,22 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3114,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3130,42 +3135,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14214-2025</t>
+          <t>A 12590-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3179,10 +3188,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45740</v>
+        <v>46090</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3194,8 +3203,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3204,10 +3218,10 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3222,59 +3236,59 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12305-2026</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3288,10 +3302,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46087</v>
+        <v>45481</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3303,19 +3317,14 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3349,46 +3358,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12590-2026</t>
+          <t>A 12842-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3402,10 +3407,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3423,10 +3428,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3463,46 +3468,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12842-2026</t>
+          <t>A 61514-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3516,10 +3517,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46092</v>
+        <v>44916</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3531,22 +3532,17 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3561,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3573,46 +3569,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 14214-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3626,10 +3622,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44586</v>
+        <v>45740</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3642,20 +3638,20 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>17.1</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3666,58 +3662,62 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 1691-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45481</v>
+        <v>44938</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
@@ -3791,38 +3791,38 @@
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1691-2023</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44938</v>
+        <v>44586</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>17.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3888,46 +3888,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61514-2022</t>
+          <t>A 15690-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44916</v>
+        <v>45020</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3957,17 +3957,17 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3997,35 +3997,35 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 73772-2021</t>
+          <t>A 52035-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44552</v>
+        <v>44463</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 52035-2021</t>
+          <t>A 48656-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44463</v>
+        <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4363,8 +4363,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4407,7 +4412,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48647-2022</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4421,10 +4426,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44859</v>
+        <v>45406</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4436,13 +4441,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4485,7 +4485,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 48647-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45740</v>
+        <v>44859</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4514,8 +4514,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4558,7 +4563,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 73772-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4572,10 +4577,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45062</v>
+        <v>44552</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4631,7 +4636,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30925-2023</t>
+          <t>A 46405-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4645,10 +4650,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45113</v>
+        <v>44846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4660,13 +4665,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4709,7 +4709,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 14217-2025</t>
+          <t>A 20649-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45740</v>
+        <v>44700</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4738,8 +4738,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4782,7 +4787,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 73194-2021</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4796,10 +4801,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44550</v>
+        <v>44812</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4812,7 +4817,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4855,7 +4860,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 16483-2023</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4865,14 +4870,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45029</v>
+        <v>44599</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4885,7 +4890,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4928,7 +4933,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12306-2026</t>
+          <t>A 8528-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4938,14 +4943,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46087</v>
+        <v>45355</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4957,13 +4962,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5006,7 +5006,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 12294-2026</t>
+          <t>A 3686-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5020,10 +5020,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46087</v>
+        <v>44586</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5035,13 +5035,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5084,7 +5079,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 54468-2025</t>
+          <t>A 12306-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5098,10 +5093,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45965</v>
+        <v>46087</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5113,8 +5108,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 46405-2022</t>
+          <t>A 12294-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44846</v>
+        <v>46087</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5186,8 +5186,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5230,7 +5235,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 20649-2022</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5244,10 +5249,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44700</v>
+        <v>44550</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5259,13 +5264,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5308,7 +5308,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8528-2024</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5318,14 +5318,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45355</v>
+        <v>45020</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5381,7 +5381,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45869-2022</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44844</v>
+        <v>45740</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5454,7 +5454,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3686-2022</t>
+          <t>A 54468-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44586</v>
+        <v>45965</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5527,7 +5527,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 9032-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5541,10 +5541,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45020</v>
+        <v>44979</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5600,7 +5600,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 25217-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5610,14 +5610,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44550</v>
+        <v>45462</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5629,8 +5629,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5673,7 +5678,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5687,10 +5692,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46154</v>
+        <v>45062</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5703,7 +5708,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5746,7 +5751,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5760,10 +5765,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5776,7 +5781,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5819,7 +5824,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 23716-2026</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5833,10 +5838,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46164</v>
+        <v>45678</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5848,8 +5853,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5892,7 +5902,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5909,7 +5919,7 @@
         <v>46164</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5922,7 +5932,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5965,7 +5975,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 27717-2026</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5979,10 +5989,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46190</v>
+        <v>46164</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5994,13 +6004,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6043,7 +6048,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 9032-2023</t>
+          <t>A 23716-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6057,10 +6062,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44979</v>
+        <v>46164</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6073,7 +6078,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6116,7 +6121,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6130,10 +6135,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44550</v>
+        <v>45376</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6146,7 +6151,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6189,7 +6194,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35108-2026</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6203,10 +6208,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46258</v>
+        <v>44550</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6219,7 +6224,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6262,7 +6267,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 48656-2022</t>
+          <t>A 73194-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6276,10 +6281,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44859</v>
+        <v>44550</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6289,11 +6294,6 @@
       <c r="G63" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -6340,7 +6340,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 16483-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6354,10 +6354,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44812</v>
+        <v>45029</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6413,7 +6413,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 27717-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6427,10 +6427,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45376</v>
+        <v>46190</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6442,8 +6442,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6486,7 +6491,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 25217-2024</t>
+          <t>A 30622-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6500,10 +6505,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45462</v>
+        <v>45495</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6515,13 +6520,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30622-2024</t>
+          <t>A 30925-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6574,14 +6574,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45495</v>
+        <v>45113</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6593,8 +6593,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6637,7 +6642,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 35108-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6651,10 +6656,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45406</v>
+        <v>46258</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6667,7 +6672,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>6.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6710,7 +6715,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 45869-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6724,10 +6729,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45678</v>
+        <v>44844</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6739,13 +6744,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6788,7 +6788,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 14217-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6798,14 +6798,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44599</v>
+        <v>45740</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6861,7 +6861,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 16142-2024</t>
+          <t>A 11876-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45406</v>
+        <v>45376</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6934,7 +6934,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11876-2024</t>
+          <t>A 16142-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6948,10 +6948,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45376</v>
+        <v>45406</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
         <v>46065</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -601,7 +601,7 @@
         <v>44727</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 695-2023</t>
+          <t>A 25306-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44930</v>
+        <v>46176</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -728,16 +728,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.6</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -752,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -761,12 +761,130 @@
         <v>10</v>
       </c>
       <c r="T3" t="n">
+        <v>14</v>
+      </c>
+      <c r="U3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Slåtterfibbla
+Tallticka
+Blåmossa
+Mindre märgborre
+Kransmossa
+Liljekonvalj
+Spillkråka
+Tofsmes
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 695-2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>44930</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="n">
         <v>18</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>18</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Brunlångöra
 Dropptaggsvamp
@@ -780,154 +898,36 @@
 Vattenfladdermus</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 25306-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>14</v>
-      </c>
-      <c r="U4" t="n">
-        <v>14</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Slåtterfibbla
-Tallticka
-Blåmossa
-Mindre märgborre
-Kransmossa
-Liljekonvalj
-Spillkråka
-Tofsmes
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
         <v/>
       </c>
     </row>
@@ -951,7 +951,7 @@
         <v>46154</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>45684</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 12818-2026</t>
+          <t>A 48514-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46092</v>
+        <v>45936</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1203,20 +1203,20 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>17.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="n">
         <v>2</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
@@ -1227,21 +1227,142 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
+        <v>7</v>
+      </c>
+      <c r="R7" t="n">
         <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
       </c>
       <c r="T7" t="n">
+        <v>90</v>
+      </c>
+      <c r="U7" t="n">
+        <v>88</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Lammticka
+Motaggsvamp
+Skarp dropptaggsvamp
+Svartvit taggsvamp
+Tallticka
+Talltita
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 48514-2025 artfynd.xlsx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 48514-2025 karta.png", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 48514-2025 georefererad karta.tif", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 48514-2025 FSC-klagomål.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 48514-2025 FSC-klagomål mail.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 48514-2025 tillsynsbegäran.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 48514-2025 tillsynsbegäran mail.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 48514-2025 prioriterade fågelarter.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 12818-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
         <v>13</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>3</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Vintertagging
@@ -1253,157 +1374,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12818-2026 artfynd.xlsx", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12818-2026 karta.png", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12818-2026 georefererad karta.tif", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12818-2026 FSC-klagomål.docx", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12818-2026 FSC-klagomål mail.docx", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12818-2026 tillsynsbegäran.docx", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12818-2026 tillsynsbegäran mail.docx", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12818-2026 prioriterade fågelarter.docx", "A 12818-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 48514-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45936</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>7</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>90</v>
-      </c>
-      <c r="U8" t="n">
-        <v>88</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Lammticka
-Motaggsvamp
-Skarp dropptaggsvamp
-Svartvit taggsvamp
-Tallticka
-Talltita
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 48514-2025 artfynd.xlsx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 48514-2025 karta.png", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 48514-2025 georefererad karta.tif", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 48514-2025 FSC-klagomål.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 48514-2025 FSC-klagomål mail.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 48514-2025 tillsynsbegäran.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 48514-2025 tillsynsbegäran mail.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 48514-2025 prioriterade fågelarter.docx", "A 48514-2025")</f>
         <v/>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18100-2022</t>
+          <t>A 30378-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2202,14 +2202,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44684</v>
+        <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2222,16 +2222,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2246,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2255,696 +2255,696 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 30378-2024 artfynd.xlsx", "A 30378-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 30378-2024 karta.png", "A 30378-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 30378-2024 georefererad karta.tif", "A 30378-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 30378-2024 FSC-klagomål.docx", "A 30378-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 30378-2024 FSC-klagomål mail.docx", "A 30378-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 30378-2024 tillsynsbegäran.docx", "A 30378-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 30378-2024 tillsynsbegäran mail.docx", "A 30378-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 15905-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44664</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>3</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15905-2022 artfynd.xlsx", "A 15905-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15905-2022 karta.png", "A 15905-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15905-2022 georefererad karta.tif", "A 15905-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15905-2022 FSC-klagomål.docx", "A 15905-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15905-2022 FSC-klagomål mail.docx", "A 15905-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15905-2022 tillsynsbegäran.docx", "A 15905-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15905-2022 tillsynsbegäran mail.docx", "A 15905-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 60406-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 60406-2025 artfynd.xlsx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 60406-2025 karta.png", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 60406-2025 georefererad karta.tif", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 60406-2025 FSC-klagomål.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 60406-2025 FSC-klagomål mail.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 60406-2025 tillsynsbegäran.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 60406-2025 tillsynsbegäran mail.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 24799-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Mindre märgborre
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24799-2026 artfynd.xlsx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24799-2026 karta.png", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24799-2026 georefererad karta.tif", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24799-2026 FSC-klagomål.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24799-2026 FSC-klagomål mail.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24799-2026 tillsynsbegäran.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24799-2026 tillsynsbegäran mail.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 24799-2026 prioriterade fågelarter.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 25319-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Grovticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 25315-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 18100-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44684</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Svart trolldruva
 Gullviva</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 30378-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45491</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Mindre tåtelsmygare
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 30378-2024 artfynd.xlsx", "A 30378-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 30378-2024 karta.png", "A 30378-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 30378-2024 georefererad karta.tif", "A 30378-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 30378-2024 FSC-klagomål.docx", "A 30378-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 30378-2024 FSC-klagomål mail.docx", "A 30378-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 30378-2024 tillsynsbegäran.docx", "A 30378-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 30378-2024 tillsynsbegäran mail.docx", "A 30378-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 15905-2022</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44664</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15905-2022 artfynd.xlsx", "A 15905-2022")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15905-2022 karta.png", "A 15905-2022")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15905-2022 georefererad karta.tif", "A 15905-2022")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15905-2022 FSC-klagomål.docx", "A 15905-2022")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15905-2022 FSC-klagomål mail.docx", "A 15905-2022")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15905-2022 tillsynsbegäran.docx", "A 15905-2022")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15905-2022 tillsynsbegäran mail.docx", "A 15905-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 60406-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45995</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 60406-2025 artfynd.xlsx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 60406-2025 karta.png", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 60406-2025 georefererad karta.tif", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 60406-2025 FSC-klagomål.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 60406-2025 FSC-klagomål mail.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 60406-2025 tillsynsbegäran.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 60406-2025 tillsynsbegäran mail.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 24799-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Mindre märgborre
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24799-2026 artfynd.xlsx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24799-2026 karta.png", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24799-2026 georefererad karta.tif", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24799-2026 FSC-klagomål.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24799-2026 FSC-klagomål mail.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24799-2026 tillsynsbegäran.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24799-2026 tillsynsbegäran mail.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 24799-2026 prioriterade fågelarter.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 25319-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Grovticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 25315-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
         <v/>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12305-2026</t>
+          <t>A 15690-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46087</v>
+        <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3089,23 +3089,18 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3119,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3135,46 +3130,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12590-2026</t>
+          <t>A 14214-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3188,10 +3179,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46090</v>
+        <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3203,13 +3194,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3218,10 +3204,10 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3236,59 +3222,59 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 12305-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3302,10 +3288,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45481</v>
+        <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3317,14 +3303,19 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3358,42 +3349,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12842-2026</t>
+          <t>A 12590-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3407,10 +3402,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46092</v>
+        <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3428,10 +3423,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3468,42 +3463,46 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 61514-2022</t>
+          <t>A 12842-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3517,10 +3516,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44916</v>
+        <v>46092</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,18 +3531,23 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3557,7 +3561,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3569,46 +3573,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 14214-2025</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3622,10 +3626,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45740</v>
+        <v>44586</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3638,19 +3642,19 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>17.1</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3662,62 +3666,58 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1691-2023</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44938</v>
+        <v>45481</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
@@ -3791,38 +3791,38 @@
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 1691-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44586</v>
+        <v>44938</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>17.1</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3888,46 +3888,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 15690-2023</t>
+          <t>A 61514-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45020</v>
+        <v>44916</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3957,16 +3957,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3997,35 +3997,35 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 52035-2021</t>
+          <t>A 73772-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44463</v>
+        <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 48656-2022</t>
+          <t>A 52035-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44859</v>
+        <v>44463</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4363,13 +4363,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4412,7 +4407,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 48647-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4426,10 +4421,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45406</v>
+        <v>44859</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4441,8 +4436,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4485,7 +4485,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 48647-2022</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44859</v>
+        <v>45740</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4514,13 +4514,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4563,7 +4558,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 73772-2021</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4577,10 +4572,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44552</v>
+        <v>45062</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4636,7 +4631,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 46405-2022</t>
+          <t>A 30925-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4650,10 +4645,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44846</v>
+        <v>45113</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4665,8 +4660,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4709,7 +4709,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20649-2022</t>
+          <t>A 14217-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44700</v>
+        <v>45740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4738,13 +4738,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4787,7 +4782,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 73194-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4801,10 +4796,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44812</v>
+        <v>44550</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4817,7 +4812,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4860,7 +4855,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 16483-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4870,14 +4865,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44599</v>
+        <v>45029</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4890,7 +4885,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4933,7 +4928,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8528-2024</t>
+          <t>A 54468-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4943,14 +4938,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45355</v>
+        <v>45965</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4963,7 +4958,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5006,7 +5001,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 3686-2022</t>
+          <t>A 46405-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5020,10 +5015,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44586</v>
+        <v>44846</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5036,7 +5031,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5079,7 +5074,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 12306-2026</t>
+          <t>A 20649-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5093,10 +5088,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46087</v>
+        <v>44700</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5114,7 +5109,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5157,7 +5152,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 12294-2026</t>
+          <t>A 8528-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5167,14 +5162,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46087</v>
+        <v>45355</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5186,13 +5181,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5235,7 +5225,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 12306-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5249,10 +5239,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44550</v>
+        <v>46087</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5264,8 +5254,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5308,7 +5303,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 12294-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5322,10 +5317,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45020</v>
+        <v>46087</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5337,8 +5332,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5381,7 +5381,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 45869-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45740</v>
+        <v>44844</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5454,7 +5454,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 54468-2025</t>
+          <t>A 3686-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45965</v>
+        <v>44586</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5527,7 +5527,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 9032-2023</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5541,10 +5541,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44979</v>
+        <v>45020</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5600,7 +5600,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 25217-2024</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5610,14 +5610,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45462</v>
+        <v>44550</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5629,13 +5629,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5678,7 +5673,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 9032-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5692,10 +5687,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45062</v>
+        <v>44979</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5708,7 +5703,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5751,7 +5746,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5765,10 +5760,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46154</v>
+        <v>44550</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5781,7 +5776,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5824,7 +5819,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 48656-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5838,10 +5833,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45678</v>
+        <v>44859</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5859,7 +5854,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5902,7 +5897,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5916,10 +5911,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46164</v>
+        <v>44812</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5932,7 +5927,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5975,7 +5970,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5989,10 +5984,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46164</v>
+        <v>45376</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6005,7 +6000,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6048,7 +6043,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 23716-2026</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6062,10 +6057,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6078,7 +6073,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6121,7 +6116,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6135,10 +6130,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45376</v>
+        <v>46164</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6151,7 +6146,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6194,7 +6189,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 23716-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6208,10 +6203,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44550</v>
+        <v>46164</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6224,7 +6219,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6267,7 +6262,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 73194-2021</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6281,10 +6276,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44550</v>
+        <v>46164</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6297,7 +6292,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6340,7 +6335,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16483-2023</t>
+          <t>A 25217-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6350,14 +6345,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45029</v>
+        <v>45462</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6369,8 +6364,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>46190</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>45495</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30925-2023</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45113</v>
+        <v>45406</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6593,13 +6593,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6659,7 +6654,7 @@
         <v>46258</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6715,7 +6710,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 45869-2022</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6729,10 +6724,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44844</v>
+        <v>45678</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6744,8 +6739,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6788,7 +6788,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14217-2025</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6798,14 +6798,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45740</v>
+        <v>44599</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6861,7 +6861,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11876-2024</t>
+          <t>A 16142-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45376</v>
+        <v>45406</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6934,7 +6934,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 16142-2024</t>
+          <t>A 11876-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6948,10 +6948,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45406</v>
+        <v>45376</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
         <v>46065</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 24599-2022</t>
+          <t>A 695-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44727</v>
+        <v>44930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>13.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -638,21 +638,139 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
       </c>
       <c r="T2" t="n">
+        <v>18</v>
+      </c>
+      <c r="U2" t="n">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Brunlångöra
+Dropptaggsvamp
+Gulsparv
+Motaggsvamp
+Nordfladdermus
+Spillkråka
+Dvärgpipistrell
+Kungsfågel
+Större brunfladdermus
+Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 24599-2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44727</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
         <v>11</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U3" t="n">
         <v>3</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -666,107 +784,107 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>A 25306-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D4" s="1" t="n">
         <v>46176</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
+      <c r="E4" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>3.2</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>4</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" t="n">
         <v>2</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>10</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T4" t="n">
         <v>14</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>14</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Slåtterfibbla
@@ -780,154 +898,36 @@
 Gröngöling</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 695-2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44930</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>18</v>
-      </c>
-      <c r="U4" t="n">
-        <v>18</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Brunlångöra
-Dropptaggsvamp
-Gulsparv
-Motaggsvamp
-Nordfladdermus
-Spillkråka
-Dvärgpipistrell
-Kungsfågel
-Större brunfladdermus
-Vattenfladdermus</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
         <v/>
       </c>
     </row>
@@ -951,7 +951,7 @@
         <v>46154</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>45684</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 48514-2025</t>
+          <t>A 12818-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45936</v>
+        <v>46092</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1203,45 +1203,166 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>17.1</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>7</v>
-      </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
       </c>
       <c r="T7" t="n">
+        <v>13</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Vintertagging
+Blomkålssvamp
+Blåmossa
+Grovticka
+Nattskärra
+Tofsmes
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12818-2026 artfynd.xlsx", "A 12818-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12818-2026 karta.png", "A 12818-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12818-2026 georefererad karta.tif", "A 12818-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12818-2026 FSC-klagomål.docx", "A 12818-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12818-2026 FSC-klagomål mail.docx", "A 12818-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12818-2026 tillsynsbegäran.docx", "A 12818-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12818-2026 tillsynsbegäran mail.docx", "A 12818-2026")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12818-2026 prioriterade fågelarter.docx", "A 12818-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 48514-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45936</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
         <v>90</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>88</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Lammticka
@@ -1253,157 +1374,36 @@
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 48514-2025 artfynd.xlsx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 48514-2025 karta.png", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 48514-2025 georefererad karta.tif", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 48514-2025 FSC-klagomål.docx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 48514-2025 FSC-klagomål mail.docx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 48514-2025 tillsynsbegäran.docx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 48514-2025 tillsynsbegäran mail.docx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 48514-2025 prioriterade fågelarter.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 12818-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46092</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>13</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Vintertagging
-Blomkålssvamp
-Blåmossa
-Grovticka
-Nattskärra
-Tofsmes
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12818-2026 artfynd.xlsx", "A 12818-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12818-2026 karta.png", "A 12818-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12818-2026 georefererad karta.tif", "A 12818-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12818-2026 FSC-klagomål.docx", "A 12818-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12818-2026 FSC-klagomål mail.docx", "A 12818-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12818-2026 tillsynsbegäran.docx", "A 12818-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12818-2026 tillsynsbegäran mail.docx", "A 12818-2026")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12818-2026 prioriterade fågelarter.docx", "A 12818-2026")</f>
         <v/>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 60406-2025</t>
+          <t>A 24799-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45995</v>
+        <v>46171</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,19 +2433,14 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2479,472 +2474,477 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
+          <t>Mindre märgborre
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24799-2026 artfynd.xlsx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24799-2026 karta.png", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24799-2026 georefererad karta.tif", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24799-2026 FSC-klagomål.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24799-2026 FSC-klagomål mail.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24799-2026 tillsynsbegäran.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24799-2026 tillsynsbegäran mail.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 24799-2026 prioriterade fågelarter.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 25319-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Grovticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 25315-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 18100-2022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>44684</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Svart trolldruva
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 60406-2025</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>Björksplintborre
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 60406-2025 artfynd.xlsx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 60406-2025 karta.png", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 60406-2025 georefererad karta.tif", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 60406-2025 FSC-klagomål.docx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 60406-2025 FSC-klagomål mail.docx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 60406-2025 tillsynsbegäran.docx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 60406-2025 tillsynsbegäran mail.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 24799-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Mindre märgborre
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24799-2026 artfynd.xlsx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24799-2026 karta.png", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24799-2026 georefererad karta.tif", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24799-2026 FSC-klagomål.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24799-2026 FSC-klagomål mail.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24799-2026 tillsynsbegäran.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24799-2026 tillsynsbegäran mail.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 24799-2026 prioriterade fågelarter.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 25319-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Grovticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 25315-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 18100-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44684</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Svart trolldruva
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
         <v/>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15690-2023</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45020</v>
+        <v>45481</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3090,16 +3090,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3130,42 +3130,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14214-2025</t>
+          <t>A 61514-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45740</v>
+        <v>44916</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3207,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3219,55 +3219,51 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
     </row>
@@ -3291,7 +3287,7 @@
         <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3405,7 +3401,7 @@
         <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3519,7 +3515,7 @@
         <v>46092</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3612,7 +3608,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 14214-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3626,10 +3622,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44586</v>
+        <v>45740</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3642,20 +3638,20 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>17.1</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3666,58 +3662,62 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 1691-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45481</v>
+        <v>44938</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
@@ -3791,38 +3791,38 @@
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1691-2023</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44938</v>
+        <v>44586</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>17.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3888,46 +3888,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61514-2022</t>
+          <t>A 15690-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44916</v>
+        <v>45020</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3957,17 +3957,17 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3997,35 +3997,35 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>44463</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>44859</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45740</v>
+        <v>45406</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4558,7 +4558,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 46405-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45062</v>
+        <v>44846</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4631,7 +4631,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30925-2023</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45113</v>
+        <v>44812</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4660,13 +4660,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4709,7 +4704,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 14217-2025</t>
+          <t>A 48656-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4723,10 +4718,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45740</v>
+        <v>44859</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4738,8 +4733,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4782,7 +4782,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 73194-2021</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4799,7 +4799,7 @@
         <v>44550</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4855,7 +4855,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 16483-2023</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45029</v>
+        <v>45020</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4928,7 +4928,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54468-2025</t>
+          <t>A 12306-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4942,10 +4942,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45965</v>
+        <v>46087</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4957,8 +4957,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5001,7 +5006,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46405-2022</t>
+          <t>A 12294-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5015,10 +5020,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44846</v>
+        <v>46087</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5030,8 +5035,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5074,7 +5084,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20649-2022</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5088,10 +5098,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44700</v>
+        <v>45740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5103,13 +5113,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5152,7 +5157,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 8528-2024</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5162,14 +5167,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45355</v>
+        <v>45062</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5182,7 +5187,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5225,7 +5230,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 12306-2026</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5239,10 +5244,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46087</v>
+        <v>45678</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5260,7 +5265,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5303,7 +5308,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12294-2026</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5317,10 +5322,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46087</v>
+        <v>45376</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5332,13 +5337,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5381,7 +5381,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45869-2022</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44844</v>
+        <v>46154</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5454,7 +5454,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3686-2022</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44586</v>
+        <v>44550</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5527,7 +5527,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 73194-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5541,10 +5541,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45020</v>
+        <v>44550</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5600,7 +5600,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44550</v>
+        <v>46164</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5673,7 +5673,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9032-2023</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44979</v>
+        <v>46164</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5746,7 +5746,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 23716-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5760,10 +5760,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44550</v>
+        <v>46164</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5819,7 +5819,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 48656-2022</t>
+          <t>A 27717-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44859</v>
+        <v>46190</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5897,7 +5897,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 54468-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5911,10 +5911,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44812</v>
+        <v>45965</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5970,7 +5970,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 20649-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45376</v>
+        <v>44700</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5999,8 +5999,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6043,7 +6048,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 35108-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6057,10 +6062,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46154</v>
+        <v>46258</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6073,7 +6078,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>6.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6116,7 +6121,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6126,14 +6131,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46164</v>
+        <v>44599</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6146,7 +6151,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6189,7 +6194,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 23716-2026</t>
+          <t>A 8528-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6199,14 +6204,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46164</v>
+        <v>45355</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6219,7 +6224,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6262,7 +6267,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 3686-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6276,10 +6281,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46164</v>
+        <v>44586</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6292,7 +6297,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6335,7 +6340,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 25217-2024</t>
+          <t>A 9032-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6345,14 +6350,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45462</v>
+        <v>44979</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6364,13 +6369,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6413,7 +6413,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27717-2026</t>
+          <t>A 25217-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6423,14 +6423,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46190</v>
+        <v>45462</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30622-2024</t>
+          <t>A 16483-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6501,14 +6501,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45495</v>
+        <v>45029</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 30622-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6574,14 +6574,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45406</v>
+        <v>45495</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 35108-2026</t>
+          <t>A 30925-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46258</v>
+        <v>45113</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6666,8 +6666,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>6.4</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6710,7 +6715,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 45869-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6724,10 +6729,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45678</v>
+        <v>44844</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6739,13 +6744,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6788,7 +6788,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 14217-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6798,14 +6798,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44599</v>
+        <v>45740</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6861,7 +6861,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 16142-2024</t>
+          <t>A 11876-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45406</v>
+        <v>45376</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6934,7 +6934,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11876-2024</t>
+          <t>A 16142-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6948,10 +6948,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45376</v>
+        <v>45406</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
         <v>46065</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 695-2023</t>
+          <t>A 24599-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44930</v>
+        <v>44727</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>13.6</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -638,21 +638,135 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
       </c>
       <c r="T2" t="n">
+        <v>11</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Almsnabbvinge
+Mindre tåtelsmygare
+Igelkottsröksvamp
+Mandelriska
+Sotriska
+Mattlummer
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 695-2023</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44930</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
         <v>18</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U3" t="n">
         <v>18</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Brunlångöra
 Dropptaggsvamp
@@ -666,150 +780,36 @@
 Vattenfladdermus</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 24599-2022</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>44727</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="n">
-        <v>11</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Almsnabbvinge
-Mindre tåtelsmygare
-Igelkottsröksvamp
-Mandelriska
-Sotriska
-Mattlummer
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
         <v/>
       </c>
     </row>
@@ -833,7 +833,7 @@
         <v>46176</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>46154</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>45684</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 12818-2026</t>
+          <t>A 48514-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46092</v>
+        <v>45936</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1203,20 +1203,20 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>17.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="n">
         <v>2</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
@@ -1227,21 +1227,142 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
+        <v>7</v>
+      </c>
+      <c r="R7" t="n">
         <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
       </c>
       <c r="T7" t="n">
+        <v>90</v>
+      </c>
+      <c r="U7" t="n">
+        <v>88</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Lammticka
+Motaggsvamp
+Skarp dropptaggsvamp
+Svartvit taggsvamp
+Tallticka
+Talltita
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 48514-2025 artfynd.xlsx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 48514-2025 karta.png", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 48514-2025 georefererad karta.tif", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 48514-2025 FSC-klagomål.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 48514-2025 FSC-klagomål mail.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 48514-2025 tillsynsbegäran.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 48514-2025 tillsynsbegäran mail.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 48514-2025 prioriterade fågelarter.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 12818-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
         <v>13</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>3</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Vintertagging
@@ -1253,157 +1374,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12818-2026 artfynd.xlsx", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12818-2026 karta.png", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12818-2026 georefererad karta.tif", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12818-2026 FSC-klagomål.docx", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12818-2026 FSC-klagomål mail.docx", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12818-2026 tillsynsbegäran.docx", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12818-2026 tillsynsbegäran mail.docx", "A 12818-2026")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12818-2026 prioriterade fågelarter.docx", "A 12818-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 48514-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45936</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>7</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>90</v>
-      </c>
-      <c r="U8" t="n">
-        <v>88</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Lammticka
-Motaggsvamp
-Skarp dropptaggsvamp
-Svartvit taggsvamp
-Tallticka
-Talltita
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 48514-2025 artfynd.xlsx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 48514-2025 karta.png", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 48514-2025 georefererad karta.tif", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 48514-2025 FSC-klagomål.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 48514-2025 FSC-klagomål mail.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 48514-2025 tillsynsbegäran.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 48514-2025 tillsynsbegäran mail.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 48514-2025 prioriterade fågelarter.docx", "A 48514-2025")</f>
         <v/>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24799-2026</t>
+          <t>A 60406-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46171</v>
+        <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,14 +2433,19 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2474,477 +2479,472 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
+          <t>Björksplintborre
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 60406-2025 artfynd.xlsx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 60406-2025 karta.png", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 60406-2025 georefererad karta.tif", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 60406-2025 FSC-klagomål.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 60406-2025 FSC-klagomål mail.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 60406-2025 tillsynsbegäran.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 60406-2025 tillsynsbegäran mail.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 24799-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>Mindre märgborre
 Spillkråka</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24799-2026 artfynd.xlsx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24799-2026 karta.png", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24799-2026 georefererad karta.tif", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24799-2026 FSC-klagomål.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24799-2026 FSC-klagomål mail.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24799-2026 tillsynsbegäran.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24799-2026 tillsynsbegäran mail.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 24799-2026 prioriterade fågelarter.docx", "A 24799-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 25319-2026</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>46176</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>1.6</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>3</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>3</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Grovticka
 Spillkråka</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 25315-2026</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>46176</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>1.4</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>3</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tofsmes</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 18100-2022</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>44684</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+      <c r="E22" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>3.1</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>3</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>3</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Svart trolldruva
 Gullviva</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 60406-2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45995</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 60406-2025 artfynd.xlsx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 60406-2025 karta.png", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 60406-2025 georefererad karta.tif", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 60406-2025 FSC-klagomål.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 60406-2025 FSC-klagomål mail.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 60406-2025 tillsynsbegäran.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 60406-2025 tillsynsbegäran mail.docx", "A 60406-2025")</f>
         <v/>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 15690-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45481</v>
+        <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3090,17 +3090,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3130,42 +3130,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 61514-2022</t>
+          <t>A 14214-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44916</v>
+        <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3207,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3219,58 +3219,62 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12305-2026</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3284,10 +3288,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46087</v>
+        <v>44586</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3299,19 +3303,14 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>17.1</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3345,46 +3344,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12590-2026</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3398,10 +3393,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46090</v>
+        <v>45481</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3413,22 +3408,17 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3443,7 +3433,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3455,50 +3445,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12842-2026</t>
+          <t>A 12305-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3512,10 +3498,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46092</v>
+        <v>46087</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3533,16 +3519,16 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3557,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3569,46 +3555,50 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 14214-2025</t>
+          <t>A 12590-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3622,10 +3612,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45740</v>
+        <v>46090</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3637,8 +3627,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3647,10 +3642,10 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3665,59 +3660,59 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1691-2023</t>
+          <t>A 12842-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3731,10 +3726,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44938</v>
+        <v>46092</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3744,6 +3739,11 @@
       <c r="G30" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -3753,11 +3753,11 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
@@ -3771,7 +3771,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3787,42 +3787,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 1691-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44586</v>
+        <v>44938</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>17.1</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3888,46 +3888,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 15690-2023</t>
+          <t>A 61514-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45020</v>
+        <v>44916</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3957,16 +3957,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3997,35 +3997,35 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>44463</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>44859</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45406</v>
+        <v>45062</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4558,7 +4558,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 46405-2022</t>
+          <t>A 30925-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44846</v>
+        <v>45113</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4587,8 +4587,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4631,7 +4636,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4645,10 +4650,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44812</v>
+        <v>45740</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4661,7 +4666,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4704,7 +4709,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 48656-2022</t>
+          <t>A 14217-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4718,10 +4723,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44859</v>
+        <v>45740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4733,13 +4738,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4782,7 +4782,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 73194-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4799,7 +4799,7 @@
         <v>44550</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4855,7 +4855,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 16483-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45020</v>
+        <v>45029</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4928,7 +4928,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12306-2026</t>
+          <t>A 46405-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4942,10 +4942,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46087</v>
+        <v>44846</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4957,13 +4957,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5006,7 +5001,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 12294-2026</t>
+          <t>A 20649-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5020,10 +5015,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46087</v>
+        <v>44700</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5041,7 +5036,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5084,7 +5079,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 8528-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5094,14 +5089,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45740</v>
+        <v>45355</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5114,7 +5109,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5157,7 +5152,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 45869-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5171,10 +5166,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45062</v>
+        <v>44844</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5187,7 +5182,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5230,7 +5225,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 3686-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5244,10 +5239,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45678</v>
+        <v>44586</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5259,13 +5254,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5308,7 +5298,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5322,10 +5312,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45376</v>
+        <v>45020</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5338,7 +5328,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5381,7 +5371,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5395,10 +5385,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46154</v>
+        <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5411,7 +5401,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5454,7 +5444,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 9032-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5468,10 +5458,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44550</v>
+        <v>44979</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5484,7 +5474,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5527,7 +5517,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 73194-2021</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5541,10 +5531,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44550</v>
+        <v>46154</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5557,7 +5547,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5600,7 +5590,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 54468-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5614,10 +5604,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46164</v>
+        <v>45965</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5630,7 +5620,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5673,7 +5663,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5687,10 +5677,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46164</v>
+        <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5703,7 +5693,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5746,7 +5736,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23716-2026</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5763,7 +5753,7 @@
         <v>46164</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5776,7 +5766,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5819,7 +5809,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 27717-2026</t>
+          <t>A 48656-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5833,10 +5823,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46190</v>
+        <v>44859</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5854,7 +5844,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5897,7 +5887,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 54468-2025</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5911,10 +5901,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45965</v>
+        <v>44812</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5927,7 +5917,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5970,7 +5960,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 20649-2022</t>
+          <t>A 23716-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5984,10 +5974,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44700</v>
+        <v>46164</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5999,13 +5989,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6048,7 +6033,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35108-2026</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6062,10 +6047,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46258</v>
+        <v>46164</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6078,7 +6063,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6121,7 +6106,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6131,14 +6116,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44599</v>
+        <v>45376</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6151,7 +6136,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6194,7 +6179,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8528-2024</t>
+          <t>A 25217-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6208,10 +6193,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45355</v>
+        <v>45462</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6223,8 +6208,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6267,7 +6257,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 3686-2022</t>
+          <t>A 12306-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6281,10 +6271,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44586</v>
+        <v>46087</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6296,8 +6286,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6340,7 +6335,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 9032-2023</t>
+          <t>A 12294-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6354,10 +6349,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44979</v>
+        <v>46087</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6369,8 +6364,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6413,7 +6413,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 25217-2024</t>
+          <t>A 27717-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6423,14 +6423,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45462</v>
+        <v>46190</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 16483-2023</t>
+          <t>A 30622-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6501,14 +6501,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45029</v>
+        <v>45495</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30622-2024</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6574,14 +6574,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45495</v>
+        <v>45406</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 30925-2023</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45113</v>
+        <v>45678</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6715,7 +6715,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 45869-2022</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6725,14 +6725,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44844</v>
+        <v>44599</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6788,7 +6788,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14217-2025</t>
+          <t>A 35108-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6802,10 +6802,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45740</v>
+        <v>46258</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6861,7 +6861,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11876-2024</t>
+          <t>A 16142-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45376</v>
+        <v>45406</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6934,7 +6934,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 16142-2024</t>
+          <t>A 11876-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6948,10 +6948,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45406</v>
+        <v>45376</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
         <v>46065</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -601,7 +601,7 @@
         <v>44727</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>44930</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>46176</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>46154</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,24 +1051,24 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S 254-2025</t>
+          <t>A 48514-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45684</v>
+        <v>45936</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1080,21 +1080,26 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>4.5</v>
+        <v>17.1</v>
       </c>
       <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="n">
         <v>3</v>
       </c>
-      <c r="K6" t="n">
-        <v>4</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
@@ -1105,21 +1110,138 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
       </c>
       <c r="T6" t="n">
+        <v>91</v>
+      </c>
+      <c r="U6" t="n">
+        <v>89</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Hasselsnok
+Igelkott
+Lammticka
+Motaggsvamp
+Skarp dropptaggsvamp
+Svartvit taggsvamp
+Tallticka
+Talltita
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 48514-2025 artfynd.xlsx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 48514-2025 karta.png", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 48514-2025 georefererad karta.tif", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 48514-2025 FSC-klagomål.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 48514-2025 FSC-klagomål mail.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 48514-2025 tillsynsbegäran.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 48514-2025 tillsynsbegäran mail.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 48514-2025 prioriterade fågelarter.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S 254-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45684</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>9</v>
+      </c>
+      <c r="T7" t="n">
         <v>13</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Fyrflikig jordstjärna
 Orange taggsvamp
@@ -1132,157 +1254,36 @@
 Mattlummer</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/S 254-2025 artfynd.xlsx", "S 254-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/S 254-2025 karta.png", "S 254-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/S 254-2025 georefererad karta.tif", "S 254-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/S 254-2025 FSC-klagomål.docx", "S 254-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/S 254-2025 FSC-klagomål mail.docx", "S 254-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/S 254-2025 tillsynsbegäran.docx", "S 254-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/S 254-2025 tillsynsbegäran mail.docx", "S 254-2025")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/S 254-2025 prioriterade fågelarter.docx", "S 254-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 48514-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45936</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>7</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>90</v>
-      </c>
-      <c r="U7" t="n">
-        <v>88</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Lammticka
-Motaggsvamp
-Skarp dropptaggsvamp
-Svartvit taggsvamp
-Tallticka
-Talltita
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 48514-2025 artfynd.xlsx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 48514-2025 karta.png", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 48514-2025 georefererad karta.tif", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 48514-2025 FSC-klagomål.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 48514-2025 FSC-klagomål mail.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 48514-2025 tillsynsbegäran.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 48514-2025 tillsynsbegäran mail.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 48514-2025 prioriterade fågelarter.docx", "A 48514-2025")</f>
         <v/>
       </c>
     </row>
@@ -1306,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1357,10 +1358,10 @@
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
@@ -1427,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1766,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1878,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1990,7 +1991,7 @@
         <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2097,7 +2098,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2209,7 +2210,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2315,7 +2316,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2421,7 +2422,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2532,7 +2533,7 @@
         <v>46171</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2642,7 +2643,7 @@
         <v>46176</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2752,7 +2753,7 @@
         <v>46176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2862,7 +2863,7 @@
         <v>44684</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2968,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3077,7 +3078,7 @@
         <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3182,7 +3183,7 @@
         <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3291,7 +3292,7 @@
         <v>44586</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3396,7 +3397,7 @@
         <v>45481</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3501,7 +3502,7 @@
         <v>46087</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3615,7 +3616,7 @@
         <v>46090</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3729,7 +3730,7 @@
         <v>46092</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3839,7 +3840,7 @@
         <v>44938</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3944,7 +3945,7 @@
         <v>44916</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4049,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4122,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4200,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4278,7 +4279,7 @@
         <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4351,7 +4352,7 @@
         <v>44463</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4424,7 +4425,7 @@
         <v>44859</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4502,7 +4503,7 @@
         <v>45062</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4575,7 +4576,7 @@
         <v>45113</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4653,7 +4654,7 @@
         <v>45740</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4726,7 +4727,7 @@
         <v>45740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4799,7 +4800,7 @@
         <v>44550</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4872,7 +4873,7 @@
         <v>45029</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4945,7 +4946,7 @@
         <v>44846</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5018,7 +5019,7 @@
         <v>44700</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5096,7 +5097,7 @@
         <v>45355</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5169,7 +5170,7 @@
         <v>44844</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5242,7 +5243,7 @@
         <v>44586</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5315,7 +5316,7 @@
         <v>45020</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5388,7 +5389,7 @@
         <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5461,7 +5462,7 @@
         <v>44979</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5534,7 +5535,7 @@
         <v>46154</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5607,7 +5608,7 @@
         <v>45965</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5680,7 +5681,7 @@
         <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5753,7 +5754,7 @@
         <v>46164</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5826,7 +5827,7 @@
         <v>44859</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5904,7 +5905,7 @@
         <v>44812</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5977,7 +5978,7 @@
         <v>46164</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6050,7 +6051,7 @@
         <v>46164</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6123,7 +6124,7 @@
         <v>45376</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6196,7 +6197,7 @@
         <v>45462</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6274,7 +6275,7 @@
         <v>46087</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6352,7 +6353,7 @@
         <v>46087</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6430,7 +6431,7 @@
         <v>46190</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6508,7 +6509,7 @@
         <v>45495</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6581,7 +6582,7 @@
         <v>45406</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6654,7 +6655,7 @@
         <v>45678</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6732,7 +6733,7 @@
         <v>44599</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6805,7 +6806,7 @@
         <v>46258</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6878,7 +6879,7 @@
         <v>45406</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6951,7 +6952,7 @@
         <v>45376</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7024,7 +7025,7 @@
         <v>46065</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -601,7 +601,7 @@
         <v>44727</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 695-2023</t>
+          <t>A 25306-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44930</v>
+        <v>46176</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -728,16 +728,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.6</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -752,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -761,12 +761,130 @@
         <v>10</v>
       </c>
       <c r="T3" t="n">
+        <v>14</v>
+      </c>
+      <c r="U3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Slåtterfibbla
+Tallticka
+Blåmossa
+Mindre märgborre
+Kransmossa
+Liljekonvalj
+Spillkråka
+Tofsmes
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 695-2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>44930</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="n">
         <v>18</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>18</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Brunlångöra
 Dropptaggsvamp
@@ -780,154 +898,36 @@
 Vattenfladdermus</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 25306-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>14</v>
-      </c>
-      <c r="U4" t="n">
-        <v>14</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Slåtterfibbla
-Tallticka
-Blåmossa
-Mindre märgborre
-Kransmossa
-Liljekonvalj
-Spillkråka
-Tofsmes
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
         <v/>
       </c>
     </row>
@@ -951,7 +951,7 @@
         <v>46154</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>45936</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>46171</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>46176</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>46176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>44684</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 12305-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44586</v>
+        <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3304,14 +3304,19 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>17.1</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3345,42 +3350,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 12590-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3394,10 +3403,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45481</v>
+        <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3409,18 +3418,23 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
@@ -3434,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3446,46 +3460,50 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12305-2026</t>
+          <t>A 12842-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3499,10 +3517,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3520,17 +3538,17 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3544,7 +3562,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3556,50 +3574,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12590-2026</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3613,10 +3627,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46090</v>
+        <v>44586</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3628,22 +3642,17 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>17.1</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3658,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3670,50 +3679,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12842-2026</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3727,10 +3732,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46092</v>
+        <v>45481</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3742,22 +3747,17 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3784,39 +3784,39 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
         <v>44938</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>44916</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44463</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44859</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45062</v>
+        <v>45740</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30925-2023</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45113</v>
+        <v>45062</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4586,11 +4586,6 @@
       <c r="G40" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -4637,7 +4632,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 30925-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4651,10 +4646,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45740</v>
+        <v>45113</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4666,8 +4661,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4727,7 +4727,7 @@
         <v>45740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44550</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>45029</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>44846</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>44700</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45355</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>44844</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>44586</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45020</v>
+        <v>46154</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5372,7 +5372,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44550</v>
+        <v>45020</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5445,7 +5445,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9032-2023</t>
+          <t>A 54468-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44979</v>
+        <v>45965</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5518,7 +5518,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46154</v>
+        <v>44550</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54468-2025</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5605,10 +5605,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45965</v>
+        <v>46164</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 23716-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44550</v>
+        <v>46164</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5737,7 +5737,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5754,7 +5754,7 @@
         <v>46164</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5810,7 +5810,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 48656-2022</t>
+          <t>A 9032-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5824,10 +5824,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44859</v>
+        <v>44979</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5839,13 +5839,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5888,7 +5883,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5902,10 +5897,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44812</v>
+        <v>44550</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5918,7 +5913,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5961,7 +5956,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 23716-2026</t>
+          <t>A 27717-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5975,10 +5970,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46164</v>
+        <v>46190</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5990,8 +5985,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 48656-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6048,10 +6048,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46164</v>
+        <v>44859</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6063,8 +6063,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6107,7 +6112,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6121,10 +6126,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45376</v>
+        <v>44812</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6137,7 +6142,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6180,7 +6185,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25217-2024</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6190,14 +6195,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45462</v>
+        <v>45376</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6209,13 +6214,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6275,7 +6275,7 @@
         <v>46087</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>46087</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27717-2026</t>
+          <t>A 25217-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6424,14 +6424,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46190</v>
+        <v>45462</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>45495</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 35108-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45406</v>
+        <v>46258</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>6.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6638,7 +6638,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45678</v>
+        <v>45406</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6667,13 +6667,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6716,7 +6711,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6726,14 +6721,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44599</v>
+        <v>45678</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6745,8 +6740,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6789,7 +6789,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 35108-2026</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6799,14 +6799,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46258</v>
+        <v>44599</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6879,7 +6879,7 @@
         <v>45406</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>45376</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>46065</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 24599-2022</t>
+          <t>A 695-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44727</v>
+        <v>44930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>13.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -638,21 +638,139 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
       </c>
       <c r="T2" t="n">
+        <v>18</v>
+      </c>
+      <c r="U2" t="n">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Brunlångöra
+Dropptaggsvamp
+Gulsparv
+Motaggsvamp
+Nordfladdermus
+Spillkråka
+Dvärgpipistrell
+Kungsfågel
+Större brunfladdermus
+Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 24599-2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44727</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
         <v>11</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U3" t="n">
         <v>3</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -666,107 +784,107 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>A 25306-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D4" s="1" t="n">
         <v>46176</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
+      <c r="E4" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>3.2</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>4</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" t="n">
         <v>2</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>10</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T4" t="n">
         <v>14</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>14</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Slåtterfibbla
@@ -780,161 +898,43 @@
 Gröngöling</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 695-2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44930</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>18</v>
-      </c>
-      <c r="U4" t="n">
-        <v>18</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Brunlångöra
-Dropptaggsvamp
-Gulsparv
-Motaggsvamp
-Nordfladdermus
-Spillkråka
-Dvärgpipistrell
-Kungsfågel
-Större brunfladdermus
-Vattenfladdermus</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 22390-2026</t>
+          <t>A 48514-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46154</v>
+        <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -963,20 +963,25 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>6.9</v>
+        <v>17.1</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -988,21 +993,138 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
       </c>
       <c r="T5" t="n">
+        <v>91</v>
+      </c>
+      <c r="U5" t="n">
+        <v>89</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Hasselsnok
+Igelkott
+Lammticka
+Motaggsvamp
+Skarp dropptaggsvamp
+Svartvit taggsvamp
+Tallticka
+Talltita
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 48514-2025 artfynd.xlsx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 48514-2025 karta.png", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 48514-2025 georefererad karta.tif", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 48514-2025 FSC-klagomål.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 48514-2025 FSC-klagomål mail.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 48514-2025 tillsynsbegäran.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 48514-2025 tillsynsbegäran mail.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 48514-2025 prioriterade fågelarter.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 22390-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9</v>
+      </c>
+      <c r="T6" t="n">
         <v>16</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Järnsparv
@@ -1015,158 +1137,36 @@
 Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 22390-2026 artfynd.xlsx", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 22390-2026 karta.png", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 22390-2026 georefererad karta.tif", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 22390-2026 FSC-klagomål.docx", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 22390-2026 FSC-klagomål mail.docx", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 22390-2026 tillsynsbegäran.docx", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 22390-2026 tillsynsbegäran mail.docx", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 22390-2026 prioriterade fågelarter.docx", "A 22390-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 48514-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45936</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>8</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>9</v>
-      </c>
-      <c r="T6" t="n">
-        <v>91</v>
-      </c>
-      <c r="U6" t="n">
-        <v>89</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Hasselsnok
-Igelkott
-Lammticka
-Motaggsvamp
-Skarp dropptaggsvamp
-Svartvit taggsvamp
-Tallticka
-Talltita
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 48514-2025 artfynd.xlsx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 48514-2025 karta.png", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 48514-2025 georefererad karta.tif", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 48514-2025 FSC-klagomål.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 48514-2025 FSC-klagomål mail.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 48514-2025 tillsynsbegäran.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 48514-2025 tillsynsbegäran mail.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 48514-2025 prioriterade fågelarter.docx", "A 48514-2025")</f>
         <v/>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1697-2023</t>
+          <t>A 23829-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44938</v>
+        <v>45078</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2003,18 +2003,23 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -2028,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2040,153 +2045,148 @@
         <v>3</v>
       </c>
       <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.
+Tallticka
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 23829-2023 artfynd.xlsx", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 23829-2023 karta.png", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 23829-2023 georefererad karta.tif", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 23829-2023 FSC-klagomål.docx", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 23829-2023 FSC-klagomål mail.docx", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 23829-2023 tillsynsbegäran.docx", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 23829-2023 tillsynsbegäran mail.docx", "A 23829-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 1697-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44938</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Lunglav
 Bårdlav
 Grön sköldmossa</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1697-2023 artfynd.xlsx", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1697-2023 karta.png", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1697-2023 georefererad karta.tif", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1697-2023 FSC-klagomål.docx", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1697-2023 FSC-klagomål mail.docx", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1697-2023 tillsynsbegäran.docx", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1697-2023 tillsynsbegäran mail.docx", "A 1697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 23829-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45078</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.
-Tallticka
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 23829-2023 artfynd.xlsx", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 23829-2023 karta.png", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 23829-2023 georefererad karta.tif", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 23829-2023 FSC-klagomål.docx", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 23829-2023 FSC-klagomål mail.docx", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 23829-2023 tillsynsbegäran.docx", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 23829-2023 tillsynsbegäran mail.docx", "A 23829-2023")</f>
         <v/>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 60406-2025</t>
+          <t>A 18100-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45995</v>
+        <v>44684</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2434,19 +2434,14 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2473,479 +2468,484 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Svart trolldruva
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 60406-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>2</v>
       </c>
-      <c r="U18" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 60406-2025 artfynd.xlsx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 60406-2025 karta.png", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 60406-2025 georefererad karta.tif", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 60406-2025 FSC-klagomål.docx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 60406-2025 FSC-klagomål mail.docx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 60406-2025 tillsynsbegäran.docx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 60406-2025 tillsynsbegäran mail.docx", "A 60406-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 24799-2026</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>46171</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>1.7</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>2</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Mindre märgborre
 Spillkråka</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24799-2026 artfynd.xlsx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24799-2026 karta.png", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24799-2026 georefererad karta.tif", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24799-2026 FSC-klagomål.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24799-2026 FSC-klagomål mail.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24799-2026 tillsynsbegäran.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24799-2026 tillsynsbegäran mail.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 24799-2026 prioriterade fågelarter.docx", "A 24799-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 25319-2026</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>46176</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>1.6</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>3</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Grovticka
 Spillkråka</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 25315-2026</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>46176</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+      <c r="E22" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>1.4</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>3</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>3</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tofsmes</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 18100-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44684</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Svart trolldruva
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
         <v/>
       </c>
     </row>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15690-2023</t>
+          <t>A 14214-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45020</v>
+        <v>45740</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3091,19 +3091,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3118,55 +3118,59 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14214-2025</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3180,10 +3184,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45740</v>
+        <v>45481</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3196,19 +3200,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3220,62 +3224,58 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12305-2026</t>
+          <t>A 1691-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46087</v>
+        <v>44938</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3304,19 +3304,14 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3346,50 +3341,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12590-2026</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3403,10 +3394,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46090</v>
+        <v>44586</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3418,22 +3409,17 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>17.1</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3448,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3460,50 +3446,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12842-2026</t>
+          <t>A 15690-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3517,10 +3499,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46092</v>
+        <v>45020</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,13 +3514,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3574,46 +3551,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 61514-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3627,10 +3604,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44586</v>
+        <v>44916</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3643,13 +3620,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>17.1</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3683,42 +3660,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 12305-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3732,10 +3709,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45481</v>
+        <v>46087</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3747,14 +3724,19 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3788,42 +3770,46 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1691-2023</t>
+          <t>A 12590-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3837,10 +3823,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44938</v>
+        <v>46090</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3852,18 +3838,23 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
@@ -3877,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3893,42 +3884,46 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61514-2022</t>
+          <t>A 12842-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3942,10 +3937,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44916</v>
+        <v>46092</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3957,18 +3952,23 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3994,39 +3994,39 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 73772-2021</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44552</v>
+        <v>45062</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 52035-2021</t>
+          <t>A 73772-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44463</v>
+        <v>44552</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48647-2022</t>
+          <t>A 16142-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44859</v>
+        <v>45406</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4437,13 +4437,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4486,7 +4481,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 52035-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4500,10 +4495,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45740</v>
+        <v>44463</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4516,7 +4511,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4559,7 +4554,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 48647-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4573,10 +4568,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45062</v>
+        <v>44859</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4588,8 +4583,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30925-2023</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45113</v>
+        <v>45678</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4710,7 +4710,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 14217-2025</t>
+          <t>A 48656-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45740</v>
+        <v>44859</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4739,8 +4739,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4783,7 +4788,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 73194-2021</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4797,10 +4802,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44550</v>
+        <v>45406</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4813,7 +4818,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4856,7 +4861,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 16483-2023</t>
+          <t>A 46405-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4870,10 +4875,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45029</v>
+        <v>44846</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4886,7 +4891,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4929,7 +4934,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 46405-2022</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4943,10 +4948,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44846</v>
+        <v>45376</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4959,7 +4964,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5002,7 +5007,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 20649-2022</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5016,10 +5021,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44700</v>
+        <v>44812</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5031,13 +5036,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5080,7 +5080,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8528-2024</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5090,14 +5090,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45355</v>
+        <v>44550</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5153,7 +5153,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 45869-2022</t>
+          <t>A 73194-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44844</v>
+        <v>44550</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5226,7 +5226,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3686-2022</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44586</v>
+        <v>44550</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46154</v>
+        <v>45020</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5372,7 +5372,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 54468-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45020</v>
+        <v>45965</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5445,7 +5445,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 54468-2025</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45965</v>
+        <v>45740</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5518,7 +5518,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 20649-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44550</v>
+        <v>44700</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5547,8 +5547,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5591,7 +5596,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5601,14 +5606,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46164</v>
+        <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5621,7 +5626,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5664,7 +5669,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23716-2026</t>
+          <t>A 8528-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5674,14 +5679,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46164</v>
+        <v>45355</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5694,7 +5699,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5737,7 +5742,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 3686-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5751,10 +5756,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46164</v>
+        <v>44586</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5767,7 +5772,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5827,7 +5832,7 @@
         <v>44979</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5883,7 +5888,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 12306-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5897,10 +5902,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44550</v>
+        <v>46087</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5912,8 +5917,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5956,7 +5966,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 27717-2026</t>
+          <t>A 12294-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5970,10 +5980,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46190</v>
+        <v>46087</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5991,7 +6001,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6034,7 +6044,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 48656-2022</t>
+          <t>A 25217-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6044,14 +6054,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44859</v>
+        <v>45462</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6069,7 +6079,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6112,7 +6122,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 16483-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6126,10 +6136,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44812</v>
+        <v>45029</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6142,7 +6152,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6185,7 +6195,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 30622-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6195,14 +6205,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45376</v>
+        <v>45495</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6215,7 +6225,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6258,7 +6268,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12306-2026</t>
+          <t>A 30925-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6272,10 +6282,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46087</v>
+        <v>45113</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6293,7 +6303,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6336,7 +6346,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12294-2026</t>
+          <t>A 45869-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6350,10 +6360,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46087</v>
+        <v>44844</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6365,13 +6375,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6414,7 +6419,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 25217-2024</t>
+          <t>A 14217-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6424,14 +6429,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45462</v>
+        <v>45740</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6443,13 +6448,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6492,7 +6492,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30622-2024</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6502,14 +6502,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45495</v>
+        <v>46154</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6565,7 +6565,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 35108-2026</t>
+          <t>A 11876-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46258</v>
+        <v>45376</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6638,7 +6638,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45406</v>
+        <v>46164</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6711,7 +6711,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6725,10 +6725,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45678</v>
+        <v>46164</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6740,13 +6740,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6789,7 +6784,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 23716-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6799,14 +6794,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44599</v>
+        <v>46164</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6819,7 +6814,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6862,7 +6857,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 16142-2024</t>
+          <t>A 27717-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6876,10 +6871,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45406</v>
+        <v>46190</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6891,8 +6886,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6935,7 +6935,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11876-2024</t>
+          <t>A 35108-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45376</v>
+        <v>46258</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7025,7 +7025,7 @@
         <v>46065</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE73"/>
+  <dimension ref="A1:AE72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 695-2023</t>
+          <t>A 24599-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44930</v>
+        <v>44727</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>13.6</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -638,21 +638,253 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
       </c>
       <c r="T2" t="n">
+        <v>11</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Almsnabbvinge
+Mindre tåtelsmygare
+Igelkottsröksvamp
+Mandelriska
+Sotriska
+Mattlummer
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 25306-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
+        <v>14</v>
+      </c>
+      <c r="U3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Slåtterfibbla
+Tallticka
+Blåmossa
+Mindre märgborre
+Kransmossa
+Liljekonvalj
+Spillkråka
+Tofsmes
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 695-2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>44930</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="n">
         <v>18</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U4" t="n">
         <v>18</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Brunlångöra
 Dropptaggsvamp
@@ -666,275 +898,43 @@
 Vattenfladdermus</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 24599-2022</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>44727</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="n">
-        <v>11</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Almsnabbvinge
-Mindre tåtelsmygare
-Igelkottsröksvamp
-Mandelriska
-Sotriska
-Mattlummer
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 25306-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>14</v>
-      </c>
-      <c r="U4" t="n">
-        <v>14</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Slåtterfibbla
-Tallticka
-Blåmossa
-Mindre märgborre
-Kransmossa
-Liljekonvalj
-Spillkråka
-Tofsmes
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 48514-2025</t>
+          <t>A 22390-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45936</v>
+        <v>46154</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -963,25 +963,20 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>17.1</v>
+        <v>6.9</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -993,21 +988,143 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
       </c>
       <c r="T5" t="n">
+        <v>16</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Duvhök
+Järnsparv
+Rödvingetrast
+Sparvuggla
+Spillkråka
+Fjällvråk
+Gröngöling
+Kungsfågel
+Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 22390-2026 artfynd.xlsx", "A 22390-2026")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 22390-2026 karta.png", "A 22390-2026")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 22390-2026 georefererad karta.tif", "A 22390-2026")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 22390-2026 FSC-klagomål.docx", "A 22390-2026")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 22390-2026 FSC-klagomål mail.docx", "A 22390-2026")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 22390-2026 tillsynsbegäran.docx", "A 22390-2026")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 22390-2026 tillsynsbegäran mail.docx", "A 22390-2026")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 22390-2026 prioriterade fågelarter.docx", "A 22390-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 48514-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45936</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>8</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9</v>
+      </c>
+      <c r="T6" t="n">
         <v>91</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>89</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Hasselsnok
 Igelkott
@@ -1020,153 +1137,36 @@
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 48514-2025 artfynd.xlsx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 48514-2025 karta.png", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 48514-2025 georefererad karta.tif", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 48514-2025 FSC-klagomål.docx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 48514-2025 FSC-klagomål mail.docx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 48514-2025 tillsynsbegäran.docx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 48514-2025 tillsynsbegäran mail.docx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 48514-2025 prioriterade fågelarter.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 22390-2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>46154</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>9</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>9</v>
-      </c>
-      <c r="T6" t="n">
-        <v>16</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Duvhök
-Järnsparv
-Rödvingetrast
-Sparvuggla
-Spillkråka
-Fjällvråk
-Gröngöling
-Kungsfågel
-Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 22390-2026 artfynd.xlsx", "A 22390-2026")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 22390-2026 karta.png", "A 22390-2026")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 22390-2026 georefererad karta.tif", "A 22390-2026")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 22390-2026 FSC-klagomål.docx", "A 22390-2026")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 22390-2026 FSC-klagomål mail.docx", "A 22390-2026")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 22390-2026 tillsynsbegäran.docx", "A 22390-2026")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 22390-2026 tillsynsbegäran mail.docx", "A 22390-2026")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 22390-2026 prioriterade fågelarter.docx", "A 22390-2026")</f>
         <v/>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 23829-2023</t>
+          <t>A 1697-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45078</v>
+        <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2003,22 +2003,17 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2045,148 +2040,153 @@
         <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Lunglav
+Bårdlav
+Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1697-2023 artfynd.xlsx", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1697-2023 karta.png", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1697-2023 georefererad karta.tif", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1697-2023 FSC-klagomål.docx", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1697-2023 FSC-klagomål mail.docx", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1697-2023 tillsynsbegäran.docx", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1697-2023 tillsynsbegäran mail.docx", "A 1697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 23829-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Fjällig taggsvamp s.str.
 Tallticka
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 23829-2023 artfynd.xlsx", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 23829-2023 karta.png", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 23829-2023 georefererad karta.tif", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 23829-2023 FSC-klagomål.docx", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 23829-2023 FSC-klagomål mail.docx", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 23829-2023 tillsynsbegäran.docx", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 23829-2023 tillsynsbegäran mail.docx", "A 23829-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 1697-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44938</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lunglav
-Bårdlav
-Grön sköldmossa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1697-2023 artfynd.xlsx", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1697-2023 karta.png", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1697-2023 georefererad karta.tif", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1697-2023 FSC-klagomål.docx", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1697-2023 FSC-klagomål mail.docx", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1697-2023 tillsynsbegäran.docx", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1697-2023 tillsynsbegäran mail.docx", "A 1697-2023")</f>
         <v/>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 18100-2022</t>
+          <t>A 60406-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44684</v>
+        <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2434,14 +2434,19 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2468,484 +2473,479 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 60406-2025 artfynd.xlsx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 60406-2025 karta.png", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 60406-2025 georefererad karta.tif", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 60406-2025 FSC-klagomål.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 60406-2025 FSC-klagomål mail.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 60406-2025 tillsynsbegäran.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 60406-2025 tillsynsbegäran mail.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 24799-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Mindre märgborre
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24799-2026 artfynd.xlsx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24799-2026 karta.png", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24799-2026 georefererad karta.tif", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24799-2026 FSC-klagomål.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24799-2026 FSC-klagomål mail.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24799-2026 tillsynsbegäran.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24799-2026 tillsynsbegäran mail.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 24799-2026 prioriterade fågelarter.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 25319-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
         <v>3</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U20" t="n">
         <v>3</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Grovticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 25315-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 18100-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44684</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Svart trolldruva
 Gullviva</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 60406-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45995</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 60406-2025 artfynd.xlsx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 60406-2025 karta.png", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 60406-2025 georefererad karta.tif", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 60406-2025 FSC-klagomål.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 60406-2025 FSC-klagomål mail.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 60406-2025 tillsynsbegäran.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 60406-2025 tillsynsbegäran mail.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 24799-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Mindre märgborre
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24799-2026 artfynd.xlsx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24799-2026 karta.png", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24799-2026 georefererad karta.tif", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24799-2026 FSC-klagomål.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24799-2026 FSC-klagomål mail.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24799-2026 tillsynsbegäran.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24799-2026 tillsynsbegäran mail.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 24799-2026 prioriterade fågelarter.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 25319-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Grovticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 25315-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
         <v/>
       </c>
     </row>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 14214-2025</t>
+          <t>A 15690-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45740</v>
+        <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3091,19 +3091,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3118,59 +3118,55 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 14214-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3184,10 +3180,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45481</v>
+        <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3200,20 +3196,20 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
@@ -3224,58 +3220,62 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 1691-2023</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44938</v>
+        <v>44586</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>17.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3341,46 +3341,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44586</v>
+        <v>45481</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>17.1</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3450,42 +3450,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15690-2023</t>
+          <t>A 12305-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45020</v>
+        <v>46087</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3514,17 +3514,22 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3539,7 +3544,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3555,42 +3560,46 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 61514-2022</t>
+          <t>A 12590-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3604,10 +3613,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44916</v>
+        <v>46090</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3619,8 +3628,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3629,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3644,7 +3658,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3656,46 +3670,50 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12305-2026</t>
+          <t>A 12842-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3709,10 +3727,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3730,17 +3748,17 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
@@ -3754,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3766,50 +3784,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12590-2026</t>
+          <t>A 1691-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3823,10 +3837,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46090</v>
+        <v>44938</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3838,22 +3852,17 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3868,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3884,46 +3893,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12842-2026</t>
+          <t>A 61514-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3937,10 +3942,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46092</v>
+        <v>44916</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3952,22 +3957,17 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3982,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3994,39 +3994,39 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 73772-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45062</v>
+        <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 73772-2021</t>
+          <t>A 48647-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44552</v>
+        <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4364,8 +4364,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4408,7 +4413,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 16142-2024</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4422,10 +4427,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45406</v>
+        <v>45740</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4438,7 +4443,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4481,7 +4486,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 52035-2021</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4495,10 +4500,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44463</v>
+        <v>45062</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4511,7 +4516,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4554,7 +4559,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 48647-2022</t>
+          <t>A 30925-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4568,10 +4573,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44859</v>
+        <v>45113</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4589,7 +4594,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4632,7 +4637,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 14217-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4646,10 +4651,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45678</v>
+        <v>45740</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4661,13 +4666,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4710,7 +4710,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 48656-2022</t>
+          <t>A 73194-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44859</v>
+        <v>44550</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4737,11 +4737,6 @@
       <c r="G42" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -4788,7 +4783,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 16483-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4802,10 +4797,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45406</v>
+        <v>45029</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4818,7 +4813,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4878,7 +4873,7 @@
         <v>44846</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4934,7 +4929,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 20649-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4948,10 +4943,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45376</v>
+        <v>44700</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4963,8 +4958,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5007,7 +5007,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 8528-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5017,14 +5017,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44812</v>
+        <v>45355</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5080,7 +5080,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 45869-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44550</v>
+        <v>44844</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5153,7 +5153,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 73194-2021</t>
+          <t>A 3686-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44550</v>
+        <v>44586</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5226,7 +5226,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44550</v>
+        <v>45020</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45020</v>
+        <v>44550</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5389,7 +5389,7 @@
         <v>45965</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 9032-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45740</v>
+        <v>44979</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5518,7 +5518,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20649-2022</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44700</v>
+        <v>46154</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5547,13 +5547,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5596,7 +5591,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5606,14 +5601,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44599</v>
+        <v>44550</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5626,7 +5621,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5669,7 +5664,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8528-2024</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5679,14 +5674,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45355</v>
+        <v>46164</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5699,7 +5694,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5742,7 +5737,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 3686-2022</t>
+          <t>A 23716-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5756,10 +5751,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44586</v>
+        <v>46164</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5772,7 +5767,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5815,7 +5810,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 9032-2023</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5829,10 +5824,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44979</v>
+        <v>46164</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5845,7 +5840,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5888,7 +5883,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12306-2026</t>
+          <t>A 48656-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5902,10 +5897,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46087</v>
+        <v>44859</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5966,7 +5961,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 12294-2026</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5980,10 +5975,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46087</v>
+        <v>44812</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5995,13 +5990,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6044,7 +6034,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 25217-2024</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6054,14 +6044,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45462</v>
+        <v>45376</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6073,13 +6063,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6122,7 +6107,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16483-2023</t>
+          <t>A 12306-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6136,10 +6121,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45029</v>
+        <v>46087</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6151,8 +6136,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6195,7 +6185,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 30622-2024</t>
+          <t>A 12294-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6205,14 +6195,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45495</v>
+        <v>46087</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6224,8 +6214,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6268,7 +6263,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30925-2023</t>
+          <t>A 27717-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6282,10 +6277,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45113</v>
+        <v>46190</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6303,7 +6298,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6346,7 +6341,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 45869-2022</t>
+          <t>A 25217-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6356,14 +6351,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44844</v>
+        <v>45462</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6375,8 +6370,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6419,7 +6419,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14217-2025</t>
+          <t>A 30622-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6429,14 +6429,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45740</v>
+        <v>45495</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6492,7 +6492,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46154</v>
+        <v>45406</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6565,7 +6565,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 11876-2024</t>
+          <t>A 35108-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45376</v>
+        <v>46258</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6638,7 +6638,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46164</v>
+        <v>45678</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6667,8 +6667,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6711,7 +6716,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6721,14 +6726,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46164</v>
+        <v>44599</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6741,7 +6746,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6784,7 +6789,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 23716-2026</t>
+          <t>A 16142-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6798,10 +6803,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46164</v>
+        <v>45406</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6814,7 +6819,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6857,7 +6862,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 27717-2026</t>
+          <t>A 11876-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6871,10 +6876,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46190</v>
+        <v>45376</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6886,13 +6891,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6932,27 +6932,27 @@
       </c>
       <c r="V71" s="2" t="inlineStr"/>
     </row>
-    <row r="72" ht="15" customHeight="1">
+    <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 35108-2026</t>
+          <t>S 380-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46258</v>
+        <v>46065</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6964,8 +6964,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>6.4</v>
+        <v>0.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7004,84 +7009,6 @@
         <v>0</v>
       </c>
       <c r="V72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>S 380-2026</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="n">
-        <v>46065</v>
-      </c>
-      <c r="E73" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I73" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
-        <v>0</v>
-      </c>
-      <c r="V73" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 24599-2022</t>
+          <t>A 695-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44727</v>
+        <v>44930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>13.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -638,21 +638,257 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
       </c>
       <c r="T2" t="n">
+        <v>18</v>
+      </c>
+      <c r="U2" t="n">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Brunlångöra
+Dropptaggsvamp
+Gulsparv
+Motaggsvamp
+Nordfladdermus
+Spillkråka
+Dvärgpipistrell
+Kungsfågel
+Större brunfladdermus
+Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 25306-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
+        <v>14</v>
+      </c>
+      <c r="U3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Slåtterfibbla
+Tallticka
+Blåmossa
+Mindre märgborre
+Kransmossa
+Liljekonvalj
+Spillkråka
+Tofsmes
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 24599-2022</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>44727</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="n">
         <v>11</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U4" t="n">
         <v>3</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -666,275 +902,39 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 25306-2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="n">
-        <v>14</v>
-      </c>
-      <c r="U3" t="n">
-        <v>14</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Slåtterfibbla
-Tallticka
-Blåmossa
-Mindre märgborre
-Kransmossa
-Liljekonvalj
-Spillkråka
-Tofsmes
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 695-2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44930</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>18</v>
-      </c>
-      <c r="U4" t="n">
-        <v>18</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Brunlångöra
-Dropptaggsvamp
-Gulsparv
-Motaggsvamp
-Nordfladdermus
-Spillkråka
-Dvärgpipistrell
-Kungsfågel
-Större brunfladdermus
-Vattenfladdermus</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 22390-2026</t>
+          <t>A 48514-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46154</v>
+        <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -963,20 +963,25 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>6.9</v>
+        <v>17.1</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -988,21 +993,138 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
       </c>
       <c r="T5" t="n">
+        <v>91</v>
+      </c>
+      <c r="U5" t="n">
+        <v>89</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Hasselsnok
+Igelkott
+Lammticka
+Motaggsvamp
+Skarp dropptaggsvamp
+Svartvit taggsvamp
+Tallticka
+Talltita
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 48514-2025 artfynd.xlsx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 48514-2025 karta.png", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 48514-2025 georefererad karta.tif", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 48514-2025 FSC-klagomål.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 48514-2025 FSC-klagomål mail.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 48514-2025 tillsynsbegäran.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 48514-2025 tillsynsbegäran mail.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 48514-2025 prioriterade fågelarter.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 22390-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9</v>
+      </c>
+      <c r="T6" t="n">
         <v>16</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Järnsparv
@@ -1015,158 +1137,36 @@
 Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 22390-2026 artfynd.xlsx", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 22390-2026 karta.png", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 22390-2026 georefererad karta.tif", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 22390-2026 FSC-klagomål.docx", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 22390-2026 FSC-klagomål mail.docx", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 22390-2026 tillsynsbegäran.docx", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 22390-2026 tillsynsbegäran mail.docx", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 22390-2026 prioriterade fågelarter.docx", "A 22390-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 48514-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45936</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>8</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>9</v>
-      </c>
-      <c r="T6" t="n">
-        <v>91</v>
-      </c>
-      <c r="U6" t="n">
-        <v>89</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Hasselsnok
-Igelkott
-Lammticka
-Motaggsvamp
-Skarp dropptaggsvamp
-Svartvit taggsvamp
-Tallticka
-Talltita
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 48514-2025 artfynd.xlsx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 48514-2025 karta.png", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 48514-2025 georefererad karta.tif", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 48514-2025 FSC-klagomål.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 48514-2025 FSC-klagomål mail.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 48514-2025 tillsynsbegäran.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 48514-2025 tillsynsbegäran mail.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 48514-2025 prioriterade fågelarter.docx", "A 48514-2025")</f>
         <v/>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>46171</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>46176</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>46176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>44684</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15690-2023</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45020</v>
+        <v>45481</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3091,16 +3091,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3131,42 +3131,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14214-2025</t>
+          <t>A 61514-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45740</v>
+        <v>44916</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3208,7 +3208,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3220,62 +3220,58 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 12305-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3289,10 +3285,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44586</v>
+        <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3304,14 +3300,19 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>17.1</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3345,42 +3346,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 12590-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3394,10 +3399,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45481</v>
+        <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3409,18 +3414,23 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
@@ -3434,7 +3444,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3446,46 +3456,50 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12305-2026</t>
+          <t>A 12842-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3499,10 +3513,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3520,17 +3534,17 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3544,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3556,50 +3570,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12590-2026</t>
+          <t>A 14214-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3613,10 +3623,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46090</v>
+        <v>45740</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3628,13 +3638,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3643,10 +3648,10 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3661,59 +3666,59 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12842-2026</t>
+          <t>A 1691-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3727,10 +3732,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46092</v>
+        <v>44938</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3740,11 +3745,6 @@
       <c r="G30" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -3754,10 +3754,10 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3788,42 +3788,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1691-2023</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44938</v>
+        <v>44586</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>17.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3889,46 +3889,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61514-2022</t>
+          <t>A 15690-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44916</v>
+        <v>45020</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3958,17 +3958,17 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3998,35 +3998,35 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 48656-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45740</v>
+        <v>44859</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4442,8 +4442,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4486,7 +4491,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4500,10 +4505,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45062</v>
+        <v>45406</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4516,7 +4521,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4559,7 +4564,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30925-2023</t>
+          <t>A 46405-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4573,10 +4578,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45113</v>
+        <v>44846</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4588,13 +4593,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4637,7 +4637,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 14217-2025</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45740</v>
+        <v>44812</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4710,7 +4710,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 73194-2021</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4727,7 +4727,7 @@
         <v>44550</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4783,7 +4783,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 16483-2023</t>
+          <t>A 12306-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45029</v>
+        <v>46087</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4812,8 +4812,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4856,7 +4861,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 46405-2022</t>
+          <t>A 12294-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4870,10 +4875,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44846</v>
+        <v>46087</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4885,8 +4890,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4929,7 +4939,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 20649-2022</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4943,10 +4953,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44700</v>
+        <v>45020</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4958,13 +4968,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5007,7 +5012,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8528-2024</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5017,14 +5022,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45355</v>
+        <v>45740</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5037,7 +5042,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5080,7 +5085,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 45869-2022</t>
+          <t>A 54468-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5094,10 +5099,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44844</v>
+        <v>45965</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5110,7 +5115,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5153,7 +5158,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3686-2022</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5167,10 +5172,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44586</v>
+        <v>45062</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5183,7 +5188,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5226,7 +5231,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5240,10 +5245,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45020</v>
+        <v>45678</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5255,8 +5260,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5299,7 +5309,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5313,10 +5323,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44550</v>
+        <v>46154</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5329,7 +5339,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5372,7 +5382,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 54468-2025</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5386,10 +5396,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45965</v>
+        <v>45376</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5402,7 +5412,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5445,7 +5455,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9032-2023</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5459,10 +5469,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44979</v>
+        <v>46164</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5475,7 +5485,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5518,7 +5528,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5532,10 +5542,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5548,7 +5558,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5591,7 +5601,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 23716-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5605,10 +5615,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44550</v>
+        <v>46164</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5621,7 +5631,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5664,7 +5674,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5678,10 +5688,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46164</v>
+        <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5694,7 +5704,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5737,7 +5747,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23716-2026</t>
+          <t>A 73194-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5751,10 +5761,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46164</v>
+        <v>44550</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5767,7 +5777,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5810,7 +5820,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 27717-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5824,10 +5834,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46164</v>
+        <v>46190</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5839,8 +5849,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5883,7 +5898,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 48656-2022</t>
+          <t>A 35108-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5897,10 +5912,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44859</v>
+        <v>46258</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5912,13 +5927,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5961,7 +5971,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 20649-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5975,10 +5985,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44812</v>
+        <v>44700</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5990,8 +6000,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6034,7 +6049,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6044,14 +6059,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45376</v>
+        <v>44599</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6064,7 +6079,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6107,7 +6122,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12306-2026</t>
+          <t>A 8528-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6117,14 +6132,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46087</v>
+        <v>45355</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6136,13 +6151,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6185,7 +6195,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12294-2026</t>
+          <t>A 3686-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6199,10 +6209,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46087</v>
+        <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6214,13 +6224,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6263,7 +6268,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 27717-2026</t>
+          <t>A 9032-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6277,10 +6282,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46190</v>
+        <v>44979</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6292,13 +6297,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6358,7 +6358,7 @@
         <v>45462</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30622-2024</t>
+          <t>A 16483-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6429,14 +6429,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45495</v>
+        <v>45029</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6492,7 +6492,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 30622-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6502,14 +6502,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45406</v>
+        <v>45495</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6565,7 +6565,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 35108-2026</t>
+          <t>A 30925-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46258</v>
+        <v>45113</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6594,8 +6594,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>6.4</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6638,7 +6643,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 45869-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6652,10 +6657,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45678</v>
+        <v>44844</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6667,13 +6672,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6716,7 +6716,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 14217-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6726,14 +6726,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44599</v>
+        <v>45740</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6789,7 +6789,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 16142-2024</t>
+          <t>A 11876-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6803,10 +6803,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45406</v>
+        <v>45376</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6862,7 +6862,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11876-2024</t>
+          <t>A 16142-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6876,10 +6876,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45376</v>
+        <v>45406</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>46065</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -601,7 +601,7 @@
         <v>44930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>46176</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>44727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>46171</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>46176</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>46176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>44684</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>45481</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>44916</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>46092</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>45740</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>44938</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>44586</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>45020</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>44859</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>45406</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>44846</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>44812</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44550</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>46087</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>46087</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>45020</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45740</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>45965</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45062</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>45678</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>46154</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45376</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>46164</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>46164</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>46164</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>44550</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>46190</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>46258</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>44700</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>44599</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>45355</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>44979</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>45462</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>45029</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>45495</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>45113</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>44844</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>45740</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>45376</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45406</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>46065</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -601,7 +601,7 @@
         <v>44930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>46176</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>44727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>46171</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>46176</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>46176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>44684</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>45481</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>44916</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>46092</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>45740</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>44938</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>44586</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>45020</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>44859</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>45406</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>44846</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>44812</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44550</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>46087</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>46087</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>45020</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45740</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>45965</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45062</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>45678</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>46154</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45376</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>46164</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>46164</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>46164</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>44550</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>46190</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>46258</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>44700</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>44599</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>45355</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>44979</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>45462</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>45029</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>45495</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>45113</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>44844</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>45740</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>45376</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45406</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>46065</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 695-2023</t>
+          <t>A 24599-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44930</v>
+        <v>44727</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>13.6</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -638,21 +638,253 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
       </c>
       <c r="T2" t="n">
+        <v>11</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Almsnabbvinge
+Mindre tåtelsmygare
+Igelkottsröksvamp
+Mandelriska
+Sotriska
+Mattlummer
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 25306-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
+        <v>14</v>
+      </c>
+      <c r="U3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Slåtterfibbla
+Tallticka
+Blåmossa
+Mindre märgborre
+Kransmossa
+Liljekonvalj
+Spillkråka
+Tofsmes
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 695-2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>44930</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="n">
         <v>18</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U4" t="n">
         <v>18</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Brunlångöra
 Dropptaggsvamp
@@ -666,268 +898,36 @@
 Vattenfladdermus</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 25306-2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="n">
-        <v>14</v>
-      </c>
-      <c r="U3" t="n">
-        <v>14</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Slåtterfibbla
-Tallticka
-Blåmossa
-Mindre märgborre
-Kransmossa
-Liljekonvalj
-Spillkråka
-Tofsmes
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 24599-2022</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44727</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>11</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Almsnabbvinge
-Mindre tåtelsmygare
-Igelkottsröksvamp
-Mandelriska
-Sotriska
-Mattlummer
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
         <v/>
       </c>
     </row>
@@ -951,7 +951,7 @@
         <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>46171</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>46176</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>46176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>44684</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 15690-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45481</v>
+        <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3091,17 +3091,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3131,42 +3131,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 61514-2022</t>
+          <t>A 14214-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44916</v>
+        <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3208,7 +3208,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3220,51 +3220,55 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
         <v/>
       </c>
     </row>
@@ -3288,7 +3292,7 @@
         <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3402,7 +3406,7 @@
         <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3516,7 +3520,7 @@
         <v>46092</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3609,7 +3613,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 14214-2025</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3623,10 +3627,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45740</v>
+        <v>44586</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3639,19 +3643,19 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>17.1</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3663,62 +3667,58 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1691-2023</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44938</v>
+        <v>45481</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3784,7 +3784,7 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
@@ -3792,38 +3792,38 @@
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 1691-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44586</v>
+        <v>44938</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>17.1</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3889,46 +3889,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 15690-2023</t>
+          <t>A 61514-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45020</v>
+        <v>44916</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3958,16 +3958,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3982,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3998,35 +3998,35 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48656-2022</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44859</v>
+        <v>45740</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4442,13 +4442,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4491,7 +4486,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4505,10 +4500,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45406</v>
+        <v>45062</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4521,7 +4516,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4564,7 +4559,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 46405-2022</t>
+          <t>A 30925-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4578,10 +4573,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44846</v>
+        <v>45113</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4593,8 +4588,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4637,7 +4637,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 11876-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44812</v>
+        <v>45376</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4710,7 +4710,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 14217-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44550</v>
+        <v>45740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4783,7 +4783,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12306-2026</t>
+          <t>A 73194-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46087</v>
+        <v>44550</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4810,11 +4810,6 @@
       <c r="G43" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -4861,7 +4856,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12294-2026</t>
+          <t>A 16483-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4875,10 +4870,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46087</v>
+        <v>45029</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4890,13 +4885,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4939,7 +4929,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 54468-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4953,10 +4943,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45020</v>
+        <v>45965</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4969,7 +4959,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5012,7 +5002,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 46405-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5026,10 +5016,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45740</v>
+        <v>44846</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5042,7 +5032,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5085,7 +5075,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 54468-2025</t>
+          <t>A 20649-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5099,10 +5089,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45965</v>
+        <v>44700</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5114,8 +5104,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5158,7 +5153,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 8528-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5168,14 +5163,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45062</v>
+        <v>45355</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5188,7 +5183,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5231,7 +5226,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 45869-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5245,10 +5240,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45678</v>
+        <v>44844</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5260,13 +5255,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5309,7 +5299,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 3686-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5323,10 +5313,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46154</v>
+        <v>44586</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5339,7 +5329,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5382,7 +5372,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 12306-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5396,10 +5386,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45376</v>
+        <v>46087</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5411,8 +5401,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5455,7 +5450,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 12294-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5469,10 +5464,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46164</v>
+        <v>46087</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5484,8 +5479,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5528,7 +5528,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46164</v>
+        <v>45020</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5601,7 +5601,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23716-2026</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46164</v>
+        <v>44550</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5674,7 +5674,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 9032-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44550</v>
+        <v>44979</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5747,7 +5747,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 73194-2021</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5764,7 +5764,7 @@
         <v>44550</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5820,7 +5820,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 27717-2026</t>
+          <t>A 48656-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46190</v>
+        <v>44859</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5898,7 +5898,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35108-2026</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5912,10 +5912,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46258</v>
+        <v>44812</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.4</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5971,7 +5971,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 20649-2022</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44700</v>
+        <v>46154</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6000,13 +6000,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6049,7 +6044,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6059,14 +6054,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44599</v>
+        <v>45376</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6079,7 +6074,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6122,7 +6117,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8528-2024</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6132,14 +6127,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45355</v>
+        <v>46164</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6152,7 +6147,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6195,7 +6190,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3686-2022</t>
+          <t>A 23716-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6209,10 +6204,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44586</v>
+        <v>46164</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6225,7 +6220,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6268,7 +6263,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9032-2023</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6282,10 +6277,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44979</v>
+        <v>46164</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6298,7 +6293,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6358,7 +6353,7 @@
         <v>45462</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6419,7 +6414,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16483-2023</t>
+          <t>A 27717-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6433,10 +6428,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45029</v>
+        <v>46190</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6448,8 +6443,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>45495</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30925-2023</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45113</v>
+        <v>45406</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6594,13 +6594,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6643,7 +6638,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 45869-2022</t>
+          <t>A 35108-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6657,10 +6652,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44844</v>
+        <v>46258</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6673,7 +6668,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6716,7 +6711,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 14217-2025</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6730,10 +6725,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45740</v>
+        <v>45678</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6745,8 +6740,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6789,7 +6789,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11876-2024</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6799,14 +6799,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45376</v>
+        <v>44599</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6879,7 +6879,7 @@
         <v>45406</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>46065</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 24599-2022</t>
+          <t>A 695-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44727</v>
+        <v>44930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>13.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -638,21 +638,139 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
       </c>
       <c r="T2" t="n">
+        <v>18</v>
+      </c>
+      <c r="U2" t="n">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Brunlångöra
+Dropptaggsvamp
+Gulsparv
+Motaggsvamp
+Nordfladdermus
+Spillkråka
+Dvärgpipistrell
+Kungsfågel
+Större brunfladdermus
+Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 24599-2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44727</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
         <v>11</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U3" t="n">
         <v>3</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -666,107 +784,107 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>A 25306-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D4" s="1" t="n">
         <v>46176</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E4" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I4" t="n">
         <v>3.2</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>4</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" t="n">
         <v>2</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>10</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T4" t="n">
         <v>14</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>14</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Slåtterfibbla
@@ -780,154 +898,36 @@
 Gröngöling</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 695-2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44930</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>18</v>
-      </c>
-      <c r="U4" t="n">
-        <v>18</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Brunlångöra
-Dropptaggsvamp
-Gulsparv
-Motaggsvamp
-Nordfladdermus
-Spillkråka
-Dvärgpipistrell
-Kungsfågel
-Större brunfladdermus
-Vattenfladdermus</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
         <v/>
       </c>
     </row>
@@ -951,7 +951,7 @@
         <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24799-2026</t>
+          <t>A 18100-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46171</v>
+        <v>44684</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2579,373 +2579,373 @@
         <v>2</v>
       </c>
       <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Svart trolldruva
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 24799-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
+      <c r="T20" t="n">
         <v>2</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Mindre märgborre
 Spillkråka</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24799-2026 artfynd.xlsx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24799-2026 karta.png", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24799-2026 georefererad karta.tif", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24799-2026 FSC-klagomål.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24799-2026 FSC-klagomål mail.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24799-2026 tillsynsbegäran.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24799-2026 tillsynsbegäran mail.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 24799-2026 prioriterade fågelarter.docx", "A 24799-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 25319-2026</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>46176</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="E21" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>1.6</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>3</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Grovticka
 Spillkråka</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 25315-2026</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>46176</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="E22" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>1.4</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>3</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>3</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tofsmes</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 18100-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44684</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Svart trolldruva
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
         <v/>
       </c>
     </row>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15690-2023</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45020</v>
+        <v>45481</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3091,16 +3091,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3131,42 +3131,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14214-2025</t>
+          <t>A 61514-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45740</v>
+        <v>44916</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3208,7 +3208,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3220,55 +3220,51 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
     </row>
@@ -3292,7 +3288,7 @@
         <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3406,7 +3402,7 @@
         <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3520,7 +3516,7 @@
         <v>46092</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3613,7 +3609,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 14214-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3627,10 +3623,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44586</v>
+        <v>45740</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3643,20 +3639,20 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>17.1</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3667,58 +3663,62 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 1691-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45481</v>
+        <v>44938</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3784,7 +3784,7 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
@@ -3792,38 +3792,38 @@
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1691-2023</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44938</v>
+        <v>44586</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>17.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3889,46 +3889,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61514-2022</t>
+          <t>A 15690-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44916</v>
+        <v>45020</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3958,17 +3958,17 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3998,35 +3998,35 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 48656-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45740</v>
+        <v>44859</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4442,8 +4442,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4486,7 +4491,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4500,10 +4505,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45062</v>
+        <v>45406</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4516,7 +4521,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4559,7 +4564,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30925-2023</t>
+          <t>A 46405-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4573,10 +4578,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45113</v>
+        <v>44846</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4588,13 +4593,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4637,7 +4637,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 11876-2024</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45376</v>
+        <v>44812</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4710,7 +4710,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 14217-2025</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45740</v>
+        <v>44550</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4783,7 +4783,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 73194-2021</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44550</v>
+        <v>45020</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4856,7 +4856,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 16483-2023</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45029</v>
+        <v>45740</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4946,7 +4946,7 @@
         <v>45965</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46405-2022</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44846</v>
+        <v>45062</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20649-2022</t>
+          <t>A 12306-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5089,10 +5089,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44700</v>
+        <v>46087</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5153,7 +5153,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 8528-2024</t>
+          <t>A 12294-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5163,14 +5163,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45355</v>
+        <v>46087</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5182,8 +5182,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5226,7 +5231,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45869-2022</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5240,10 +5245,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44844</v>
+        <v>45678</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5255,8 +5260,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5299,7 +5309,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 3686-2022</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5313,10 +5323,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44586</v>
+        <v>45376</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5329,7 +5339,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5372,7 +5382,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12306-2026</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5386,10 +5396,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46087</v>
+        <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5401,13 +5411,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5450,7 +5455,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 12294-2026</t>
+          <t>A 73194-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5464,10 +5469,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46087</v>
+        <v>44550</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5479,13 +5484,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5528,7 +5528,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45020</v>
+        <v>46154</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5601,7 +5601,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44550</v>
+        <v>46164</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5674,7 +5674,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9032-2023</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44979</v>
+        <v>46164</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5747,7 +5747,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 23716-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44550</v>
+        <v>46164</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5820,7 +5820,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 48656-2022</t>
+          <t>A 20649-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44859</v>
+        <v>44700</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5898,7 +5898,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5908,14 +5908,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44812</v>
+        <v>44599</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5971,7 +5971,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 8528-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5981,14 +5981,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46154</v>
+        <v>45355</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6044,7 +6044,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 27717-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6058,10 +6058,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45376</v>
+        <v>46190</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6073,8 +6073,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6117,7 +6122,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 3686-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6131,10 +6136,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46164</v>
+        <v>44586</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6147,7 +6152,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6190,7 +6195,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 23716-2026</t>
+          <t>A 9032-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6204,10 +6209,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46164</v>
+        <v>44979</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6220,7 +6225,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6263,7 +6268,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 25217-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6273,14 +6278,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46164</v>
+        <v>45462</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6292,8 +6297,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6336,7 +6346,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 25217-2024</t>
+          <t>A 35108-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6346,14 +6356,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45462</v>
+        <v>46258</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6365,13 +6375,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6414,7 +6419,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27717-2026</t>
+          <t>A 16483-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6428,10 +6433,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46190</v>
+        <v>45029</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6443,13 +6448,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>45495</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 30925-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45406</v>
+        <v>45113</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6594,8 +6594,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6638,7 +6643,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 35108-2026</t>
+          <t>A 45869-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6652,10 +6657,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46258</v>
+        <v>44844</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6668,7 +6673,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6711,7 +6716,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 14217-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6725,10 +6730,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45678</v>
+        <v>45740</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6740,13 +6745,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6789,7 +6789,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 11876-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6799,14 +6799,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44599</v>
+        <v>45376</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6879,7 +6879,7 @@
         <v>45406</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>46065</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 695-2023</t>
+          <t>A 24599-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44930</v>
+        <v>44727</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>13.6</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -638,21 +638,135 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
       </c>
       <c r="T2" t="n">
+        <v>11</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Almsnabbvinge
+Mindre tåtelsmygare
+Igelkottsröksvamp
+Mandelriska
+Sotriska
+Mattlummer
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 695-2023</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44930</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
         <v>18</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U3" t="n">
         <v>18</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Brunlångöra
 Dropptaggsvamp
@@ -666,150 +780,36 @@
 Vattenfladdermus</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 24599-2022</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>44727</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="n">
-        <v>11</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Almsnabbvinge
-Mindre tåtelsmygare
-Igelkottsröksvamp
-Mandelriska
-Sotriska
-Mattlummer
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
         <v/>
       </c>
     </row>
@@ -833,7 +833,7 @@
         <v>46176</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1697-2023</t>
+          <t>A 23829-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44938</v>
+        <v>45078</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2003,18 +2003,23 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -2028,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2040,160 +2045,155 @@
         <v>3</v>
       </c>
       <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.
+Tallticka
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 23829-2023 artfynd.xlsx", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 23829-2023 karta.png", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 23829-2023 georefererad karta.tif", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 23829-2023 FSC-klagomål.docx", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 23829-2023 FSC-klagomål mail.docx", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 23829-2023 tillsynsbegäran.docx", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 23829-2023 tillsynsbegäran mail.docx", "A 23829-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 1697-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44938</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Lunglav
 Bårdlav
 Grön sköldmossa</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1697-2023 artfynd.xlsx", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1697-2023 karta.png", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1697-2023 georefererad karta.tif", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1697-2023 FSC-klagomål.docx", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1697-2023 FSC-klagomål mail.docx", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1697-2023 tillsynsbegäran.docx", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1697-2023 tillsynsbegäran mail.docx", "A 1697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 23829-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45078</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.
-Tallticka
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 23829-2023 artfynd.xlsx", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 23829-2023 karta.png", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 23829-2023 georefererad karta.tif", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 23829-2023 FSC-klagomål.docx", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 23829-2023 FSC-klagomål mail.docx", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 23829-2023 tillsynsbegäran.docx", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 23829-2023 tillsynsbegäran mail.docx", "A 23829-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 30378-2024</t>
+          <t>A 18100-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2203,14 +2203,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45491</v>
+        <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2223,16 +2223,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2256,366 +2256,366 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Svart trolldruva
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 30378-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45491</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Mindre tåtelsmygare
 Svinrot</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 30378-2024 artfynd.xlsx", "A 30378-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 30378-2024 karta.png", "A 30378-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 30378-2024 georefererad karta.tif", "A 30378-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 30378-2024 FSC-klagomål.docx", "A 30378-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 30378-2024 FSC-klagomål mail.docx", "A 30378-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 30378-2024 tillsynsbegäran.docx", "A 30378-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 30378-2024 tillsynsbegäran mail.docx", "A 30378-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 15905-2022</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>44664</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>11.2</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>2</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>3</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15905-2022 artfynd.xlsx", "A 15905-2022")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15905-2022 karta.png", "A 15905-2022")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15905-2022 georefererad karta.tif", "A 15905-2022")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15905-2022 FSC-klagomål.docx", "A 15905-2022")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15905-2022 FSC-klagomål mail.docx", "A 15905-2022")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15905-2022 tillsynsbegäran.docx", "A 15905-2022")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15905-2022 tillsynsbegäran mail.docx", "A 15905-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 60406-2025</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>45995</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="E19" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I19" t="n">
         <v>2.3</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>2</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>2</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 60406-2025 artfynd.xlsx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 60406-2025 karta.png", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 60406-2025 georefererad karta.tif", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 60406-2025 FSC-klagomål.docx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 60406-2025 FSC-klagomål mail.docx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 60406-2025 tillsynsbegäran.docx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 60406-2025 tillsynsbegäran mail.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 18100-2022</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44684</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Svart trolldruva
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
         <v/>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
         <v>46171</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>46176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>46176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45481</v>
+        <v>44586</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>17.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3131,42 +3131,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 61514-2022</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44916</v>
+        <v>45481</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3236,42 +3236,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12305-2026</t>
+          <t>A 15690-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3285,10 +3285,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46087</v>
+        <v>45020</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3300,23 +3300,18 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
@@ -3330,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3346,46 +3341,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12590-2026</t>
+          <t>A 14214-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3399,10 +3390,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46090</v>
+        <v>45740</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3414,13 +3405,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3429,10 +3415,10 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3447,59 +3433,59 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12842-2026</t>
+          <t>A 1691-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3513,10 +3499,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46092</v>
+        <v>44938</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3526,11 +3512,6 @@
       <c r="G28" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -3540,10 +3521,10 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3558,7 +3539,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3574,42 +3555,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 14214-2025</t>
+          <t>A 61514-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3623,10 +3604,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45740</v>
+        <v>44916</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3639,7 +3620,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3651,7 +3632,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3663,62 +3644,58 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1691-2023</t>
+          <t>A 12305-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3732,10 +3709,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44938</v>
+        <v>46087</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3747,14 +3724,19 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3784,46 +3766,50 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 12590-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3837,10 +3823,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44586</v>
+        <v>46090</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3852,18 +3838,23 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>17.1</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
@@ -3877,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3889,46 +3880,50 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 15690-2023</t>
+          <t>A 12842-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3942,10 +3937,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45020</v>
+        <v>46092</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3957,8 +3952,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3994,39 +3994,39 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48656-2022</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44859</v>
+        <v>45740</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4442,13 +4442,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4491,7 +4486,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 48656-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4505,10 +4500,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45406</v>
+        <v>44859</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4520,8 +4515,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4564,7 +4564,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 46405-2022</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44846</v>
+        <v>44812</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4637,7 +4637,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44812</v>
+        <v>45062</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4710,7 +4710,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44550</v>
+        <v>45678</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4739,8 +4739,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4783,7 +4788,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4797,10 +4802,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45020</v>
+        <v>45376</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4813,7 +4818,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4856,7 +4861,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 30925-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4870,10 +4875,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45740</v>
+        <v>45113</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4885,8 +4890,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4929,7 +4939,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54468-2025</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4939,14 +4949,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45965</v>
+        <v>44599</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4959,7 +4969,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5002,7 +5012,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 46405-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5016,10 +5026,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45062</v>
+        <v>44846</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5032,7 +5042,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5075,7 +5085,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 12306-2026</t>
+          <t>A 20649-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5089,10 +5099,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46087</v>
+        <v>44700</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5110,7 +5120,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5153,7 +5163,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 12294-2026</t>
+          <t>A 8528-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5163,14 +5173,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46087</v>
+        <v>45355</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5182,13 +5192,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5231,7 +5236,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 25217-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5241,14 +5246,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45678</v>
+        <v>45462</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5266,7 +5271,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5309,7 +5314,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 45869-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5323,10 +5328,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45376</v>
+        <v>44844</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5339,7 +5344,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5382,7 +5387,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 3686-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5396,10 +5401,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44550</v>
+        <v>44586</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5412,7 +5417,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5455,7 +5460,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 73194-2021</t>
+          <t>A 16142-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5469,10 +5474,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44550</v>
+        <v>45406</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5485,7 +5490,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5528,7 +5533,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 11876-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5542,10 +5547,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46154</v>
+        <v>45376</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5558,7 +5563,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5601,7 +5606,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5615,10 +5620,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46164</v>
+        <v>45020</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5631,7 +5636,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5674,7 +5679,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 14217-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5688,10 +5693,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46164</v>
+        <v>45740</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5704,7 +5709,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5747,7 +5752,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23716-2026</t>
+          <t>A 30622-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5757,14 +5762,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46164</v>
+        <v>45495</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5777,7 +5782,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5820,7 +5825,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 20649-2022</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5834,10 +5839,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44700</v>
+        <v>44550</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5849,13 +5854,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5898,7 +5898,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 73194-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5908,14 +5908,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44599</v>
+        <v>44550</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8528-2024</t>
+          <t>A 9032-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5981,14 +5981,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45355</v>
+        <v>44979</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6044,7 +6044,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 27717-2026</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6058,10 +6058,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46190</v>
+        <v>45406</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6073,13 +6073,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6122,7 +6117,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3686-2022</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6136,10 +6131,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44586</v>
+        <v>44550</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6152,7 +6147,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6195,7 +6190,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9032-2023</t>
+          <t>A 16483-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6209,10 +6204,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44979</v>
+        <v>45029</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6225,7 +6220,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6268,7 +6263,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25217-2024</t>
+          <t>A 54468-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6278,14 +6273,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45462</v>
+        <v>45965</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6297,13 +6292,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6346,7 +6336,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 35108-2026</t>
+          <t>A 12306-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6360,10 +6350,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46258</v>
+        <v>46087</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6375,8 +6365,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6419,7 +6414,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16483-2023</t>
+          <t>A 12294-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6433,10 +6428,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45029</v>
+        <v>46087</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6448,8 +6443,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6492,7 +6492,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30622-2024</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6502,14 +6502,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45495</v>
+        <v>46154</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6565,7 +6565,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30925-2023</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45113</v>
+        <v>46164</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6594,13 +6594,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6643,7 +6638,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 45869-2022</t>
+          <t>A 23716-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6657,10 +6652,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44844</v>
+        <v>46164</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6673,7 +6668,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6716,7 +6711,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 14217-2025</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6730,10 +6725,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45740</v>
+        <v>46164</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6746,7 +6741,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6789,7 +6784,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11876-2024</t>
+          <t>A 27717-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6803,10 +6798,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45376</v>
+        <v>46190</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6818,8 +6813,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6862,7 +6862,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 16142-2024</t>
+          <t>A 35108-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6876,10 +6876,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45406</v>
+        <v>46258</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>46065</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 24599-2022</t>
+          <t>A 695-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44727</v>
+        <v>44930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>13.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -638,21 +638,257 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
       </c>
       <c r="T2" t="n">
+        <v>18</v>
+      </c>
+      <c r="U2" t="n">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Brunlångöra
+Dropptaggsvamp
+Gulsparv
+Motaggsvamp
+Nordfladdermus
+Spillkråka
+Dvärgpipistrell
+Kungsfågel
+Större brunfladdermus
+Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 25306-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
+        <v>14</v>
+      </c>
+      <c r="U3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Slåtterfibbla
+Tallticka
+Blåmossa
+Mindre märgborre
+Kransmossa
+Liljekonvalj
+Spillkråka
+Tofsmes
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 24599-2022</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>44727</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="n">
         <v>11</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U4" t="n">
         <v>3</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -666,268 +902,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 695-2023</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>44930</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="J3" t="n">
-        <v>8</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="n">
-        <v>18</v>
-      </c>
-      <c r="U3" t="n">
-        <v>18</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Brunlångöra
-Dropptaggsvamp
-Gulsparv
-Motaggsvamp
-Nordfladdermus
-Spillkråka
-Dvärgpipistrell
-Kungsfågel
-Större brunfladdermus
-Vattenfladdermus</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 25306-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>14</v>
-      </c>
-      <c r="U4" t="n">
-        <v>14</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Slåtterfibbla
-Tallticka
-Blåmossa
-Mindre märgborre
-Kransmossa
-Liljekonvalj
-Spillkråka
-Tofsmes
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
         <v/>
       </c>
     </row>
@@ -951,7 +951,7 @@
         <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 23829-2023</t>
+          <t>A 1697-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45078</v>
+        <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2003,22 +2003,17 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2045,155 +2040,160 @@
         <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Lunglav
+Bårdlav
+Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1697-2023 artfynd.xlsx", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1697-2023 karta.png", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1697-2023 georefererad karta.tif", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1697-2023 FSC-klagomål.docx", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1697-2023 FSC-klagomål mail.docx", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1697-2023 tillsynsbegäran.docx", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1697-2023 tillsynsbegäran mail.docx", "A 1697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 23829-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Fjällig taggsvamp s.str.
 Tallticka
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 23829-2023 artfynd.xlsx", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 23829-2023 karta.png", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 23829-2023 georefererad karta.tif", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 23829-2023 FSC-klagomål.docx", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 23829-2023 FSC-klagomål mail.docx", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 23829-2023 tillsynsbegäran.docx", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 23829-2023 tillsynsbegäran mail.docx", "A 23829-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 1697-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44938</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lunglav
-Bårdlav
-Grön sköldmossa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1697-2023 artfynd.xlsx", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1697-2023 karta.png", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1697-2023 georefererad karta.tif", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1697-2023 FSC-klagomål.docx", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1697-2023 FSC-klagomål mail.docx", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1697-2023 tillsynsbegäran.docx", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1697-2023 tillsynsbegäran mail.docx", "A 1697-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18100-2022</t>
+          <t>A 30378-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2203,14 +2203,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44684</v>
+        <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2223,16 +2223,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2256,696 +2256,696 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 30378-2024 artfynd.xlsx", "A 30378-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 30378-2024 karta.png", "A 30378-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 30378-2024 georefererad karta.tif", "A 30378-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 30378-2024 FSC-klagomål.docx", "A 30378-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 30378-2024 FSC-klagomål mail.docx", "A 30378-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 30378-2024 tillsynsbegäran.docx", "A 30378-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 30378-2024 tillsynsbegäran mail.docx", "A 30378-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 15905-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44664</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>3</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15905-2022 artfynd.xlsx", "A 15905-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15905-2022 karta.png", "A 15905-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15905-2022 georefererad karta.tif", "A 15905-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15905-2022 FSC-klagomål.docx", "A 15905-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15905-2022 FSC-klagomål mail.docx", "A 15905-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15905-2022 tillsynsbegäran.docx", "A 15905-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15905-2022 tillsynsbegäran mail.docx", "A 15905-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 60406-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 60406-2025 artfynd.xlsx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 60406-2025 karta.png", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 60406-2025 georefererad karta.tif", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 60406-2025 FSC-klagomål.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 60406-2025 FSC-klagomål mail.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 60406-2025 tillsynsbegäran.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 60406-2025 tillsynsbegäran mail.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 24799-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Mindre märgborre
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24799-2026 artfynd.xlsx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24799-2026 karta.png", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24799-2026 georefererad karta.tif", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24799-2026 FSC-klagomål.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24799-2026 FSC-klagomål mail.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24799-2026 tillsynsbegäran.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24799-2026 tillsynsbegäran mail.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 24799-2026 prioriterade fågelarter.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 25319-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Grovticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 25315-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 18100-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44684</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Svart trolldruva
 Gullviva</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 30378-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45491</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Mindre tåtelsmygare
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 30378-2024 artfynd.xlsx", "A 30378-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 30378-2024 karta.png", "A 30378-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 30378-2024 georefererad karta.tif", "A 30378-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 30378-2024 FSC-klagomål.docx", "A 30378-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 30378-2024 FSC-klagomål mail.docx", "A 30378-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 30378-2024 tillsynsbegäran.docx", "A 30378-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 30378-2024 tillsynsbegäran mail.docx", "A 30378-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 15905-2022</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44664</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15905-2022 artfynd.xlsx", "A 15905-2022")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15905-2022 karta.png", "A 15905-2022")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15905-2022 georefererad karta.tif", "A 15905-2022")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15905-2022 FSC-klagomål.docx", "A 15905-2022")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15905-2022 FSC-klagomål mail.docx", "A 15905-2022")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15905-2022 tillsynsbegäran.docx", "A 15905-2022")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15905-2022 tillsynsbegäran mail.docx", "A 15905-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 60406-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45995</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 60406-2025 artfynd.xlsx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 60406-2025 karta.png", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 60406-2025 georefererad karta.tif", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 60406-2025 FSC-klagomål.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 60406-2025 FSC-klagomål mail.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 60406-2025 tillsynsbegäran.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 60406-2025 tillsynsbegäran mail.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 24799-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Mindre märgborre
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24799-2026 artfynd.xlsx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24799-2026 karta.png", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24799-2026 georefererad karta.tif", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24799-2026 FSC-klagomål.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24799-2026 FSC-klagomål mail.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24799-2026 tillsynsbegäran.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24799-2026 tillsynsbegäran mail.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 24799-2026 prioriterade fågelarter.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 25319-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Grovticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 25315-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
         <v/>
       </c>
     </row>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44586</v>
+        <v>45481</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>17.1</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3131,42 +3131,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 12305-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45481</v>
+        <v>46087</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3195,14 +3195,19 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3236,42 +3241,46 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 15690-2023</t>
+          <t>A 12590-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3285,10 +3294,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45020</v>
+        <v>46090</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3300,11 +3309,16 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3337,46 +3351,50 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 14214-2025</t>
+          <t>A 12842-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3390,10 +3408,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45740</v>
+        <v>46092</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3405,20 +3423,25 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3433,59 +3456,55 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 1691-2023</t>
+          <t>A 61514-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3499,10 +3518,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44938</v>
+        <v>44916</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3515,13 +3534,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3551,46 +3570,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 61514-2022</t>
+          <t>A 14214-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3604,10 +3623,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44916</v>
+        <v>45740</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3620,7 +3639,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3632,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3644,58 +3663,62 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12305-2026</t>
+          <t>A 1691-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3709,10 +3732,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46087</v>
+        <v>44938</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3724,19 +3747,14 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3766,50 +3784,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12590-2026</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3823,10 +3837,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46090</v>
+        <v>44586</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3838,22 +3852,17 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>17.1</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3868,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3880,50 +3889,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12842-2026</t>
+          <t>A 15690-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3937,10 +3942,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46092</v>
+        <v>45020</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3952,13 +3957,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3994,39 +3994,39 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45740</v>
+        <v>45406</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
         <v>44859</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 46405-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44812</v>
+        <v>44846</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4637,7 +4637,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45062</v>
+        <v>44812</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4710,7 +4710,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45678</v>
+        <v>44550</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4739,13 +4739,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4788,7 +4783,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 12306-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4802,10 +4797,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45376</v>
+        <v>46087</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4817,8 +4812,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4861,7 +4861,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30925-2023</t>
+          <t>A 12294-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45113</v>
+        <v>46087</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4939,7 +4939,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4949,14 +4949,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44599</v>
+        <v>45020</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46405-2022</t>
+          <t>A 54468-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44846</v>
+        <v>45965</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5085,7 +5085,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20649-2022</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44700</v>
+        <v>45740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5114,13 +5114,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5163,7 +5158,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 8528-2024</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5173,14 +5168,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45355</v>
+        <v>45062</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5193,7 +5188,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5236,7 +5231,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 25217-2024</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5246,14 +5241,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45462</v>
+        <v>45678</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5271,7 +5266,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5314,7 +5309,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 45869-2022</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5328,10 +5323,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44844</v>
+        <v>45376</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5344,7 +5339,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5387,7 +5382,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3686-2022</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5401,10 +5396,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44586</v>
+        <v>46154</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5417,7 +5412,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5460,7 +5455,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 16142-2024</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5474,10 +5469,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45406</v>
+        <v>44550</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5490,7 +5485,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5533,7 +5528,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11876-2024</t>
+          <t>A 73194-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5547,10 +5542,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45376</v>
+        <v>44550</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5563,7 +5558,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5606,7 +5601,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5620,10 +5615,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45020</v>
+        <v>46164</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5636,7 +5631,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5679,7 +5674,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 14217-2025</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5693,10 +5688,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45740</v>
+        <v>46164</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5709,7 +5704,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5752,7 +5747,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30622-2024</t>
+          <t>A 23716-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5762,14 +5757,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45495</v>
+        <v>46164</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5782,7 +5777,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5825,7 +5820,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 27717-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5839,10 +5834,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44550</v>
+        <v>46190</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5854,8 +5849,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5898,7 +5898,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 73194-2021</t>
+          <t>A 20649-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5912,10 +5912,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44550</v>
+        <v>44700</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5927,8 +5927,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5971,7 +5976,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9032-2023</t>
+          <t>A 35108-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5985,10 +5990,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44979</v>
+        <v>46258</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6001,7 +6006,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6044,7 +6049,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6054,14 +6059,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45406</v>
+        <v>44599</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6074,7 +6079,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6117,7 +6122,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 8528-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6127,14 +6132,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44550</v>
+        <v>45355</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6147,7 +6152,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6190,7 +6195,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16483-2023</t>
+          <t>A 3686-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6204,10 +6209,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45029</v>
+        <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6220,7 +6225,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6263,7 +6268,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 54468-2025</t>
+          <t>A 9032-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6277,10 +6282,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45965</v>
+        <v>44979</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6293,7 +6298,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6336,7 +6341,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12306-2026</t>
+          <t>A 25217-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6346,14 +6351,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46087</v>
+        <v>45462</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6371,7 +6376,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6414,7 +6419,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12294-2026</t>
+          <t>A 16483-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6428,10 +6433,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46087</v>
+        <v>45029</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6443,13 +6448,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6492,7 +6492,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 30622-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6502,14 +6502,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46154</v>
+        <v>45495</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6565,7 +6565,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 30925-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46164</v>
+        <v>45113</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6594,8 +6594,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6638,7 +6643,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 23716-2026</t>
+          <t>A 45869-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6652,10 +6657,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46164</v>
+        <v>44844</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6668,7 +6673,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6711,7 +6716,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 14217-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6725,10 +6730,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46164</v>
+        <v>45740</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6741,7 +6746,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6784,7 +6789,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 27717-2026</t>
+          <t>A 11876-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6798,10 +6803,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46190</v>
+        <v>45376</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6813,13 +6818,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6862,7 +6862,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35108-2026</t>
+          <t>A 16142-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6876,10 +6876,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46258</v>
+        <v>45406</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>46065</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 695-2023</t>
+          <t>A 24599-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44930</v>
+        <v>44727</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>13.6</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -638,21 +638,253 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
       </c>
       <c r="T2" t="n">
+        <v>11</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Almsnabbvinge
+Mindre tåtelsmygare
+Igelkottsröksvamp
+Mandelriska
+Sotriska
+Mattlummer
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 25306-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
+        <v>14</v>
+      </c>
+      <c r="U3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Slåtterfibbla
+Tallticka
+Blåmossa
+Mindre märgborre
+Kransmossa
+Liljekonvalj
+Spillkråka
+Tofsmes
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 695-2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>44930</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="n">
         <v>18</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U4" t="n">
         <v>18</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Brunlångöra
 Dropptaggsvamp
@@ -666,268 +898,36 @@
 Vattenfladdermus</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 25306-2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="n">
-        <v>14</v>
-      </c>
-      <c r="U3" t="n">
-        <v>14</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Slåtterfibbla
-Tallticka
-Blåmossa
-Mindre märgborre
-Kransmossa
-Liljekonvalj
-Spillkråka
-Tofsmes
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 24599-2022</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44727</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>11</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Almsnabbvinge
-Mindre tåtelsmygare
-Igelkottsröksvamp
-Mandelriska
-Sotriska
-Mattlummer
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
         <v/>
       </c>
     </row>
@@ -951,7 +951,7 @@
         <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>46171</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>46176</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>46176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>44684</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 15690-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45481</v>
+        <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3091,17 +3091,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3131,42 +3131,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12305-2026</t>
+          <t>A 14214-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46087</v>
+        <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3195,13 +3195,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3213,7 +3208,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3225,62 +3220,62 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12590-2026</t>
+          <t>A 12305-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3294,10 +3289,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46090</v>
+        <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3315,7 +3310,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3324,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3339,7 +3334,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3351,50 +3346,50 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12842-2026</t>
+          <t>A 12590-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3408,10 +3403,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46092</v>
+        <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3429,10 +3424,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3469,42 +3464,46 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 61514-2022</t>
+          <t>A 12842-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3518,10 +3517,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44916</v>
+        <v>46092</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3533,18 +3532,23 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3558,7 +3562,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3570,46 +3574,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 14214-2025</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3623,10 +3627,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45740</v>
+        <v>44586</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3639,19 +3643,19 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>17.1</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3663,62 +3667,58 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1691-2023</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44938</v>
+        <v>45481</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3784,7 +3784,7 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
@@ -3792,38 +3792,38 @@
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 1691-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44586</v>
+        <v>44938</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>17.1</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3889,46 +3889,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 15690-2023</t>
+          <t>A 61514-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45020</v>
+        <v>44916</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3958,16 +3958,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3982,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3998,35 +3998,35 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45406</v>
+        <v>45740</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4486,7 +4486,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 48656-2022</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44859</v>
+        <v>45062</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4515,13 +4515,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4564,7 +4559,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 46405-2022</t>
+          <t>A 30925-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4578,10 +4573,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44846</v>
+        <v>45113</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4593,8 +4588,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4637,7 +4637,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 11876-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44812</v>
+        <v>45376</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4710,7 +4710,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 14217-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44550</v>
+        <v>45740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4783,7 +4783,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12306-2026</t>
+          <t>A 73194-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46087</v>
+        <v>44550</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4810,11 +4810,6 @@
       <c r="G43" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -4861,7 +4856,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12294-2026</t>
+          <t>A 16483-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4875,10 +4870,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46087</v>
+        <v>45029</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4890,13 +4885,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4939,7 +4929,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 12306-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4953,10 +4943,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45020</v>
+        <v>46087</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4968,8 +4958,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5012,7 +5007,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 54468-2025</t>
+          <t>A 12294-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5026,10 +5021,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45965</v>
+        <v>46087</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5041,8 +5036,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5085,7 +5085,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 54468-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45740</v>
+        <v>45965</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5158,7 +5158,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 46405-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45062</v>
+        <v>44846</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5231,7 +5231,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 20649-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45678</v>
+        <v>44700</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5309,7 +5309,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 8528-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5319,14 +5319,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45376</v>
+        <v>45355</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 45869-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46154</v>
+        <v>44844</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5455,7 +5455,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 3686-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44550</v>
+        <v>44586</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5528,7 +5528,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 73194-2021</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44550</v>
+        <v>45020</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5601,7 +5601,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46164</v>
+        <v>44550</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5674,7 +5674,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 9032-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46164</v>
+        <v>44979</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5747,7 +5747,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23716-2026</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5820,7 +5820,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 27717-2026</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46190</v>
+        <v>44550</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5849,13 +5849,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5898,7 +5893,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 20649-2022</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5912,10 +5907,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44700</v>
+        <v>46164</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5927,13 +5922,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>6</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5976,7 +5966,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35108-2026</t>
+          <t>A 23716-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5990,10 +5980,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46258</v>
+        <v>46164</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6006,7 +5996,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.4</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6049,7 +6039,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6059,14 +6049,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44599</v>
+        <v>46164</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6079,7 +6069,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6122,7 +6112,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8528-2024</t>
+          <t>A 27717-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6132,14 +6122,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45355</v>
+        <v>46190</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6151,8 +6141,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6195,7 +6190,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3686-2022</t>
+          <t>A 48656-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6209,10 +6204,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44586</v>
+        <v>44859</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6224,8 +6219,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6268,7 +6268,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9032-2023</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44979</v>
+        <v>44812</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6341,7 +6341,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 25217-2024</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6351,14 +6351,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45462</v>
+        <v>45376</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6370,13 +6370,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6419,7 +6414,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16483-2023</t>
+          <t>A 35108-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6433,10 +6428,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45029</v>
+        <v>46258</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6449,7 +6444,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6492,7 +6487,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30622-2024</t>
+          <t>A 25217-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6506,10 +6501,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45495</v>
+        <v>45462</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6521,8 +6516,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6565,7 +6565,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30925-2023</t>
+          <t>A 30622-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6575,14 +6575,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45113</v>
+        <v>45495</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6594,13 +6594,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6643,7 +6638,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 45869-2022</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6657,10 +6652,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44844</v>
+        <v>45406</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6673,7 +6668,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6716,7 +6711,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 14217-2025</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6730,10 +6725,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45740</v>
+        <v>45678</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6745,8 +6740,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6789,7 +6789,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11876-2024</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6799,14 +6799,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45376</v>
+        <v>44599</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6879,7 +6879,7 @@
         <v>45406</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>46065</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -601,7 +601,7 @@
         <v>44727</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46176</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>44930</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>46171</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>46176</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>46176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>44684</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>46092</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>44586</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>45481</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>44938</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>44916</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>45740</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>45062</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>45113</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>45376</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>45740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44550</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>45029</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>46087</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>46087</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>45965</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>44846</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>44700</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>45355</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>44844</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>44586</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>45020</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>44550</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>44979</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>46154</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>44550</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>46164</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>46164</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>46164</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>46190</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>44859</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>44812</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>45376</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>46258</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>45462</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>45495</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>45406</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>45678</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>44599</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45406</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>46065</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -601,7 +601,7 @@
         <v>44727</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46176</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>44930</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>46171</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>46176</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>46176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>44684</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>46092</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>44586</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>45481</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>44938</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>44916</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>45740</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>45062</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>45113</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>45376</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>45740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44550</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>45029</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>46087</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>46087</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>45965</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>44846</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>44700</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>45355</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>44844</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>44586</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>45020</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>44550</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>44979</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>46154</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>44550</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>46164</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>46164</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>46164</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>46190</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>44859</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>44812</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>45376</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>46258</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>45462</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>45495</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>45406</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>45678</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>44599</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45406</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>46065</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 24599-2022</t>
+          <t>A 695-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44727</v>
+        <v>44930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>13.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -638,21 +638,139 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
       </c>
       <c r="T2" t="n">
+        <v>18</v>
+      </c>
+      <c r="U2" t="n">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Brunlångöra
+Dropptaggsvamp
+Gulsparv
+Motaggsvamp
+Nordfladdermus
+Spillkråka
+Dvärgpipistrell
+Kungsfågel
+Större brunfladdermus
+Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 24599-2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44727</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
         <v>11</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U3" t="n">
         <v>3</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -666,107 +784,107 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>A 25306-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D4" s="1" t="n">
         <v>46176</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E4" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I4" t="n">
         <v>3.2</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>4</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" t="n">
         <v>2</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>10</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T4" t="n">
         <v>14</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>14</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Slåtterfibbla
@@ -780,154 +898,36 @@
 Gröngöling</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 695-2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44930</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>18</v>
-      </c>
-      <c r="U4" t="n">
-        <v>18</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Brunlångöra
-Dropptaggsvamp
-Gulsparv
-Motaggsvamp
-Nordfladdermus
-Spillkråka
-Dvärgpipistrell
-Kungsfågel
-Större brunfladdermus
-Vattenfladdermus</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
         <v/>
       </c>
     </row>
@@ -951,7 +951,7 @@
         <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>46171</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>46176</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>46176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>44684</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15690-2023</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45020</v>
+        <v>45481</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3091,16 +3091,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3131,42 +3131,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14214-2025</t>
+          <t>A 61514-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45740</v>
+        <v>44916</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3208,7 +3208,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3220,55 +3220,51 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
     </row>
@@ -3292,7 +3288,7 @@
         <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3406,7 +3402,7 @@
         <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3520,7 +3516,7 @@
         <v>46092</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3613,7 +3609,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 14214-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3627,10 +3623,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44586</v>
+        <v>45740</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3643,20 +3639,20 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>17.1</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3667,58 +3663,62 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 1691-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45481</v>
+        <v>44938</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3784,7 +3784,7 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
@@ -3792,38 +3792,38 @@
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1691-2023</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44938</v>
+        <v>44586</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>17.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3889,46 +3889,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61514-2022</t>
+          <t>A 15690-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44916</v>
+        <v>45020</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3958,17 +3958,17 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3998,35 +3998,35 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 48656-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45740</v>
+        <v>44859</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4442,8 +4442,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4486,7 +4491,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4500,10 +4505,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45062</v>
+        <v>45406</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4516,7 +4521,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4559,7 +4564,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30925-2023</t>
+          <t>A 46405-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4573,10 +4578,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45113</v>
+        <v>44846</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4588,13 +4593,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4637,7 +4637,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 11876-2024</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45376</v>
+        <v>44812</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4710,7 +4710,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 14217-2025</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45740</v>
+        <v>44550</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4783,7 +4783,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 73194-2021</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44550</v>
+        <v>45020</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4856,7 +4856,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 16483-2023</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45029</v>
+        <v>45740</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4929,7 +4929,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12306-2026</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46087</v>
+        <v>45062</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4958,13 +4958,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5007,7 +5002,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 12294-2026</t>
+          <t>A 12306-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5024,7 +5019,7 @@
         <v>46087</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5042,7 +5037,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5085,7 +5080,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 54468-2025</t>
+          <t>A 12294-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5099,10 +5094,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45965</v>
+        <v>46087</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5114,8 +5109,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5158,7 +5158,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 46405-2022</t>
+          <t>A 54468-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44846</v>
+        <v>45965</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5231,7 +5231,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 20649-2022</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44700</v>
+        <v>45678</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5309,7 +5309,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8528-2024</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5319,14 +5319,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45355</v>
+        <v>45376</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45869-2022</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44844</v>
+        <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5455,7 +5455,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3686-2022</t>
+          <t>A 73194-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44586</v>
+        <v>44550</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5528,7 +5528,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45020</v>
+        <v>46154</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5601,7 +5601,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44550</v>
+        <v>46164</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5674,7 +5674,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9032-2023</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44979</v>
+        <v>46164</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5747,7 +5747,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 23716-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5820,7 +5820,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 20649-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44550</v>
+        <v>44700</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5849,8 +5849,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5893,7 +5898,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 27717-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5907,10 +5912,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46164</v>
+        <v>46190</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5922,8 +5927,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5966,7 +5976,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 23716-2026</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5976,14 +5986,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46164</v>
+        <v>44599</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5996,7 +6006,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6039,7 +6049,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 8528-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6049,14 +6059,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46164</v>
+        <v>45355</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6069,7 +6079,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6112,7 +6122,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 27717-2026</t>
+          <t>A 3686-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6126,10 +6136,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46190</v>
+        <v>44586</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6141,13 +6151,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6190,7 +6195,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48656-2022</t>
+          <t>A 9032-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6204,10 +6209,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44859</v>
+        <v>44979</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6219,13 +6224,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6268,7 +6268,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 25217-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6278,14 +6278,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44812</v>
+        <v>45462</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6297,8 +6297,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6341,7 +6346,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 16483-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6355,10 +6360,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45376</v>
+        <v>45029</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6371,7 +6376,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6414,7 +6419,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 35108-2026</t>
+          <t>A 30622-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6424,14 +6429,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46258</v>
+        <v>45495</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6444,7 +6449,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.4</v>
+        <v>0.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6487,7 +6492,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 25217-2024</t>
+          <t>A 30925-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6497,14 +6502,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45462</v>
+        <v>45113</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6522,7 +6527,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6565,7 +6570,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30622-2024</t>
+          <t>A 45869-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6575,14 +6580,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45495</v>
+        <v>44844</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6595,7 +6600,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6638,7 +6643,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 14217-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6652,10 +6657,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45406</v>
+        <v>45740</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6668,7 +6673,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6711,7 +6716,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 11876-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6725,10 +6730,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45678</v>
+        <v>45376</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6740,13 +6745,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6789,7 +6789,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 16142-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6799,14 +6799,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44599</v>
+        <v>45406</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6862,7 +6862,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 16142-2024</t>
+          <t>A 35108-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6876,10 +6876,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45406</v>
+        <v>46258</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>46065</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 695-2023</t>
+          <t>A 25306-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44930</v>
+        <v>46176</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>13.6</v>
+        <v>3.2</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -647,12 +647,244 @@
         <v>10</v>
       </c>
       <c r="T2" t="n">
+        <v>14</v>
+      </c>
+      <c r="U2" t="n">
+        <v>14</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Slåtterfibbla
+Tallticka
+Blåmossa
+Mindre märgborre
+Kransmossa
+Liljekonvalj
+Spillkråka
+Tofsmes
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 24599-2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44727</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
+        <v>11</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Almsnabbvinge
+Mindre tåtelsmygare
+Igelkottsröksvamp
+Mandelriska
+Sotriska
+Mattlummer
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 695-2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>44930</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="n">
         <v>18</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U4" t="n">
         <v>18</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Brunlångöra
 Dropptaggsvamp
@@ -666,268 +898,36 @@
 Vattenfladdermus</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 24599-2022</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>44727</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="n">
-        <v>11</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Almsnabbvinge
-Mindre tåtelsmygare
-Igelkottsröksvamp
-Mandelriska
-Sotriska
-Mattlummer
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 25306-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>14</v>
-      </c>
-      <c r="U4" t="n">
-        <v>14</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Slåtterfibbla
-Tallticka
-Blåmossa
-Mindre märgborre
-Kransmossa
-Liljekonvalj
-Spillkråka
-Tofsmes
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
         <v/>
       </c>
     </row>
@@ -951,7 +951,7 @@
         <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>46171</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>46176</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>46176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>44684</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 15690-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45481</v>
+        <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3091,17 +3091,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3131,42 +3131,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 61514-2022</t>
+          <t>A 14214-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44916</v>
+        <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3208,7 +3208,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3220,51 +3220,55 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
         <v/>
       </c>
     </row>
@@ -3288,7 +3292,7 @@
         <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3402,7 +3406,7 @@
         <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3516,7 +3520,7 @@
         <v>46092</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3609,7 +3613,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 14214-2025</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3623,10 +3627,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45740</v>
+        <v>44586</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3639,19 +3643,19 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>17.1</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3663,62 +3667,58 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1691-2023</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44938</v>
+        <v>45481</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3784,7 +3784,7 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
@@ -3792,38 +3792,38 @@
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 1691-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44586</v>
+        <v>44938</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>17.1</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3889,46 +3889,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 15690-2023</t>
+          <t>A 61514-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45020</v>
+        <v>44916</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3958,16 +3958,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3982,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3998,35 +3998,35 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48656-2022</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44859</v>
+        <v>45740</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4442,13 +4442,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4491,7 +4486,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4505,10 +4500,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45406</v>
+        <v>45062</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4521,7 +4516,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4564,7 +4559,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 46405-2022</t>
+          <t>A 30925-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4578,10 +4573,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44846</v>
+        <v>45113</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4593,8 +4588,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4637,7 +4637,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 14217-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44812</v>
+        <v>45740</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4710,7 +4710,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 73194-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4727,7 +4727,7 @@
         <v>44550</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4783,7 +4783,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 16483-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45020</v>
+        <v>45029</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4856,7 +4856,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 12306-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45740</v>
+        <v>46087</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4885,8 +4885,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4929,7 +4934,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 12294-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4943,10 +4948,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45062</v>
+        <v>46087</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4958,8 +4963,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5002,7 +5012,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 12306-2026</t>
+          <t>A 54468-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5016,10 +5026,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46087</v>
+        <v>45965</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5031,13 +5041,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5080,7 +5085,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 12294-2026</t>
+          <t>A 46405-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5094,10 +5099,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46087</v>
+        <v>44846</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5109,13 +5114,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5158,7 +5158,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 54468-2025</t>
+          <t>A 20649-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45965</v>
+        <v>44700</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5187,8 +5187,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5231,7 +5236,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 8528-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5241,14 +5246,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45678</v>
+        <v>45355</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5260,13 +5265,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5309,7 +5309,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5323,10 +5323,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45376</v>
+        <v>46154</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44550</v>
+        <v>46164</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5455,7 +5455,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 73194-2021</t>
+          <t>A 23716-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44550</v>
+        <v>46164</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5528,7 +5528,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5601,7 +5601,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 45869-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46164</v>
+        <v>44844</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5674,7 +5674,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 3686-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46164</v>
+        <v>44586</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5747,7 +5747,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23716-2026</t>
+          <t>A 27717-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46164</v>
+        <v>46190</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5776,8 +5776,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5820,7 +5825,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 20649-2022</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5834,10 +5839,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44700</v>
+        <v>45020</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5849,13 +5854,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5898,7 +5898,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 27717-2026</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5912,10 +5912,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46190</v>
+        <v>44550</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5927,13 +5927,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5976,7 +5971,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 9032-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5986,14 +5981,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44599</v>
+        <v>44979</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6006,7 +6001,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6049,7 +6044,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8528-2024</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6059,14 +6054,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45355</v>
+        <v>44550</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6079,7 +6074,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6122,7 +6117,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3686-2022</t>
+          <t>A 48656-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6136,10 +6131,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44586</v>
+        <v>44859</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6151,8 +6146,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6195,7 +6195,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9032-2023</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6209,10 +6209,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44979</v>
+        <v>44812</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6268,7 +6268,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25217-2024</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6278,14 +6278,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45462</v>
+        <v>45376</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6297,13 +6297,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6346,7 +6341,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16483-2023</t>
+          <t>A 25217-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6356,14 +6351,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45029</v>
+        <v>45462</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6375,8 +6370,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
         <v>45495</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30925-2023</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45113</v>
+        <v>45406</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6521,13 +6521,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6570,7 +6565,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 45869-2022</t>
+          <t>A 35108-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6584,10 +6579,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44844</v>
+        <v>46258</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6600,7 +6595,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6643,7 +6638,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 14217-2025</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6657,10 +6652,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45740</v>
+        <v>45678</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6672,8 +6667,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6716,7 +6716,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 11876-2024</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6726,14 +6726,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45376</v>
+        <v>44599</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6806,7 +6806,7 @@
         <v>45406</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35108-2026</t>
+          <t>A 11876-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6876,10 +6876,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46258</v>
+        <v>45376</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>46065</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 25306-2026</t>
+          <t>A 695-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46176</v>
+        <v>44930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3.2</v>
+        <v>13.6</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -647,12 +647,244 @@
         <v>10</v>
       </c>
       <c r="T2" t="n">
+        <v>18</v>
+      </c>
+      <c r="U2" t="n">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Brunlångöra
+Dropptaggsvamp
+Gulsparv
+Motaggsvamp
+Nordfladdermus
+Spillkråka
+Dvärgpipistrell
+Kungsfågel
+Större brunfladdermus
+Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 24599-2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44727</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
+        <v>11</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Almsnabbvinge
+Mindre tåtelsmygare
+Igelkottsröksvamp
+Mandelriska
+Sotriska
+Mattlummer
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 25306-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="n">
         <v>14</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U4" t="n">
         <v>14</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Slåtterfibbla
@@ -666,275 +898,43 @@
 Gröngöling</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 24599-2022</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>44727</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="n">
-        <v>11</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Almsnabbvinge
-Mindre tåtelsmygare
-Igelkottsröksvamp
-Mandelriska
-Sotriska
-Mattlummer
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 695-2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44930</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>18</v>
-      </c>
-      <c r="U4" t="n">
-        <v>18</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Brunlångöra
-Dropptaggsvamp
-Gulsparv
-Motaggsvamp
-Nordfladdermus
-Spillkråka
-Dvärgpipistrell
-Kungsfågel
-Större brunfladdermus
-Vattenfladdermus</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 48514-2025</t>
+          <t>A 22390-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45936</v>
+        <v>46154</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -963,25 +963,20 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>17.1</v>
+        <v>6.9</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -993,21 +988,143 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
       </c>
       <c r="T5" t="n">
+        <v>16</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Duvhök
+Järnsparv
+Rödvingetrast
+Sparvuggla
+Spillkråka
+Fjällvråk
+Gröngöling
+Kungsfågel
+Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 22390-2026 artfynd.xlsx", "A 22390-2026")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 22390-2026 karta.png", "A 22390-2026")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 22390-2026 georefererad karta.tif", "A 22390-2026")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 22390-2026 FSC-klagomål.docx", "A 22390-2026")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 22390-2026 FSC-klagomål mail.docx", "A 22390-2026")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 22390-2026 tillsynsbegäran.docx", "A 22390-2026")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 22390-2026 tillsynsbegäran mail.docx", "A 22390-2026")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 22390-2026 prioriterade fågelarter.docx", "A 22390-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 48514-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45936</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>8</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9</v>
+      </c>
+      <c r="T6" t="n">
         <v>91</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>89</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Hasselsnok
 Igelkott
@@ -1020,153 +1137,36 @@
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 48514-2025 artfynd.xlsx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 48514-2025 karta.png", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 48514-2025 georefererad karta.tif", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 48514-2025 FSC-klagomål.docx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 48514-2025 FSC-klagomål mail.docx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 48514-2025 tillsynsbegäran.docx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 48514-2025 tillsynsbegäran mail.docx", "A 48514-2025")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 48514-2025 prioriterade fågelarter.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 22390-2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>46154</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>9</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>9</v>
-      </c>
-      <c r="T6" t="n">
-        <v>16</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Duvhök
-Järnsparv
-Rödvingetrast
-Sparvuggla
-Spillkråka
-Fjällvråk
-Gröngöling
-Kungsfågel
-Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 22390-2026 artfynd.xlsx", "A 22390-2026")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 22390-2026 karta.png", "A 22390-2026")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 22390-2026 georefererad karta.tif", "A 22390-2026")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 22390-2026 FSC-klagomål.docx", "A 22390-2026")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 22390-2026 FSC-klagomål mail.docx", "A 22390-2026")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 22390-2026 tillsynsbegäran.docx", "A 22390-2026")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 22390-2026 tillsynsbegäran mail.docx", "A 22390-2026")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 22390-2026 prioriterade fågelarter.docx", "A 22390-2026")</f>
         <v/>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1697-2023</t>
+          <t>A 23829-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44938</v>
+        <v>45078</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2003,18 +2003,23 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -2028,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2040,153 +2045,148 @@
         <v>3</v>
       </c>
       <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.
+Tallticka
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 23829-2023 artfynd.xlsx", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 23829-2023 karta.png", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 23829-2023 georefererad karta.tif", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 23829-2023 FSC-klagomål.docx", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 23829-2023 FSC-klagomål mail.docx", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 23829-2023 tillsynsbegäran.docx", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 23829-2023 tillsynsbegäran mail.docx", "A 23829-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 1697-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44938</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Lunglav
 Bårdlav
 Grön sköldmossa</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1697-2023 artfynd.xlsx", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1697-2023 karta.png", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1697-2023 georefererad karta.tif", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1697-2023 FSC-klagomål.docx", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1697-2023 FSC-klagomål mail.docx", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1697-2023 tillsynsbegäran.docx", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1697-2023 tillsynsbegäran mail.docx", "A 1697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 23829-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45078</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.
-Tallticka
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 23829-2023 artfynd.xlsx", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 23829-2023 karta.png", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 23829-2023 georefererad karta.tif", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 23829-2023 FSC-klagomål.docx", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 23829-2023 FSC-klagomål mail.docx", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 23829-2023 tillsynsbegäran.docx", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 23829-2023 tillsynsbegäran mail.docx", "A 23829-2023")</f>
         <v/>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24799-2026</t>
+          <t>A 18100-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46171</v>
+        <v>44684</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2579,373 +2579,373 @@
         <v>2</v>
       </c>
       <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Svart trolldruva
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 24799-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
+      <c r="T20" t="n">
         <v>2</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Mindre märgborre
 Spillkråka</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24799-2026 artfynd.xlsx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24799-2026 karta.png", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24799-2026 georefererad karta.tif", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24799-2026 FSC-klagomål.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24799-2026 FSC-klagomål mail.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24799-2026 tillsynsbegäran.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24799-2026 tillsynsbegäran mail.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 24799-2026 prioriterade fågelarter.docx", "A 24799-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 25319-2026</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>46176</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="E21" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>1.6</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>3</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Grovticka
 Spillkråka</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 25315-2026</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>46176</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="E22" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>1.4</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>3</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>3</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tofsmes</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 18100-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44684</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Svart trolldruva
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
         <v/>
       </c>
     </row>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15690-2023</t>
+          <t>A 14214-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45020</v>
+        <v>45740</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3091,19 +3091,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3118,55 +3118,59 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14214-2025</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3180,10 +3184,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45740</v>
+        <v>45481</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3196,19 +3200,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3220,62 +3224,58 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12305-2026</t>
+          <t>A 1691-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46087</v>
+        <v>44938</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3304,19 +3304,14 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3346,50 +3341,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12590-2026</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3403,10 +3394,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46090</v>
+        <v>44586</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3418,22 +3409,17 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>17.1</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3448,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3460,50 +3446,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12842-2026</t>
+          <t>A 15690-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3517,10 +3499,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46092</v>
+        <v>45020</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,13 +3514,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3574,46 +3551,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 61514-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3627,10 +3604,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44586</v>
+        <v>44916</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3643,13 +3620,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>17.1</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3683,42 +3660,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 12305-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3732,10 +3709,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45481</v>
+        <v>46087</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3747,14 +3724,19 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3788,42 +3770,46 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1691-2023</t>
+          <t>A 12590-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3837,10 +3823,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44938</v>
+        <v>46090</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3852,18 +3838,23 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
@@ -3877,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3893,42 +3884,46 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61514-2022</t>
+          <t>A 12842-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3942,10 +3937,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44916</v>
+        <v>46092</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3957,18 +3952,23 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3994,39 +3994,39 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 73772-2021</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44552</v>
+        <v>45678</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4291,8 +4291,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4352,7 +4357,7 @@
         <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4413,7 +4418,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 73772-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4427,10 +4432,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45740</v>
+        <v>44552</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4443,7 +4448,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4486,7 +4491,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 48656-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4500,10 +4505,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45062</v>
+        <v>44859</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4515,8 +4520,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4559,7 +4569,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30925-2023</t>
+          <t>A 11876-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4573,10 +4583,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45113</v>
+        <v>45376</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4588,13 +4598,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4637,7 +4642,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 14217-2025</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4651,10 +4656,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45740</v>
+        <v>45406</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4667,7 +4672,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4710,7 +4715,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 73194-2021</t>
+          <t>A 16142-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4724,10 +4729,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44550</v>
+        <v>45406</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4740,7 +4745,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4783,7 +4788,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 16483-2023</t>
+          <t>A 46405-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4797,10 +4802,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45029</v>
+        <v>44846</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4813,7 +4818,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4856,7 +4861,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12306-2026</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4870,10 +4875,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46087</v>
+        <v>45376</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4885,13 +4890,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12294-2026</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46087</v>
+        <v>44812</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4963,13 +4963,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5012,7 +5007,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 54468-2025</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5026,10 +5021,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45965</v>
+        <v>44550</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5042,7 +5037,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5085,7 +5080,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 46405-2022</t>
+          <t>A 73194-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5099,10 +5094,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44846</v>
+        <v>44550</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5115,7 +5110,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5158,7 +5153,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 20649-2022</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5172,10 +5167,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44700</v>
+        <v>44550</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5187,13 +5182,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5236,7 +5226,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8528-2024</t>
+          <t>A 54468-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5246,14 +5236,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45355</v>
+        <v>45965</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5266,7 +5256,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5309,7 +5299,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5323,10 +5313,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46154</v>
+        <v>45020</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5339,7 +5329,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5382,7 +5372,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5396,10 +5386,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46164</v>
+        <v>45740</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5412,7 +5402,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5455,7 +5445,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 23716-2026</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5469,10 +5459,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5485,7 +5475,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5528,7 +5518,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5545,7 +5535,7 @@
         <v>46164</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5558,7 +5548,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5601,7 +5591,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45869-2022</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5615,10 +5605,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44844</v>
+        <v>46164</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5631,7 +5621,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5674,7 +5664,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3686-2022</t>
+          <t>A 23716-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5688,10 +5678,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44586</v>
+        <v>46164</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5704,7 +5694,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5747,7 +5737,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 27717-2026</t>
+          <t>A 20649-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5761,10 +5751,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46190</v>
+        <v>44700</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5782,7 +5772,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5825,7 +5815,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5839,10 +5829,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45020</v>
+        <v>45062</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5855,7 +5845,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5898,7 +5888,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5908,14 +5898,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44550</v>
+        <v>44599</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5928,7 +5918,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5971,7 +5961,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9032-2023</t>
+          <t>A 8528-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5981,14 +5971,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44979</v>
+        <v>45355</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6001,7 +5991,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6044,7 +6034,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 3686-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6058,10 +6048,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44550</v>
+        <v>44586</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6074,7 +6064,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6117,7 +6107,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 48656-2022</t>
+          <t>A 27717-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6131,10 +6121,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44859</v>
+        <v>46190</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6152,7 +6142,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6195,7 +6185,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 9032-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6209,10 +6199,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44812</v>
+        <v>44979</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6225,7 +6215,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6268,7 +6258,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 25217-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6278,14 +6268,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45376</v>
+        <v>45462</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6297,8 +6287,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6341,7 +6336,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 25217-2024</t>
+          <t>A 12306-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6351,14 +6346,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45462</v>
+        <v>46087</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6376,7 +6371,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6419,7 +6414,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30622-2024</t>
+          <t>A 12294-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6429,14 +6424,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45495</v>
+        <v>46087</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6448,8 +6443,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6492,7 +6492,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 16483-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45406</v>
+        <v>45029</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6565,7 +6565,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 35108-2026</t>
+          <t>A 30622-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6575,14 +6575,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46258</v>
+        <v>45495</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.4</v>
+        <v>0.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6638,7 +6638,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 30925-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45678</v>
+        <v>45113</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6716,7 +6716,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 45869-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6726,14 +6726,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44599</v>
+        <v>44844</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6789,7 +6789,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 16142-2024</t>
+          <t>A 14217-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6803,10 +6803,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45406</v>
+        <v>45740</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6862,7 +6862,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11876-2024</t>
+          <t>A 35108-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6876,10 +6876,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45376</v>
+        <v>46258</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>46065</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 695-2023</t>
+          <t>A 24599-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44930</v>
+        <v>44727</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>13.6</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -638,21 +638,135 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
       </c>
       <c r="T2" t="n">
+        <v>11</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Almsnabbvinge
+Mindre tåtelsmygare
+Igelkottsröksvamp
+Mandelriska
+Sotriska
+Mattlummer
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 695-2023</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44930</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
         <v>18</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U3" t="n">
         <v>18</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Brunlångöra
 Dropptaggsvamp
@@ -666,150 +780,36 @@
 Vattenfladdermus</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 24599-2022</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>44727</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="n">
-        <v>11</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Almsnabbvinge
-Mindre tåtelsmygare
-Igelkottsröksvamp
-Mandelriska
-Sotriska
-Mattlummer
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
         <v/>
       </c>
     </row>
@@ -833,7 +833,7 @@
         <v>46176</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 22390-2026</t>
+          <t>A 48514-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46154</v>
+        <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -963,20 +963,25 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>6.9</v>
+        <v>17.1</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -988,21 +993,138 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
       </c>
       <c r="T5" t="n">
+        <v>91</v>
+      </c>
+      <c r="U5" t="n">
+        <v>89</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Hasselsnok
+Igelkott
+Lammticka
+Motaggsvamp
+Skarp dropptaggsvamp
+Svartvit taggsvamp
+Tallticka
+Talltita
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 48514-2025 artfynd.xlsx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 48514-2025 karta.png", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 48514-2025 georefererad karta.tif", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 48514-2025 FSC-klagomål.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 48514-2025 FSC-klagomål mail.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 48514-2025 tillsynsbegäran.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 48514-2025 tillsynsbegäran mail.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 48514-2025 prioriterade fågelarter.docx", "A 48514-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 22390-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9</v>
+      </c>
+      <c r="T6" t="n">
         <v>16</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Järnsparv
@@ -1015,158 +1137,36 @@
 Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 22390-2026 artfynd.xlsx", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 22390-2026 karta.png", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 22390-2026 georefererad karta.tif", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 22390-2026 FSC-klagomål.docx", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 22390-2026 FSC-klagomål mail.docx", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 22390-2026 tillsynsbegäran.docx", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 22390-2026 tillsynsbegäran mail.docx", "A 22390-2026")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 22390-2026 prioriterade fågelarter.docx", "A 22390-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 48514-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45936</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>8</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>9</v>
-      </c>
-      <c r="T6" t="n">
-        <v>91</v>
-      </c>
-      <c r="U6" t="n">
-        <v>89</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Hasselsnok
-Igelkott
-Lammticka
-Motaggsvamp
-Skarp dropptaggsvamp
-Svartvit taggsvamp
-Tallticka
-Talltita
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 48514-2025 artfynd.xlsx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 48514-2025 karta.png", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 48514-2025 georefererad karta.tif", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 48514-2025 FSC-klagomål.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 48514-2025 FSC-klagomål mail.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 48514-2025 tillsynsbegäran.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 48514-2025 tillsynsbegäran mail.docx", "A 48514-2025")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 48514-2025 prioriterade fågelarter.docx", "A 48514-2025")</f>
         <v/>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 23829-2023</t>
+          <t>A 1697-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45078</v>
+        <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2003,22 +2003,17 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2045,148 +2040,153 @@
         <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Lunglav
+Bårdlav
+Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1697-2023 artfynd.xlsx", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1697-2023 karta.png", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1697-2023 georefererad karta.tif", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1697-2023 FSC-klagomål.docx", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1697-2023 FSC-klagomål mail.docx", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1697-2023 tillsynsbegäran.docx", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1697-2023 tillsynsbegäran mail.docx", "A 1697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 23829-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Fjällig taggsvamp s.str.
 Tallticka
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 23829-2023 artfynd.xlsx", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 23829-2023 karta.png", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 23829-2023 georefererad karta.tif", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 23829-2023 FSC-klagomål.docx", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 23829-2023 FSC-klagomål mail.docx", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 23829-2023 tillsynsbegäran.docx", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 23829-2023 tillsynsbegäran mail.docx", "A 23829-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 1697-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44938</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lunglav
-Bårdlav
-Grön sköldmossa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1697-2023 artfynd.xlsx", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1697-2023 karta.png", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1697-2023 georefererad karta.tif", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1697-2023 FSC-klagomål.docx", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1697-2023 FSC-klagomål mail.docx", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1697-2023 tillsynsbegäran.docx", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1697-2023 tillsynsbegäran mail.docx", "A 1697-2023")</f>
         <v/>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18100-2022</t>
+          <t>A 24799-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44684</v>
+        <v>46171</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2579,373 +2579,373 @@
         <v>2</v>
       </c>
       <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Mindre märgborre
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24799-2026 artfynd.xlsx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24799-2026 karta.png", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24799-2026 georefererad karta.tif", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24799-2026 FSC-klagomål.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24799-2026 FSC-klagomål mail.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24799-2026 tillsynsbegäran.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24799-2026 tillsynsbegäran mail.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 24799-2026 prioriterade fågelarter.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 25319-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
         <v>3</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>3</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Grovticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 25315-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 18100-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44684</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Svart trolldruva
 Gullviva</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 24799-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Mindre märgborre
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24799-2026 artfynd.xlsx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24799-2026 karta.png", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24799-2026 georefererad karta.tif", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24799-2026 FSC-klagomål.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24799-2026 FSC-klagomål mail.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24799-2026 tillsynsbegäran.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24799-2026 tillsynsbegäran mail.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 24799-2026 prioriterade fågelarter.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 25319-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Grovticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 25315-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
         <v/>
       </c>
     </row>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 14214-2025</t>
+          <t>A 15690-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45740</v>
+        <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3091,19 +3091,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3118,59 +3118,55 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 14214-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3184,10 +3180,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45481</v>
+        <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3200,20 +3196,20 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
@@ -3224,58 +3220,62 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 1691-2023</t>
+          <t>A 12305-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44938</v>
+        <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3304,14 +3304,19 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3341,46 +3346,50 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 12590-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3394,10 +3403,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44586</v>
+        <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3409,18 +3418,23 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>17.1</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
@@ -3434,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3446,46 +3460,50 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15690-2023</t>
+          <t>A 12842-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3499,10 +3517,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45020</v>
+        <v>46092</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3514,8 +3532,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3551,46 +3574,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 61514-2022</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3604,10 +3627,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44916</v>
+        <v>44586</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3620,13 +3643,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>17.1</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3660,42 +3683,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12305-2026</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3709,10 +3732,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46087</v>
+        <v>45481</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3724,19 +3747,14 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3770,46 +3788,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12590-2026</t>
+          <t>A 1691-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3823,10 +3837,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46090</v>
+        <v>44938</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3838,22 +3852,17 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3868,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3884,46 +3893,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12842-2026</t>
+          <t>A 61514-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3937,10 +3942,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46092</v>
+        <v>44916</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3952,22 +3957,17 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3982,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3994,39 +3994,39 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 73772-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45678</v>
+        <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4291,13 +4291,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4357,7 +4352,7 @@
         <v>44859</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4418,7 +4413,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 73772-2021</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4432,10 +4427,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44552</v>
+        <v>45062</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4491,7 +4486,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 48656-2022</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4505,10 +4500,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44859</v>
+        <v>45740</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4520,13 +4515,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4569,7 +4559,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11876-2024</t>
+          <t>A 30925-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4583,10 +4573,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45376</v>
+        <v>45113</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4598,8 +4588,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4642,7 +4637,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 14217-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4656,10 +4651,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45406</v>
+        <v>45740</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4672,7 +4667,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4715,7 +4710,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16142-2024</t>
+          <t>A 73194-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4729,10 +4724,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45406</v>
+        <v>44550</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4745,7 +4740,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4788,7 +4783,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 46405-2022</t>
+          <t>A 16483-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4802,10 +4797,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44846</v>
+        <v>45029</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4818,7 +4813,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4861,7 +4856,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 12306-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4875,10 +4870,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45376</v>
+        <v>46087</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4890,8 +4885,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 12294-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44812</v>
+        <v>46087</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4963,8 +4963,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5007,7 +5012,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 46405-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5021,10 +5026,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44550</v>
+        <v>44846</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5037,7 +5042,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5080,7 +5085,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 73194-2021</t>
+          <t>A 20649-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5094,10 +5099,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44550</v>
+        <v>44700</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5109,8 +5114,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5153,7 +5163,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 8528-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5163,14 +5173,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44550</v>
+        <v>45355</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5183,7 +5193,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5226,7 +5236,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 54468-2025</t>
+          <t>A 45869-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5240,10 +5250,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45965</v>
+        <v>44844</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5256,7 +5266,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5299,7 +5309,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 3686-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5313,10 +5323,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45020</v>
+        <v>44586</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5329,7 +5339,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5372,7 +5382,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5386,10 +5396,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45740</v>
+        <v>45020</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5402,7 +5412,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5445,7 +5455,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 54468-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5459,10 +5469,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46154</v>
+        <v>45965</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5475,7 +5485,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5518,7 +5528,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5532,10 +5542,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46164</v>
+        <v>44550</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5548,7 +5558,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5591,7 +5601,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 9032-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5605,10 +5615,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46164</v>
+        <v>44979</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5621,7 +5631,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5664,7 +5674,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23716-2026</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5678,10 +5688,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46164</v>
+        <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5694,7 +5704,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5737,7 +5747,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20649-2022</t>
+          <t>A 48656-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5751,10 +5761,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44700</v>
+        <v>44859</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5772,7 +5782,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5815,7 +5825,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5829,10 +5839,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45062</v>
+        <v>44812</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5845,7 +5855,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5888,7 +5898,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5898,14 +5908,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44599</v>
+        <v>45376</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5918,7 +5928,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5961,7 +5971,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8528-2024</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5971,14 +5981,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45355</v>
+        <v>46154</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5991,7 +6001,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6034,7 +6044,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3686-2022</t>
+          <t>A 25217-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6044,14 +6054,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44586</v>
+        <v>45462</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6063,8 +6073,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6107,7 +6122,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 27717-2026</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6121,10 +6136,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46190</v>
+        <v>46164</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6136,13 +6151,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6185,7 +6195,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9032-2023</t>
+          <t>A 23716-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6199,10 +6209,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44979</v>
+        <v>46164</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6215,7 +6225,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6258,7 +6268,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25217-2024</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6268,14 +6278,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45462</v>
+        <v>46164</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6287,13 +6297,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6336,7 +6341,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12306-2026</t>
+          <t>A 30622-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6346,14 +6351,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46087</v>
+        <v>45495</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6365,13 +6370,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12294-2026</t>
+          <t>A 27717-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6428,10 +6428,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46087</v>
+        <v>46190</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6492,7 +6492,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 16483-2023</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45029</v>
+        <v>45406</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6565,7 +6565,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30622-2024</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6575,14 +6575,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45495</v>
+        <v>45678</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6594,8 +6594,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6638,7 +6643,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 30925-2023</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6648,14 +6653,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45113</v>
+        <v>44599</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6667,13 +6672,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6716,7 +6716,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 45869-2022</t>
+          <t>A 16142-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6730,10 +6730,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44844</v>
+        <v>45406</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6789,7 +6789,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14217-2025</t>
+          <t>A 11876-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6803,10 +6803,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45740</v>
+        <v>45376</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6879,7 +6879,7 @@
         <v>46258</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>46065</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 24599-2022</t>
+          <t>A 695-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44727</v>
+        <v>44930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>13.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -638,21 +638,139 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
       </c>
       <c r="T2" t="n">
+        <v>18</v>
+      </c>
+      <c r="U2" t="n">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Brunlångöra
+Dropptaggsvamp
+Gulsparv
+Motaggsvamp
+Nordfladdermus
+Spillkråka
+Dvärgpipistrell
+Kungsfågel
+Större brunfladdermus
+Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 24599-2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44727</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
         <v>11</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U3" t="n">
         <v>3</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -666,150 +784,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 695-2023</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>44930</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="J3" t="n">
-        <v>8</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="n">
-        <v>18</v>
-      </c>
-      <c r="U3" t="n">
-        <v>18</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Brunlångöra
-Dropptaggsvamp
-Gulsparv
-Motaggsvamp
-Nordfladdermus
-Spillkråka
-Dvärgpipistrell
-Kungsfågel
-Större brunfladdermus
-Vattenfladdermus</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 695-2023 artfynd.xlsx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 695-2023 karta.png", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 695-2023 georefererad karta.tif", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 695-2023 FSC-klagomål.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 695-2023 FSC-klagomål mail.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 695-2023 tillsynsbegäran.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 695-2023 tillsynsbegäran mail.docx", "A 695-2023")</f>
-        <v/>
-      </c>
-      <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 695-2023 prioriterade fågelarter.docx", "A 695-2023")</f>
         <v/>
       </c>
     </row>
@@ -833,7 +833,7 @@
         <v>46176</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1697-2023</t>
+          <t>A 23829-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44938</v>
+        <v>45078</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2003,18 +2003,23 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -2028,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2040,153 +2045,148 @@
         <v>3</v>
       </c>
       <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.
+Tallticka
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 23829-2023 artfynd.xlsx", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 23829-2023 karta.png", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 23829-2023 georefererad karta.tif", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 23829-2023 FSC-klagomål.docx", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 23829-2023 FSC-klagomål mail.docx", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 23829-2023 tillsynsbegäran.docx", "A 23829-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 23829-2023 tillsynsbegäran mail.docx", "A 23829-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 1697-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44938</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Lunglav
 Bårdlav
 Grön sköldmossa</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1697-2023 artfynd.xlsx", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1697-2023 karta.png", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1697-2023 georefererad karta.tif", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1697-2023 FSC-klagomål.docx", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1697-2023 FSC-klagomål mail.docx", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1697-2023 tillsynsbegäran.docx", "A 1697-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1697-2023 tillsynsbegäran mail.docx", "A 1697-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 23829-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45078</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.
-Tallticka
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 23829-2023 artfynd.xlsx", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 23829-2023 karta.png", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 23829-2023 georefererad karta.tif", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 23829-2023 FSC-klagomål.docx", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 23829-2023 FSC-klagomål mail.docx", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 23829-2023 tillsynsbegäran.docx", "A 23829-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 23829-2023 tillsynsbegäran mail.docx", "A 23829-2023")</f>
         <v/>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 60406-2025</t>
+          <t>A 18100-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45995</v>
+        <v>44684</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2434,19 +2434,14 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2473,479 +2468,484 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Svart trolldruva
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 60406-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>2</v>
       </c>
-      <c r="U18" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 60406-2025 artfynd.xlsx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 60406-2025 karta.png", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 60406-2025 georefererad karta.tif", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 60406-2025 FSC-klagomål.docx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 60406-2025 FSC-klagomål mail.docx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 60406-2025 tillsynsbegäran.docx", "A 60406-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 60406-2025 tillsynsbegäran mail.docx", "A 60406-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 24799-2026</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>46171</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="E20" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I20" t="n">
         <v>1.7</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>2</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Mindre märgborre
 Spillkråka</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24799-2026 artfynd.xlsx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24799-2026 karta.png", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24799-2026 georefererad karta.tif", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24799-2026 FSC-klagomål.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24799-2026 FSC-klagomål mail.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24799-2026 tillsynsbegäran.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24799-2026 tillsynsbegäran mail.docx", "A 24799-2026")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 24799-2026 prioriterade fågelarter.docx", "A 24799-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 25319-2026</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>46176</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="E21" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>1.6</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>3</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Grovticka
 Spillkråka</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 25315-2026</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>46176</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="E22" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>1.4</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>3</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>3</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tofsmes</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 18100-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44684</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Svart trolldruva
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
         <v/>
       </c>
     </row>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15690-2023</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45020</v>
+        <v>45481</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3091,16 +3091,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3131,42 +3131,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14214-2025</t>
+          <t>A 1691-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45740</v>
+        <v>44938</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3196,19 +3196,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3220,62 +3220,58 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12305-2026</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3289,10 +3285,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46087</v>
+        <v>44586</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3304,19 +3300,14 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>17.1</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3350,46 +3341,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12590-2026</t>
+          <t>A 15690-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3403,10 +3390,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46090</v>
+        <v>45020</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3418,16 +3405,11 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3460,50 +3442,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12842-2026</t>
+          <t>A 61514-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3517,10 +3495,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46092</v>
+        <v>44916</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,22 +3510,17 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3562,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3574,46 +3547,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 14214-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3627,10 +3600,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44586</v>
+        <v>45740</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3643,20 +3616,20 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>17.1</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3667,58 +3640,62 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 12305-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3732,10 +3709,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45481</v>
+        <v>46087</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3747,14 +3724,19 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3788,42 +3770,46 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1691-2023</t>
+          <t>A 12590-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3837,10 +3823,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44938</v>
+        <v>46090</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3852,18 +3838,23 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
@@ -3877,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3893,42 +3884,46 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61514-2022</t>
+          <t>A 12842-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3942,10 +3937,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44916</v>
+        <v>46092</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3957,18 +3952,23 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3994,39 +3994,39 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 73772-2021</t>
+          <t>A 48647-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44552</v>
+        <v>44859</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4291,8 +4291,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4335,7 +4340,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 48647-2022</t>
+          <t>A 73772-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4349,10 +4354,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44859</v>
+        <v>44552</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4364,13 +4369,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45062</v>
+        <v>45406</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4486,7 +4486,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 46405-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45740</v>
+        <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30925-2023</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45113</v>
+        <v>45376</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4588,13 +4588,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4637,7 +4632,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 14217-2025</t>
+          <t>A 30622-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4647,14 +4642,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45740</v>
+        <v>45495</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4667,7 +4662,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4710,7 +4705,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 73194-2021</t>
+          <t>A 30925-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4724,10 +4719,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44550</v>
+        <v>45113</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4739,8 +4734,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4783,7 +4783,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 16483-2023</t>
+          <t>A 48656-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45029</v>
+        <v>44859</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4812,8 +4812,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4856,7 +4861,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12306-2026</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4870,10 +4875,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46087</v>
+        <v>44812</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4885,13 +4890,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12294-2026</t>
+          <t>A 45869-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46087</v>
+        <v>44844</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4963,13 +4963,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5012,7 +5007,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46405-2022</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5026,10 +5021,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44846</v>
+        <v>44550</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5042,7 +5037,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5085,7 +5080,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20649-2022</t>
+          <t>A 73194-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5099,10 +5094,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44700</v>
+        <v>44550</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5114,13 +5109,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5163,7 +5153,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 8528-2024</t>
+          <t>A 14217-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5173,14 +5163,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45355</v>
+        <v>45740</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5193,7 +5183,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5236,7 +5226,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45869-2022</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5250,10 +5240,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44844</v>
+        <v>44550</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5266,7 +5256,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5309,7 +5299,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 3686-2022</t>
+          <t>A 11876-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5323,10 +5313,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44586</v>
+        <v>45376</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5339,7 +5329,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5382,7 +5372,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 16142-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5396,10 +5386,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45020</v>
+        <v>45406</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5412,7 +5402,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5455,7 +5445,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 54468-2025</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5469,10 +5459,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45965</v>
+        <v>45020</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5485,7 +5475,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5528,7 +5518,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5542,10 +5532,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44550</v>
+        <v>45740</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5558,7 +5548,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5601,7 +5591,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9032-2023</t>
+          <t>A 54468-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5615,10 +5605,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44979</v>
+        <v>45965</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5631,7 +5621,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5674,7 +5664,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 20649-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5688,10 +5678,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44550</v>
+        <v>44700</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5703,8 +5693,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5747,7 +5742,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 48656-2022</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5761,10 +5756,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44859</v>
+        <v>45062</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5776,13 +5771,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5825,7 +5815,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5835,14 +5825,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44812</v>
+        <v>44599</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5855,7 +5845,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5898,7 +5888,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 8528-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5908,14 +5898,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45376</v>
+        <v>45355</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5928,7 +5918,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5971,7 +5961,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5985,10 +5975,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46154</v>
+        <v>45678</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6000,8 +5990,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6044,7 +6039,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 25217-2024</t>
+          <t>A 3686-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6054,14 +6049,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45462</v>
+        <v>44586</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6073,13 +6068,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6122,7 +6112,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 9032-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6136,10 +6126,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46164</v>
+        <v>44979</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6152,7 +6142,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6195,7 +6185,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 23716-2026</t>
+          <t>A 25217-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6205,14 +6195,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46164</v>
+        <v>45462</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6224,8 +6214,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6268,7 +6263,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 16483-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6282,10 +6277,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46164</v>
+        <v>45029</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6298,7 +6293,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6341,7 +6336,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30622-2024</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6351,14 +6346,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45495</v>
+        <v>46154</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6371,7 +6366,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6414,7 +6409,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27717-2026</t>
+          <t>A 12306-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6428,10 +6423,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46190</v>
+        <v>46087</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6449,7 +6444,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6492,7 +6487,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 12294-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6506,10 +6501,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45406</v>
+        <v>46087</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6521,8 +6516,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6565,7 +6565,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45678</v>
+        <v>46164</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6594,13 +6594,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6643,7 +6638,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6653,14 +6648,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44599</v>
+        <v>46164</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6673,7 +6668,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6716,7 +6711,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16142-2024</t>
+          <t>A 23716-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6730,10 +6725,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45406</v>
+        <v>46164</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6746,7 +6741,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6789,7 +6784,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11876-2024</t>
+          <t>A 27717-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6803,10 +6798,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45376</v>
+        <v>46190</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6818,8 +6813,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6879,7 +6879,7 @@
         <v>46258</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>46065</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -601,7 +601,7 @@
         <v>44930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44727</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>46176</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45078</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>44938</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>44684</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>45995</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>46171</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>46176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>46176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>45481</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>44938</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44586</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>45020</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>44916</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>45740</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>46087</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>46090</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>46092</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44859</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>44552</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>45406</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>45376</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>45495</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>45113</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44859</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>44812</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>44844</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>44550</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>44550</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>45740</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>44550</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>45376</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>45406</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45020</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>45740</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>45965</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>44700</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45062</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>44599</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         <v>45355</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>45678</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>44586</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44979</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>45462</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>45029</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>46154</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>46087</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>46087</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>46164</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>46164</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>46164</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>46190</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>46258</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>46065</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -601,7 +601,7 @@
         <v>44930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44727</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>46176</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45078</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>44938</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>44684</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>45995</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>46171</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>46176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>46176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>44481</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>45481</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>44938</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44586</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>45020</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>44916</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>45740</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>46087</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>46090</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>46092</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44859</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44859</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>44552</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>45406</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>45376</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>45495</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>45113</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44859</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>44812</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>44844</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>44550</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>44550</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>45740</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>44550</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>45376</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>45406</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45020</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>45740</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>45965</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>44700</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45062</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>44599</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         <v>45355</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>45678</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>44586</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44979</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>45462</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>45029</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>46154</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>46087</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>46087</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>46164</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>46164</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>46164</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>46190</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>46258</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>46065</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE72"/>
+  <dimension ref="A1:AE71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 24599-2022</t>
+          <t>A 25306-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44727</v>
+        <v>46176</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -732,45 +732,163 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
         <v>3</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3</v>
       </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
       </c>
       <c r="T3" t="n">
+        <v>14</v>
+      </c>
+      <c r="U3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Slåtterfibbla
+Tallticka
+Blåmossa
+Mindre märgborre
+Kransmossa
+Liljekonvalj
+Spillkråka
+Tofsmes
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 24599-2022</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>44727</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="n">
         <v>11</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>3</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -784,150 +902,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 25306-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>14</v>
-      </c>
-      <c r="U4" t="n">
-        <v>14</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Slåtterfibbla
-Tallticka
-Blåmossa
-Mindre märgborre
-Kransmossa
-Liljekonvalj
-Spillkråka
-Tofsmes
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
         <v/>
       </c>
     </row>
@@ -951,7 +951,7 @@
         <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 23829-2023</t>
+          <t>A 1697-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45078</v>
+        <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2003,22 +2003,17 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2045,155 +2040,160 @@
         <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Lunglav
+Bårdlav
+Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1697-2023 artfynd.xlsx", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1697-2023 karta.png", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1697-2023 georefererad karta.tif", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1697-2023 FSC-klagomål.docx", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1697-2023 FSC-klagomål mail.docx", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1697-2023 tillsynsbegäran.docx", "A 1697-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1697-2023 tillsynsbegäran mail.docx", "A 1697-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 23829-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Fjällig taggsvamp s.str.
 Tallticka
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 23829-2023 artfynd.xlsx", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 23829-2023 karta.png", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 23829-2023 georefererad karta.tif", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 23829-2023 FSC-klagomål.docx", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 23829-2023 FSC-klagomål mail.docx", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 23829-2023 tillsynsbegäran.docx", "A 23829-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 23829-2023 tillsynsbegäran mail.docx", "A 23829-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 1697-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44938</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lunglav
-Bårdlav
-Grön sköldmossa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1697-2023 artfynd.xlsx", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1697-2023 karta.png", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1697-2023 georefererad karta.tif", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1697-2023 FSC-klagomål.docx", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1697-2023 FSC-klagomål mail.docx", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1697-2023 tillsynsbegäran.docx", "A 1697-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1697-2023 tillsynsbegäran mail.docx", "A 1697-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 30378-2024</t>
+          <t>A 18100-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2203,14 +2203,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45491</v>
+        <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2223,16 +2223,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2256,703 +2256,703 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Svart trolldruva
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 24799-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Mindre märgborre
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24799-2026 artfynd.xlsx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24799-2026 karta.png", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24799-2026 georefererad karta.tif", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24799-2026 FSC-klagomål.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24799-2026 FSC-klagomål mail.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24799-2026 tillsynsbegäran.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24799-2026 tillsynsbegäran mail.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 24799-2026 prioriterade fågelarter.docx", "A 24799-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 25319-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Grovticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 25315-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 60406-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 60406-2025 artfynd.xlsx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 60406-2025 karta.png", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 60406-2025 georefererad karta.tif", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 60406-2025 FSC-klagomål.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 60406-2025 FSC-klagomål mail.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 60406-2025 tillsynsbegäran.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 60406-2025 tillsynsbegäran mail.docx", "A 60406-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 30378-2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45491</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Mindre tåtelsmygare
 Svinrot</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 30378-2024 artfynd.xlsx", "A 30378-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 30378-2024 karta.png", "A 30378-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 30378-2024 georefererad karta.tif", "A 30378-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 30378-2024 FSC-klagomål.docx", "A 30378-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 30378-2024 FSC-klagomål mail.docx", "A 30378-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 30378-2024 tillsynsbegäran.docx", "A 30378-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 30378-2024 tillsynsbegäran mail.docx", "A 30378-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 15905-2022</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>44664</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E22" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I22" t="n">
         <v>11.2</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>2</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T22" t="n">
         <v>3</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U22" t="n">
         <v>3</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15905-2022 artfynd.xlsx", "A 15905-2022")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15905-2022 karta.png", "A 15905-2022")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15905-2022 georefererad karta.tif", "A 15905-2022")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15905-2022 FSC-klagomål.docx", "A 15905-2022")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15905-2022 FSC-klagomål mail.docx", "A 15905-2022")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15905-2022 tillsynsbegäran.docx", "A 15905-2022")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15905-2022 tillsynsbegäran mail.docx", "A 15905-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 18100-2022</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44684</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Svart trolldruva
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 18100-2022 artfynd.xlsx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 18100-2022 karta.png", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 18100-2022 georefererad karta.tif", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 18100-2022 FSC-klagomål.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 18100-2022 FSC-klagomål mail.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 18100-2022 tillsynsbegäran.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 18100-2022 tillsynsbegäran mail.docx", "A 18100-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 60406-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45995</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 60406-2025 artfynd.xlsx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 60406-2025 karta.png", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 60406-2025 georefererad karta.tif", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 60406-2025 FSC-klagomål.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 60406-2025 FSC-klagomål mail.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 60406-2025 tillsynsbegäran.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 60406-2025 tillsynsbegäran mail.docx", "A 60406-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 24799-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Mindre märgborre
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24799-2026 artfynd.xlsx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24799-2026 karta.png", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24799-2026 georefererad karta.tif", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24799-2026 FSC-klagomål.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24799-2026 FSC-klagomål mail.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24799-2026 tillsynsbegäran.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24799-2026 tillsynsbegäran mail.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 24799-2026 prioriterade fågelarter.docx", "A 24799-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 25319-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Grovticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25319-2026 artfynd.xlsx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25319-2026 karta.png", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25319-2026 georefererad karta.tif", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25319-2026 FSC-klagomål.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25319-2026 FSC-klagomål mail.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25319-2026 tillsynsbegäran.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25319-2026 tillsynsbegäran mail.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25319-2026 prioriterade fågelarter.docx", "A 25319-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 25315-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25315-2026 artfynd.xlsx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25315-2026 karta.png", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25315-2026 georefererad karta.tif", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25315-2026 FSC-klagomål.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25315-2026 FSC-klagomål mail.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25315-2026 tillsynsbegäran.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25315-2026 tillsynsbegäran mail.docx", "A 25315-2026")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25315-2026 prioriterade fågelarter.docx", "A 25315-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 56816-2021</t>
+          <t>A 15690-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44481</v>
+        <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>10.9</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -3022,46 +3022,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 56816-2021 artfynd.xlsx", "A 56816-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 56816-2021 karta.png", "A 56816-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 56816-2021 georefererad karta.tif", "A 56816-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 56816-2021 FSC-klagomål.docx", "A 56816-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 56816-2021 FSC-klagomål mail.docx", "A 56816-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 56816-2021 tillsynsbegäran.docx", "A 56816-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 56816-2021 tillsynsbegäran mail.docx", "A 56816-2021")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 56816-2021 prioriterade fågelarter.docx", "A 56816-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28983-2024</t>
+          <t>A 12305-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3075,10 +3071,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45481</v>
+        <v>46087</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3090,14 +3086,19 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3131,42 +3132,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 1691-2023</t>
+          <t>A 12590-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3180,10 +3185,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44938</v>
+        <v>46090</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3195,18 +3200,23 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3220,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3236,42 +3246,46 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 3726-2022</t>
+          <t>A 12842-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3285,10 +3299,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44586</v>
+        <v>46092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3300,18 +3314,23 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>17.1</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
@@ -3325,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3337,46 +3356,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15690-2023</t>
+          <t>A 14214-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3390,10 +3409,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45020</v>
+        <v>45740</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3406,19 +3425,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3433,55 +3452,59 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15690-2023 artfynd.xlsx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15690-2023 karta.png", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15690-2023 georefererad karta.tif", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15690-2023 FSC-klagomål.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15690-2023 FSC-klagomål mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15690-2023 tillsynsbegäran.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15690-2023 tillsynsbegäran mail.docx", "A 15690-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 61514-2022</t>
+          <t>A 3726-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3495,10 +3518,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44916</v>
+        <v>44586</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3511,13 +3534,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>17.1</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3551,42 +3574,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 3726-2022 artfynd.xlsx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 3726-2022 karta.png", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 3726-2022 georefererad karta.tif", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 3726-2022 FSC-klagomål.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 3726-2022 FSC-klagomål mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 3726-2022 tillsynsbegäran.docx", "A 3726-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 3726-2022 tillsynsbegäran mail.docx", "A 3726-2022")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 14214-2025</t>
+          <t>A 28983-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3600,10 +3623,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45740</v>
+        <v>45481</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3616,19 +3639,19 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3640,62 +3663,58 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 14214-2025 artfynd.xlsx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 28983-2024 artfynd.xlsx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 14214-2025 karta.png", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 28983-2024 karta.png", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 14214-2025 georefererad karta.tif", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 28983-2024 georefererad karta.tif", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 14214-2025 FSC-klagomål.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 28983-2024 FSC-klagomål.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 14214-2025 FSC-klagomål mail.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 28983-2024 FSC-klagomål mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 14214-2025 tillsynsbegäran.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 28983-2024 tillsynsbegäran.docx", "A 28983-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 14214-2025 tillsynsbegäran mail.docx", "A 14214-2025")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 14214-2025 prioriterade fågelarter.docx", "A 14214-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 28983-2024 tillsynsbegäran mail.docx", "A 28983-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12305-2026</t>
+          <t>A 1691-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3709,10 +3728,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46087</v>
+        <v>44938</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3724,19 +3743,14 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3766,50 +3780,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12305-2026 artfynd.xlsx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 1691-2023 artfynd.xlsx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12305-2026 karta.png", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 1691-2023 karta.png", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12305-2026 georefererad karta.tif", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 1691-2023 georefererad karta.tif", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12305-2026 FSC-klagomål.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 1691-2023 FSC-klagomål.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12305-2026 FSC-klagomål mail.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 1691-2023 FSC-klagomål mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12305-2026 tillsynsbegäran.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 1691-2023 tillsynsbegäran.docx", "A 1691-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12305-2026 tillsynsbegäran mail.docx", "A 12305-2026")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12305-2026 prioriterade fågelarter.docx", "A 12305-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 1691-2023 tillsynsbegäran mail.docx", "A 1691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12590-2026</t>
+          <t>A 61514-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3823,10 +3833,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46090</v>
+        <v>44916</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3838,13 +3848,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -3853,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3868,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3880,50 +3885,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12590-2026 artfynd.xlsx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 61514-2022 artfynd.xlsx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12590-2026 karta.png", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 61514-2022 karta.png", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12590-2026 georefererad karta.tif", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 61514-2022 georefererad karta.tif", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12590-2026 FSC-klagomål.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 61514-2022 FSC-klagomål.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12590-2026 FSC-klagomål mail.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 61514-2022 FSC-klagomål mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12590-2026 tillsynsbegäran.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 61514-2022 tillsynsbegäran.docx", "A 61514-2022")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12590-2026 tillsynsbegäran mail.docx", "A 12590-2026")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 12590-2026 prioriterade fågelarter.docx", "A 12590-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 61514-2022 tillsynsbegäran mail.docx", "A 61514-2022")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12842-2026</t>
+          <t>A 3681-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3937,10 +3938,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46092</v>
+        <v>44586</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3952,13 +3953,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3967,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3982,58 +3978,26 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Fyrflikig jordstjärna</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 12842-2026 artfynd.xlsx", "A 12842-2026")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 12842-2026 karta.png", "A 12842-2026")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 12842-2026 georefererad karta.tif", "A 12842-2026")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 12842-2026 FSC-klagomål.docx", "A 12842-2026")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 12842-2026 FSC-klagomål mail.docx", "A 12842-2026")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 12842-2026 tillsynsbegäran.docx", "A 12842-2026")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 12842-2026 tillsynsbegäran mail.docx", "A 12842-2026")</f>
-        <v/>
-      </c>
+      <c r="V32" s="2" t="inlineStr"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3681-2022</t>
+          <t>A 48667-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4047,10 +4011,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44586</v>
+        <v>44859</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4060,6 +4024,11 @@
       <c r="G33" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -4106,7 +4075,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 48667-2022</t>
+          <t>A 32828-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4120,10 +4089,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44859</v>
+        <v>44784</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4141,7 +4110,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4184,7 +4153,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32828-2022</t>
+          <t>A 73772-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4198,10 +4167,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44784</v>
+        <v>44552</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4213,13 +4182,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4279,7 +4243,7 @@
         <v>44859</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4340,7 +4304,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 73772-2021</t>
+          <t>A 14202-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4354,10 +4318,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44552</v>
+        <v>45740</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4370,7 +4334,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4413,7 +4377,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 16145-2024</t>
+          <t>A 3021-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4427,10 +4391,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45406</v>
+        <v>45678</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4442,8 +4406,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4486,7 +4455,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 46405-2022</t>
+          <t>A 6059-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4496,14 +4465,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44846</v>
+        <v>44599</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4516,7 +4485,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4559,7 +4528,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11867-2024</t>
+          <t>A 21285-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4573,10 +4542,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45376</v>
+        <v>45062</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4589,7 +4558,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4632,7 +4601,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30622-2024</t>
+          <t>A 27717-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4642,14 +4611,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45495</v>
+        <v>46190</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4661,8 +4630,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4722,7 +4696,7 @@
         <v>45113</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4783,7 +4757,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 48656-2022</t>
+          <t>A 54468-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4797,10 +4771,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44859</v>
+        <v>45965</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4812,13 +4786,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4861,7 +4830,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38194-2022</t>
+          <t>A 16142-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4875,10 +4844,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44812</v>
+        <v>45406</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4891,7 +4860,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4934,7 +4903,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 45869-2022</t>
+          <t>A 11876-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4948,10 +4917,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44844</v>
+        <v>45376</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4964,7 +4933,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5007,7 +4976,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 73151-2021</t>
+          <t>A 14217-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5021,10 +4990,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44550</v>
+        <v>45740</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5037,7 +5006,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5080,7 +5049,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 73194-2021</t>
+          <t>A 12306-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5094,10 +5063,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44550</v>
+        <v>46087</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5107,6 +5076,11 @@
       <c r="G47" t="inlineStr">
         <is>
           <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -5153,7 +5127,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 14217-2025</t>
+          <t>A 12294-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5167,10 +5141,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45740</v>
+        <v>46087</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5182,8 +5156,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5226,7 +5205,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 73155-2021</t>
+          <t>A 73194-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5243,7 +5222,7 @@
         <v>44550</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5256,7 +5235,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5299,7 +5278,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11876-2024</t>
+          <t>A 35108-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5313,10 +5292,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45376</v>
+        <v>46258</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5329,7 +5308,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5372,7 +5351,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16142-2024</t>
+          <t>A 16483-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5386,10 +5365,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45406</v>
+        <v>45029</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5402,7 +5381,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5445,7 +5424,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 15692-2023</t>
+          <t>A 22391-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5459,10 +5438,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45020</v>
+        <v>46154</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5475,7 +5454,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5518,7 +5497,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 14202-2025</t>
+          <t>A 23725-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5532,10 +5511,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45740</v>
+        <v>46164</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5548,7 +5527,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5591,7 +5570,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54468-2025</t>
+          <t>A 46405-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5605,10 +5584,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45965</v>
+        <v>44846</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5621,7 +5600,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5664,7 +5643,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 20649-2022</t>
+          <t>A 23716-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5678,10 +5657,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44700</v>
+        <v>46164</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5693,13 +5672,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5742,7 +5716,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 21285-2023</t>
+          <t>A 23718-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5756,10 +5730,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45062</v>
+        <v>46164</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5772,7 +5746,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5815,7 +5789,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 6059-2022</t>
+          <t>A 20649-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5825,14 +5799,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44599</v>
+        <v>44700</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5844,8 +5818,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5905,7 +5884,7 @@
         <v>45355</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5961,7 +5940,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3021-2025</t>
+          <t>A 45869-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5975,10 +5954,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45678</v>
+        <v>44844</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5990,13 +5969,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6056,7 +6030,7 @@
         <v>44586</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6112,7 +6086,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 9032-2023</t>
+          <t>A 15692-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6126,10 +6100,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44979</v>
+        <v>45020</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6142,7 +6116,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6185,7 +6159,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25217-2024</t>
+          <t>A 73151-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6195,14 +6169,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45462</v>
+        <v>44550</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6214,13 +6188,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6263,7 +6232,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 16483-2023</t>
+          <t>A 9032-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6277,10 +6246,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45029</v>
+        <v>44979</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6293,7 +6262,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6336,7 +6305,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 22391-2026</t>
+          <t>A 73155-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6350,10 +6319,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46154</v>
+        <v>44550</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6366,7 +6335,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6409,7 +6378,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12306-2026</t>
+          <t>A 48656-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6423,10 +6392,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46087</v>
+        <v>44859</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6487,7 +6456,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 12294-2026</t>
+          <t>A 38194-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6501,10 +6470,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46087</v>
+        <v>44812</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6516,13 +6485,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6565,7 +6529,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 23725-2026</t>
+          <t>A 11867-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6579,10 +6543,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46164</v>
+        <v>45376</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6595,7 +6559,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6638,7 +6602,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 23718-2026</t>
+          <t>A 25217-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6648,14 +6612,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46164</v>
+        <v>45462</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6667,8 +6631,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6711,7 +6680,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23716-2026</t>
+          <t>A 30622-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6721,14 +6690,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46164</v>
+        <v>45495</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6741,7 +6710,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6784,7 +6753,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 27717-2026</t>
+          <t>A 16145-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6798,10 +6767,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46190</v>
+        <v>45406</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6813,13 +6782,8 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6859,27 +6823,27 @@
       </c>
       <c r="V70" s="2" t="inlineStr"/>
     </row>
-    <row r="71" ht="15" customHeight="1">
+    <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35108-2026</t>
+          <t>S 380-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46258</v>
+        <v>46065</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6891,8 +6855,13 @@
           <t>BOTKYRKA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>6.4</v>
+        <v>0.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6931,84 +6900,6 @@
         <v>0</v>
       </c>
       <c r="V71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>S 380-2026</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="n">
-        <v>46065</v>
-      </c>
-      <c r="E72" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I72" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BOTKYRKA.xlsx
+++ b/Översikt BOTKYRKA.xlsx
@@ -601,7 +601,7 @@
         <v>44930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 25306-2026</t>
+          <t>A 24599-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46176</v>
+        <v>44727</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -732,45 +732,159 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>4</v>
       </c>
-      <c r="K3" t="n">
+      <c r="R3" t="n">
         <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
       </c>
       <c r="T3" t="n">
+        <v>11</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Almsnabbvinge
+Mindre tåtelsmygare
+Igelkottsröksvamp
+Mandelriska
+Sotriska
+Mattlummer
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 25306-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="n">
         <v>14</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>14</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Slåtterfibbla
@@ -784,150 +898,36 @@
 Gröngöling</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 25306-2026 artfynd.xlsx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 25306-2026 karta.png", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 25306-2026 georefererad karta.tif", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 25306-2026 FSC-klagomål.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 25306-2026 FSC-klagomål mail.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 25306-2026 tillsynsbegäran.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 25306-2026 tillsynsbegäran mail.docx", "A 25306-2026")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0127/fåglar/A 25306-2026 prioriterade fågelarter.docx", "A 25306-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 24599-2022</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44727</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BOTKYRKA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>11</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Almsnabbvinge
-Mindre tåtelsmygare
-Igelkottsröksvamp
-Mandelriska
-Sotriska
-Mattlummer
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 24599-2022 artfynd.xlsx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 24599-2022 karta.png", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 24599-2022 georefererad karta.tif", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 24599-2022 FSC-klagomål.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 24599-2022 FSC-klagomål mail.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 24599-2022 tillsynsbegäran.docx", "A 24599-2022")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 24599-2022 tillsynsbegäran mail.docx", "A 24599-2022")</f>
         <v/>
       </c>
     </row>
@@ -951,7 +951,7 @@
         <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45747</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45740</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45748</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>44938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18100-2022</t>
+          <t>A 30378-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2203,14 +2203,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44684</v>
+        <v>45491</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2223,16 +2223,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2256,703 +2256,703 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 30378-2024 artfynd.xlsx", "A 30378-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 30378-2024 karta.png", "A 30378-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 30378-2024 georefererad karta.tif", "A 30378-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 30378-2024 FSC-klagomål.docx", "A 30378-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 30378-2024 FSC-klagomål mail.docx", "A 30378-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 30378-2024 tillsynsbegäran.docx", "A 30378-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 30378-2024 tillsynsbegäran mail.docx", "A 30378-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 15905-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44664</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>3</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/artfynd/A 15905-2022 artfynd.xlsx", "A 15905-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor/A 15905-2022 karta.png", "A 15905-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/kartor_geotiff/A 15905-2022 georefererad karta.tif", "A 15905-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomål/A 15905-2022 FSC-klagomål.docx", "A 15905-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/klagomålsmail/A 15905-2022 FSC-klagomål mail.docx", "A 15905-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsyn/A 15905-2022 tillsynsbegäran.docx", "A 15905-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0127/tillsynsmail/A 15905-2022 tillsynsbegäran mail.docx", "A 15905-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 60406-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>BOTKYRKA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.3</v>
+